--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recalls" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Recalls" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17657,7 +17657,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-29 11:35 UTC</t>
+          <t>Generated: 2026-04-29 20:04 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -17657,7 +17657,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-29 20:04 UTC</t>
+          <t>Generated: 2026-04-29 20:29 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -23908,7 +23908,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 18:29 UTC</t>
+          <t>Generated: 2026-05-04 18:36 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/2026.3863</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/841474</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/2026.3862</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/841471</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/2026.3858</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/841438</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/2026.3853</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838827</t>
         </is>
       </c>
     </row>
@@ -24160,7 +24160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 20:18 UTC</t>
+          <t>Generated: 2026-05-04 20:53 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -24160,7 +24160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 20:53 UTC</t>
+          <t>Generated: 2026-05-05 13:26 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -32833,17 +32833,17 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Salaisons Jouvin</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Salaisons Jouvin</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>viandes</t>
+          <t>Merguez Bœuf Volaille Halal — Barquette de 5kg (Lot 611705, DDM 15/05/2026)</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr">
@@ -32892,17 +32892,17 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Palais des Mets</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Palais des Mets</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>plats préparés et snacks</t>
+          <t>Saumon bio Atlantique fumé Ecosse 2 tranches 80g (3 lots, GTIN 3760089333983, DLC 15-24/05/2026)</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
@@ -32951,17 +32951,17 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Germline</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Germline</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>noix et graines</t>
+          <t>Graines germées biologiques Alfalfa — Barquettes 60g (Lot 260429, DLC 15/05/2026, GTIN 3465511911608)</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
@@ -33010,17 +33010,17 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>K.S.P. (Kruz Seafood Production)</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>aucune</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>Crevette cuite réfrigérée 40/60 P. Vannamei élevage OP 2KG (Lot 180421, GTIN 3760283210035, DLC 01/05/2026)</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
@@ -33069,17 +33069,17 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>HERTA</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HERTA</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>viandes</t>
+          <t>Lardons Fumés 200g et 200g+25% (3 GTINs, Lots 6145084101/6146084101, DLC 25-26/05/2026)</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
@@ -33128,17 +33128,17 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Ferme baracand</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ferme baracand</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>lait et produits laitiers</t>
+          <t>Picodon (cheese) — emballé par 3 ou à l'unité (Lot 97, DLC 16/06/2026, GTIN 3770016897129/006)</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
@@ -33187,17 +33187,17 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>PURASANA</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PURASANA</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>aliments diététiques et nutrition</t>
+          <t>MORINGA POUDRE 200 G — sachet doypack (Lot MPCHS1224/26, GTIN 5400706615587, DLC 30/06/2028)</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -33246,17 +33246,17 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>FOODMAKER</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FOODMAKER</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>plats préparés et snacks</t>
+          <t>Salade Penne Chicken Lemon 300g (Lot TGT 01/05/2026, GTIN 5407009903120)</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
@@ -33326,7 +33326,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-06 18:26 UTC</t>
+          <t>Generated: 2026-05-06 18:52 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -588,7 +588,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1635,7 +1635,7 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Volontaire</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
@@ -18218,7 +18218,7 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr">
@@ -20108,7 +20108,7 @@
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr">
@@ -20864,7 +20864,7 @@
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I330" s="2" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I331" s="2" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I332" s="2" t="inlineStr">
@@ -21305,7 +21305,7 @@
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr">
@@ -21368,7 +21368,7 @@
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr">
@@ -21557,7 +21557,7 @@
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I337" s="2" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr">
@@ -21746,7 +21746,7 @@
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I341" s="2" t="inlineStr">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr">
@@ -21935,7 +21935,7 @@
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I349" s="2" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I350" s="2" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I351" s="2" t="inlineStr">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I359" s="2" t="inlineStr">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr">
@@ -23124,7 +23124,7 @@
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
@@ -23439,7 +23439,7 @@
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr">
@@ -23502,7 +23502,7 @@
       </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I368" s="2" t="inlineStr">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I369" s="2" t="inlineStr">
@@ -23628,7 +23628,7 @@
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall (prefectural order)</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr">
@@ -25896,7 +25896,7 @@
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>Mandatory recall</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I406" s="2" t="inlineStr">
@@ -33578,7 +33578,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-07 05:15 UTC</t>
+          <t>Generated: 2026-05-07 06:53 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recalls" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="About" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recalls" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33578,7 +33578,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-07 06:53 UTC</t>
+          <t>Generated: 2026-05-07 05:15 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -36791,7 +36791,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-11 20:18 UTC</t>
+          <t>Generated: 2026-05-12 13:21 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -36791,7 +36791,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 13:21 UTC</t>
+          <t>Generated: 2026-05-12 18:50 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M578"/>
+  <dimension ref="A1:M589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36757,6 +36757,699 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>RappelConso (FR)</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>CHARCUTERIE PIERRE SCHMIDT Pierre Schmidt</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>Les Créations de Pierre</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>poitrine fumée 350g pierre schmidt</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>Listeria monocytogenes</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>mise en évidence de la présence de listeria monocytogenes</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>volontaire (sans arrêté préfectoral)</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="J579" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K579" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L579" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M579" s="2" t="inlineStr">
+        <is>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22238/Interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>RappelConso (FR)</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>METRO FRANCE</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Aro</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>saumon fume atlantique pre tranche 600g / 900g aro</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Listeria monocytogenes</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>présence de listeria monocytogenes</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>volontaire (sans arrêté préfectoral)</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K580" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L580" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M580" s="2" t="inlineStr">
+        <is>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22252/Interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>RASFF (EU)</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>Origin: South Korea | Notifying: Sweden</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>Norovirus in nori (roasted seaweed)</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>Norovirus</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>Norovirus in nori (roasted seaweed); risk: serious; category: fruits and vegetables</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="J581" s="2" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="K581" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L581" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M581" s="2" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/843057</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>RASFF (EU)</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>Origin: Madagascar | Notifying: Croatia</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>Madagascar</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>Bacillus cereus in ground cinnamon from Madagascar</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>Bacillus cereus</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>Bacillus cereus in ground cinnamon from Madagascar; risk: serious; category: herbs and spices</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>Madagascar</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="K582" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L582" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M582" s="2" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/843280</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>RASFF (EU)</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>Origin: France | Notifying: Italy</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>norovirus in oysters from France</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>Norovirus</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>norovirus in oysters from France; risk: not serious; category: bivalve molluscs and products thereof</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="J583" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K583" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L583" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M583" s="2" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/842863</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>RASFF (EU)</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>Origin: Ireland | Notifying: Netherlands</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>Shigatoxin producing Escherichia coli (STEC) in Bovine steak from Ireland</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>Shigatoxin producing Escherichia coli (STEC) in Bovine steak from Ireland; risk: potentially serious; category: meat and meat products (other than poultry)</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K584" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L584" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M584" s="2" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/843130</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>RASFF (EU)</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>Origin: Netherlands | Notifying: Netherlands</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>Eggs from a Dutch stable that tested positive for Salmonella</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>Salmonella</t>
+        </is>
+      </c>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>Eggs from a Dutch stable that tested positive for Salmonella; risk: potentially serious; category: eggs and egg products</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="J585" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K585" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L585" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M585" s="2" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/842725</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>RASFF (EU)</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>Origin: China | Notifying: Greece</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>Aflatoxins in blanched groundnut kernels from China</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>Aflatoxin</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>Aflatoxins in blanched groundnut kernels from China; risk: serious; category: nuts, nut products and seeds</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>Border Rejection</t>
+        </is>
+      </c>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="K586" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L586" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M586" s="2" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/842971</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>RASFF (EU)</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>Origin: Ukraine | Notifying: Germany</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>Salmonella Stanley in instant noodle meal from Ukraine, via Poland</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>Salmonella</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>Salmonella Stanley in instant noodle meal from Ukraine, via Poland; risk: serious; category: prepared dishes and snacks</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K587" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L587" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M587" s="2" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/843316</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>CFIA</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>Germina</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>Germina</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>"Brocoli Calabrese" seeds</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>Escherichia coli (generic)</t>
+        </is>
+      </c>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>Germina brand "Brocoli Calabrese" seeds recalled due to possible contamination with pathogenic E. coli</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>Class 1</t>
+        </is>
+      </c>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="K588" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L588" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M588" s="2" t="inlineStr">
+        <is>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/germina-brand-brocoli-calabrese-seeds-recalled-due-possible-contamination-pathogenic-e</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>FSAI (IE)</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>Lidl</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>Picture of Free Range 100% Irish Chicken Breast Fillets</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>Salmonella</t>
+        </is>
+      </c>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>Picture of Free Range 100% Irish Chicken Breast Fillets</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="I589" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="J589" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K589" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L589" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-a-batch-of-free-range-100-irish-chicken</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36791,14 +37484,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 18:50 UTC</t>
+          <t>Generated: 2026-05-12 20:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Records: 577</t>
+          <t>Records: 588</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>présence d'ochratoxine a au dessus du seuil réglementaire</t>
+          <t>Presence of Ochratoxin A above the regulatory threshold</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>mise en évidence de la présence de listeria monocytogenes</t>
+          <t>Microbiological testing detected the presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>présence de listeria monocytogenes</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>détection listeria monocytogenes</t>
+          <t>Detection of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>présence de bactérie pathogène</t>
+          <t>Presence of pathogenic bacteria</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>taux de listeria à dlc supérieur à la réglementation</t>
+          <t>Listeria count at end of shelf life above regulatory limit</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>présence de listeria monocytogenes.</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Contamination par Salmonella</t>
+          <t>Contamination with Salmonella</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Contamination par Salmonella</t>
+          <t>Contamination with Salmonella</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Contamination par Salmonella</t>
+          <t>Contamination with Salmonella</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Contamination par Salmonella</t>
+          <t>Contamination with Salmonella</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Contamination par Salmonella</t>
+          <t>Contamination with Salmonella</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>un contrôle microbiologique a mis en évidence dans un lot de ce produit la présence de salmonelle</t>
+          <t>Microbiological testing detected the presence of Salmonella in a batch of the product</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>présence de salmonelle</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>présence de listéria</t>
+          <t>Presence of Listeria</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>présence e. coli dans l'environnement supérieure aux seuils réglementaires.</t>
+          <t>Detection of E. coli in the production environment above regulatory thresholds</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Contamination par Listeria monocytogenes</t>
+          <t>Contamination with Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Détection d'Aflatoxin</t>
+          <t>Detection of Aflatoxin</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Détection de Listeria monocytogenes</t>
+          <t>Detection of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Détection de Listeria monocytogenes</t>
+          <t>Detection of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>Présence de Salmonelles</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -33010,7 +33010,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>Présence de Salmonelles</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -33073,7 +33073,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>Contamination Salmonelle - en cours d'identification</t>
+          <t>Salmonella contamination (serotype identification in progress)</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -33640,7 +33640,7 @@
       </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
-          <t>Présence de Salmonelle</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H529" s="2" t="inlineStr">
@@ -33892,7 +33892,7 @@
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>Présence de Listeria monocytogenes</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
@@ -38429,7 +38429,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-14 06:53 UTC</t>
+          <t>Generated: 2026-05-14 07:29 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M611"/>
+  <dimension ref="A1:M613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -557,27 +557,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SARL Sarda</t>
+          <t>HH Fresh Trading</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SARL Sarda</t>
+          <t>HH Fresh Trading</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>White ham nuts or white ham heels (pork cuts)</t>
+          <t>TW Enoki Mushrooms 150g (120 cases, code 4711498860002)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -587,22 +587,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Detection of Listeria monocytogenes</t>
+          <t>Product tested positive for Listeria monocytogenes. Florida Health Department lab-tested the enoki on 2026-04-20, results returned 2026-04-28; FDA notified company 2026-05-11. Batch was sold to Texas 2026-02-23 and redistributed to Florida.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22265/Interne</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/hh-fresh-trading-recalls-tw-enoki-mushrooms-150g-because-possible-health-risk</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AGRIBERIA SARL AGRIBERIA</t>
+          <t>SARL Sarda</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Ipanema</t>
+          <t>SARL Sarda</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ipanema cheese curds</t>
+          <t>White ham nuts or white ham heels (pork cuts)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes</t>
+          <t>Detection of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22249/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22265/Interne</t>
         </is>
       </c>
     </row>
@@ -693,27 +693,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PERODIS SA INTERMARCHE</t>
+          <t>AGRIBERIA SARL AGRIBERIA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Ipanema</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Marinated chicken kebab fillets</t>
+          <t>Ipanema cheese curds</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Presence of Salmonella</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22241/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22249/Interne</t>
         </is>
       </c>
     </row>
@@ -756,27 +756,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Dulci</t>
+          <t>PERODIS SA INTERMARCHE</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Dulci</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>pâte à tartiner dulci dubaï style 40 % pistache¤lot pt08</t>
+          <t>Marinated chicken kebab fillets</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Presence of Ochratoxin A above the regulatory threshold</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -795,14 +795,14 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22253/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22241/Interne</t>
         </is>
       </c>
     </row>
@@ -814,42 +814,42 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Origin: Spain | Notifying: France</t>
+          <t>Dulci</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>Dulci</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes in cheese</t>
+          <t>pâte à tartiner dulci dubaï style 40 % pistache¤lot pt08</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes in cheese; risk: serious; category: milk and milk products</t>
+          <t>Presence of Ochratoxin A above the regulatory threshold</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -858,14 +858,14 @@
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/844028</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22253/Interne</t>
         </is>
       </c>
     </row>
@@ -877,42 +877,42 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
+          <t>Origin: Spain | Notifying: France</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>fromage montagnard 450g</t>
+          <t>Presence of Listeria monocytogenes in cheese</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing E. coli (STEC)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>présence de escherichia coli stec</t>
+          <t>Presence of Listeria monocytogenes in cheese; risk: serious; category: milk and milk products</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22273/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/844028</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>fromage montagnard 450g</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22274/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22273/Interne</t>
         </is>
       </c>
     </row>
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Metro France</t>
+          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Metro Chef</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>oignon jaune epluche 2kg metro chef</t>
+          <t>reblochon de savoie fermier aop 450g</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>présence de listeria monocytogenes</t>
+          <t>présence de escherichia coli stec</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22264/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22274/Interne</t>
         </is>
       </c>
     </row>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
+          <t>Metro France</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Le farto de Thônes</t>
+          <t>Metro Chef</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Reblochon de Savoie fermier AOP 450g</t>
+          <t>oignon jaune epluche 2kg metro chef</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Escherichia coli STEC</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>présence de escherichia coli stec</t>
+          <t>présence de listeria monocytogenes</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22275/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22264/Interne</t>
         </is>
       </c>
     </row>
@@ -1129,58 +1129,58 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FSANZ</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Sanulac Nutritionals Australia Pty Ltd</t>
+          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Alula Gold</t>
+          <t>Le farto de Thônes</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Alula Gold Reflux infant formula 900g (0-12 months) and Alula Gold Premium infant formula 900g</t>
+          <t>Reblochon de Savoie fermier AOP 450g</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Escherichia coli STEC</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Cereulide — outbreak</t>
+          <t>présence de escherichia coli stec</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://www.foodstandards.gov.au/news/cereulide-toxin-infant-formula-products</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22275/Interne</t>
         </is>
       </c>
     </row>
@@ -36954,58 +36954,58 @@
       </c>
       <c r="B582" s="2" t="inlineStr">
         <is>
-          <t>COFEPRIS (MX)</t>
+          <t>FSANZ</t>
         </is>
       </c>
       <c r="C582" s="2" t="inlineStr">
         <is>
-          <t>SANULAC NUTRICIÓN MÉXICO S. de R.L. de C.V.</t>
+          <t>Sanulac Nutritionals Australia Pty Ltd</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>ALULA Gold Premium / ALULA Gold Comfort</t>
+          <t>Alula Gold</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
         <is>
-          <t>ALULA Gold Premium 1, 2, 3 + ALULA Gold Comfort Kid Premium + ALULA Gold Comfort Premium (38 lots, imported from France, expirations Nov 2026 – Mar 2027)</t>
+          <t>Alula Gold Reflux infant formula 900g (0-12 months) and Alula Gold Premium infant formula 900g</t>
         </is>
       </c>
       <c r="F582" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="G582" s="2" t="inlineStr">
         <is>
-          <t>Preventive market withdrawal — possible cereulide contamination in one ingredient</t>
+          <t>Cereulide — outbreak</t>
         </is>
       </c>
       <c r="H582" s="2" t="inlineStr">
         <is>
-          <t>Sanitary alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="J582" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K582" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L582" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M582" s="2" t="inlineStr">
         <is>
-          <t>https://www.gob.mx/cms/uploads/attachment/file/1051500/Alerta_Sanitaria__Alula_23012026.pdf</t>
+          <t>https://www.foodstandards.gov.au/news/cereulide-toxin-infant-formula-products</t>
         </is>
       </c>
     </row>
@@ -37017,47 +37017,47 @@
       </c>
       <c r="B583" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>COFEPRIS (MX)</t>
         </is>
       </c>
       <c r="C583" s="2" t="inlineStr">
         <is>
-          <t>Navitas Organics</t>
+          <t>SANULAC NUTRICIÓN MÉXICO S. de R.L. de C.V.</t>
         </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>Navitas Organics</t>
+          <t>ALULA Gold Premium / ALULA Gold Comfort</t>
         </is>
       </c>
       <c r="E583" s="2" t="inlineStr">
         <is>
-          <t>Organic Chia Seeds, 8 oz</t>
+          <t>ALULA Gold Premium 1, 2, 3 + ALULA Gold Comfort Kid Premium + ALULA Gold Comfort Premium (38 lots, imported from France, expirations Nov 2026 – Mar 2027)</t>
         </is>
       </c>
       <c r="F583" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G583" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Preventive market withdrawal — possible cereulide contamination in one ingredient</t>
         </is>
       </c>
       <c r="H583" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Sanitary alert</t>
         </is>
       </c>
       <c r="I583" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="J583" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K583" s="2" t="n">
@@ -37068,7 +37068,7 @@
       </c>
       <c r="M583" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/navitas-organics-voluntarily-recalls-select-lots-8oz-organic-chia-seeds-because-possible-health-risk</t>
+          <t>https://www.gob.mx/cms/uploads/attachment/file/1051500/Alerta_Sanitaria__Alula_23012026.pdf</t>
         </is>
       </c>
     </row>
@@ -37080,22 +37080,22 @@
       </c>
       <c r="B584" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C584" s="2" t="inlineStr">
         <is>
-          <t>(BLV public warning — multiple producers)</t>
+          <t>Navitas Organics</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>Migros</t>
+          <t>Navitas Organics</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
         <is>
-          <t>Bio-Power Mix</t>
+          <t>Organic Chia Seeds, 8 oz</t>
         </is>
       </c>
       <c r="F584" s="2" t="inlineStr">
@@ -37105,22 +37105,22 @@
       </c>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in Bio-Power Mix</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H584" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I584" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J584" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K584" s="2" t="n">
@@ -37131,7 +37131,7 @@
       </c>
       <c r="M584" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-bio-power-mix.pdf.download.pdf/Oeffentliche%20Warnung_Salmonellen%20in%20Bio%20Power%20Mix_verkauft%20bei%20Migros%20DE.pdf</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/navitas-organics-voluntarily-recalls-select-lots-8oz-organic-chia-seeds-because-possible-health-risk</t>
         </is>
       </c>
     </row>
@@ -37143,42 +37143,42 @@
       </c>
       <c r="B585" s="2" t="inlineStr">
         <is>
-          <t>FSAI</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C585" s="2" t="inlineStr">
         <is>
-          <t>Danone infant formula and follow-on formula</t>
+          <t>(BLV public warning — multiple producers)</t>
         </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>Danone infant formula and follow-on formula</t>
+          <t>Migros</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr">
         <is>
-          <t>| Food Safety Authority of Ireland</t>
+          <t>Bio-Power Mix</t>
         </is>
       </c>
       <c r="F585" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G585" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Salmonella detected in Bio-Power Mix</t>
         </is>
       </c>
       <c r="H585" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I585" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J585" s="2" t="inlineStr">
@@ -37194,7 +37194,7 @@
       </c>
       <c r="M585" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/latest-news/danone-infant-formula-and-follow-on-formula-recall</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-bio-power-mix.pdf.download.pdf/Oeffentliche%20Warnung_Salmonellen%20in%20Bio%20Power%20Mix_verkauft%20bei%20Migros%20DE.pdf</t>
         </is>
       </c>
     </row>
@@ -37206,22 +37206,22 @@
       </c>
       <c r="B586" s="2" t="inlineStr">
         <is>
-          <t>FAVV</t>
+          <t>FSAI</t>
         </is>
       </c>
       <c r="C586" s="2" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>Danone infant formula and follow-on formula</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>Nutrilon</t>
+          <t>Danone infant formula and follow-on formula</t>
         </is>
       </c>
       <c r="E586" s="2" t="inlineStr">
         <is>
-          <t>Various Nutrilon infant formula</t>
+          <t>| Food Safety Authority of Ireland</t>
         </is>
       </c>
       <c r="F586" s="2" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="G586" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin) contamination</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="H586" s="2" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="I586" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J586" s="2" t="inlineStr">
@@ -37257,54 +37257,54 @@
       </c>
       <c r="M586" s="2" t="inlineStr">
         <is>
-          <t>https://favv-afsca.be/nl/producten/terugroeping-van-danone-0</t>
+          <t>https://www.fsai.ie/news-and-alerts/latest-news/danone-infant-formula-and-follow-on-formula-recall</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B587" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>FAVV</t>
         </is>
       </c>
       <c r="C587" s="2" t="inlineStr">
         <is>
-          <t>Origin: Italy | Notifying: Austria | Distributed: Austria, Belgium, France, Germany, Ireland, Liechtenstein, Slovenia, Spain, Switzerland, UK (Northern Ireland)</t>
+          <t>Danone</t>
         </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nutrilon</t>
         </is>
       </c>
       <c r="E587" s="2" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Various Nutrilon infant formula</t>
         </is>
       </c>
       <c r="F587" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Cereulide (B. cereus toxin)</t>
         </is>
       </c>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes detected in cheese of Italian origin distributed across 10+ EU/EEA countries plus UK (Northern Ireland) — alert notification</t>
+          <t>Cereulide (B. cereus toxin) contamination</t>
         </is>
       </c>
       <c r="H587" s="2" t="inlineStr">
         <is>
-          <t>Alert notification</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I587" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="J587" s="2" t="inlineStr">
@@ -37320,77 +37320,77 @@
       </c>
       <c r="M587" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/818280</t>
+          <t>https://favv-afsca.be/nl/producten/terugroeping-van-danone-0</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B588" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>FSANZ</t>
         </is>
       </c>
       <c r="C588" s="2" t="inlineStr">
         <is>
-          <t>Superfoods, Inc. (dba Live it Up)</t>
+          <t>Nestlé Australia</t>
         </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>Live it Up</t>
+          <t>Alfamino</t>
         </is>
       </c>
       <c r="E588" s="2" t="inlineStr">
         <is>
-          <t>Super Greens dietary supplement powder (Original + Wild Berry)</t>
+          <t>Alfamino Infant Formula (0-12 months) 400g (5 batches)</t>
         </is>
       </c>
       <c r="F588" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Typhimurium</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Potential presence of cereulide toxin (produced by Bacillus cereus). Linked to a contaminated ingredient identified through international recalls. No cases of illness reported in Australia.</t>
         </is>
       </c>
       <c r="H588" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I588" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="J588" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K588" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L588" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M588" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/superfoods-inc-dba-live-it-recalls-live-it-super-greens-because-possible-health-risk</t>
+          <t>https://www.foodstandards.gov.au/food-recalls/recall-alert/nestle-alfamino-infant-formula-0-12-months-400g</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B589" s="2" t="inlineStr">
@@ -37400,7 +37400,7 @@
       </c>
       <c r="C589" s="2" t="inlineStr">
         <is>
-          <t>Origin: Argentina | Notifying: Netherlands | Distributed: Netherlands, Uruguay</t>
+          <t>Origin: Italy | Notifying: Austria | Distributed: Austria, Belgium, France, Germany, Ireland, Liechtenstein, Slovenia, Spain, Switzerland, UK (Northern Ireland)</t>
         </is>
       </c>
       <c r="D589" s="2" t="inlineStr">
@@ -37410,27 +37410,27 @@
       </c>
       <c r="E589" s="2" t="inlineStr">
         <is>
-          <t>Groundnuts kernels runner</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="F589" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G589" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin contamination detected in groundnut runner kernels from Argentina, distributed in Netherlands and Uruguay — found by company's own check</t>
+          <t>Listeria monocytogenes detected in cheese of Italian origin distributed across 10+ EU/EEA countries plus UK (Northern Ireland) — alert notification</t>
         </is>
       </c>
       <c r="H589" s="2" t="inlineStr">
         <is>
-          <t>Information notification for attention</t>
+          <t>Alert notification</t>
         </is>
       </c>
       <c r="I589" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="J589" s="2" t="inlineStr">
@@ -37439,14 +37439,14 @@
         </is>
       </c>
       <c r="K589" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L589" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M589" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/817723</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/818280</t>
         </is>
       </c>
     </row>
@@ -37458,42 +37458,42 @@
       </c>
       <c r="B590" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C590" s="2" t="inlineStr">
         <is>
-          <t>Left Coast Organics</t>
+          <t>Superfoods, Inc. (dba Live it Up)</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>Left Coast Organics</t>
+          <t>Live it Up</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
         <is>
-          <t>Organic Chia Seeds (900 g)</t>
+          <t>Super Greens dietary supplement powder (Original + Wild Berry)</t>
         </is>
       </c>
       <c r="F590" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Salmonella Typhimurium</t>
         </is>
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I590" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J590" s="2" t="inlineStr">
@@ -37505,11 +37505,11 @@
         <v>1</v>
       </c>
       <c r="L590" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M590" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/left-coast-organics-brand-organic-chia-seeds-recalled-due-salmonella</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/superfoods-inc-dba-live-it-recalls-live-it-super-greens-because-possible-health-risk</t>
         </is>
       </c>
     </row>
@@ -37521,110 +37521,110 @@
       </c>
       <c r="B591" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C591" s="2" t="inlineStr">
         <is>
-          <t>General Mills Canada / Pillsbury</t>
+          <t>Origin: Argentina | Notifying: Netherlands | Distributed: Netherlands, Uruguay</t>
         </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>Pizza Pops (full product line)</t>
+          <t>Groundnuts kernels runner</t>
         </is>
       </c>
       <c r="F591" s="2" t="inlineStr">
         <is>
-          <t>E. coli O26 (STEC)</t>
+          <t>Aflatoxins</t>
         </is>
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Aflatoxin contamination detected in groundnut runner kernels from Argentina, distributed in Netherlands and Uruguay — found by company's own check</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Information notification for attention</t>
         </is>
       </c>
       <c r="I591" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J591" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K591" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L591" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M591" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/certain-pillsbury-brand-pizza-pops-recalled-due-e-coli-o26</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/817723</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B592" s="2" t="inlineStr">
         <is>
-          <t>INVIMA (CO)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C592" s="2" t="inlineStr">
         <is>
-          <t>Nestlé de Colombia S.A.</t>
+          <t>Left Coast Organics</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>NAN Alfamino</t>
+          <t>Left Coast Organics</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>Food for special medical purposes, powder, 400 g, lot 52660017Y2</t>
+          <t>Organic Chia Seeds (900 g)</t>
         </is>
       </c>
       <c r="F592" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>Contamination with cereulide toxin</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I592" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J592" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K592" s="2" t="n">
@@ -37635,54 +37635,54 @@
       </c>
       <c r="M592" s="2" t="inlineStr">
         <is>
-          <t>https://www.invima.gov.co/blog/sala-de-prensa-13/alimento-para-propositos-medicos-especiales-contaminado-con-toxina-cereulida-no-ha-sido-comercializado-en-colombia-279</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/left-coast-organics-brand-organic-chia-seeds-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B593" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C593" s="2" t="inlineStr">
         <is>
-          <t>Tri-Union Seafoods</t>
+          <t>General Mills Canada / Pillsbury</t>
         </is>
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>Genova</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E593" s="2" t="inlineStr">
         <is>
-          <t>Yellowfin Tuna in Olive Oil 5 oz 4-pack + 5 oz can EVOO</t>
+          <t>Pizza Pops (full product line)</t>
         </is>
       </c>
       <c r="F593" s="2" t="inlineStr">
         <is>
-          <t>Clostridium botulinum</t>
+          <t>E. coli O26 (STEC)</t>
         </is>
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>Botulism risk — defective easy-open pull tabs</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I593" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J593" s="2" t="inlineStr">
@@ -37694,38 +37694,38 @@
         <v>1</v>
       </c>
       <c r="L593" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M593" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/tri-union-seafoods-identifies-additional-quantities-recalled-genovar-tuna-limited-retailers-due</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/certain-pillsbury-brand-pizza-pops-recalled-due-e-coli-o26</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B594" s="2" t="inlineStr">
         <is>
-          <t>SFA (SG)</t>
+          <t>INVIMA (CO)</t>
         </is>
       </c>
       <c r="C594" s="2" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Nestlé de Colombia S.A.</t>
         </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>Nestle NAN HA1 SupremePro</t>
+          <t>NAN Alfamino</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
         <is>
-          <t>800 g infant formula, batch 52340017C3, expiry 2027-08-31, country of origin Switzerland</t>
+          <t>Food for special medical purposes, powder, 400 g, lot 52660017Y2</t>
         </is>
       </c>
       <c r="F594" s="2" t="inlineStr">
@@ -37735,7 +37735,7 @@
       </c>
       <c r="G594" s="2" t="inlineStr">
         <is>
-          <t>Presence of cereulide toxin</t>
+          <t>Contamination with cereulide toxin</t>
         </is>
       </c>
       <c r="H594" s="2" t="inlineStr">
@@ -37745,12 +37745,12 @@
       </c>
       <c r="I594" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="J594" s="2" t="inlineStr">
         <is>
-          <t>Asia-Pacific</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K594" s="2" t="n">
@@ -37761,44 +37761,44 @@
       </c>
       <c r="M594" s="2" t="inlineStr">
         <is>
-          <t>https://www.sfa.gov.sg/news-publications/newsroom/direction-to-recall-additional-infant-formula-products-due-to-presence-of-cereulide-toxin</t>
+          <t>https://www.invima.gov.co/blog/sala-de-prensa-13/alimento-para-propositos-medicos-especiales-contaminado-con-toxina-cereulida-no-ha-sido-comercializado-en-colombia-279</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B595" s="2" t="inlineStr">
         <is>
-          <t>USDA FSIS</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C595" s="2" t="inlineStr">
         <is>
-          <t>Suzanna's Kitchen, Inc. (Norcross, GA)</t>
+          <t>Tri-Union Seafoods</t>
         </is>
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>Suzanna's Kitchen</t>
+          <t>Genova</t>
         </is>
       </c>
       <c r="E595" s="2" t="inlineStr">
         <is>
-          <t>Ready-to-eat grilled chicken breast fillet products, ~13,720 lbs (EST P-1382)</t>
+          <t>Yellowfin Tuna in Olive Oil 5 oz 4-pack + 5 oz can EVOO</t>
         </is>
       </c>
       <c r="F595" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Clostridium botulinum</t>
         </is>
       </c>
       <c r="G595" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Botulism risk — defective easy-open pull tabs</t>
         </is>
       </c>
       <c r="H595" s="2" t="inlineStr">
@@ -37824,59 +37824,59 @@
       </c>
       <c r="M595" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsis.usda.gov/recalls-alerts/suzannas-kitchen-recalls-ready-eat-grilled-chicken-breast-fillet-products-due</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/tri-union-seafoods-identifies-additional-quantities-recalled-genovar-tuna-limited-retailers-due</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B596" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>SFA (SG)</t>
         </is>
       </c>
       <c r="C596" s="2" t="inlineStr">
         <is>
-          <t>O.P.A.DISTRIBUTION OPA DISTRIBUTION</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>AREV</t>
+          <t>Nestle NAN HA1 SupremePro</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
         <is>
-          <t>Dried Lerida figs, calibre 8, 500 g tray</t>
+          <t>800 g infant formula, batch 52340017C3, expiry 2027-08-31, country of origin Switzerland</t>
         </is>
       </c>
       <c r="F596" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins / tenuazonic acid (mycotoxins)</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>Maximum limits exceeded for mycotoxins: aflatoxin B1, total aflatoxins, and tenuazonic acid</t>
+          <t>Presence of cereulide toxin</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I596" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J596" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia-Pacific</t>
         </is>
       </c>
       <c r="K596" s="2" t="n">
@@ -37887,39 +37887,39 @@
       </c>
       <c r="M596" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/20978/Interne</t>
+          <t>https://www.sfa.gov.sg/news-publications/newsroom/direction-to-recall-additional-infant-formula-products-due-to-presence-of-cereulide-toxin</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B597" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>USDA FSIS</t>
         </is>
       </c>
       <c r="C597" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>Suzanna's Kitchen, Inc. (Norcross, GA)</t>
         </is>
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>Suzanna's Kitchen</t>
         </is>
       </c>
       <c r="E597" s="2" t="inlineStr">
         <is>
-          <t>Date-sweetened chocolate bars (8 flavors — expanded recall)</t>
+          <t>Ready-to-eat grilled chicken breast fillet products, ~13,720 lbs (EST P-1382)</t>
         </is>
       </c>
       <c r="F597" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G597" s="2" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="H597" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I597" s="2" t="inlineStr">
@@ -37950,59 +37950,59 @@
       </c>
       <c r="M597" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-expands-voluntary-recall-select-chocolate-bars-due-possible-salmonella-contamination</t>
+          <t>https://www.fsis.usda.gov/recalls-alerts/suzannas-kitchen-recalls-ready-eat-grilled-chicken-breast-fillet-products-due</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B598" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C598" s="2" t="inlineStr">
         <is>
-          <t>The Ambriola Company</t>
+          <t>O.P.A.DISTRIBUTION OPA DISTRIBUTION</t>
         </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>Ambriola / Locatelli / Member's Mark / Pinna / Boar's Head</t>
+          <t>AREV</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
         <is>
-          <t>11,530 cheese products: Pecorino Romano (multi-brand)</t>
+          <t>Dried Lerida figs, calibre 8, 500 g tray</t>
         </is>
       </c>
       <c r="F598" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Aflatoxins / tenuazonic acid (mycotoxins)</t>
         </is>
       </c>
       <c r="G598" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Maximum limits exceeded for mycotoxins: aflatoxin B1, total aflatoxins, and tenuazonic acid</t>
         </is>
       </c>
       <c r="H598" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I598" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J598" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K598" s="2" t="n">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="M598" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/ambriola-company-issues-recall-cheese-products-because-listeria-health-risk</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/20978/Interne</t>
         </is>
       </c>
     </row>
@@ -38025,47 +38025,47 @@
       </c>
       <c r="B599" s="2" t="inlineStr">
         <is>
-          <t>NCC (ZA)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C599" s="2" t="inlineStr">
         <is>
-          <t>Nestlé South Africa</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>NAN Special Pro HA</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="E599" s="2" t="inlineStr">
         <is>
-          <t>NAN Special Pro HA 0–12 infant formula (6 × 800 g)</t>
+          <t>Date-sweetened chocolate bars (8 flavors — expanded recall)</t>
         </is>
       </c>
       <c r="F599" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G599" s="2" t="inlineStr">
         <is>
-          <t>Cereulide detected in supplied ingredient</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H599" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I599" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J599" s="2" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K599" s="2" t="n">
@@ -38076,39 +38076,39 @@
       </c>
       <c r="M599" s="2" t="inlineStr">
         <is>
-          <t>https://thencc.org.za/product-recall-nan-special-pro-ha-infant-formula-800g/</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-expands-voluntary-recall-select-chocolate-bars-due-possible-salmonella-contamination</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B600" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C600" s="2" t="inlineStr">
         <is>
-          <t>Loblaws Companies Limited</t>
+          <t>The Ambriola Company</t>
         </is>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>no name</t>
+          <t>Ambriola / Locatelli / Member's Mark / Pinna / Boar's Head</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">
         <is>
-          <t>Beef Burgers (1.36 kg)</t>
+          <t>11,530 cheese products: Pecorino Romano (multi-brand)</t>
         </is>
       </c>
       <c r="F600" s="2" t="inlineStr">
         <is>
-          <t>E. coli O157:H7</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G600" s="2" t="inlineStr">
@@ -38118,12 +38118,12 @@
       </c>
       <c r="H600" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I600" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J600" s="2" t="inlineStr">
@@ -38139,59 +38139,59 @@
       </c>
       <c r="M600" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/no-name-brand-beef-burgers-recalled-due-e-coli-o157h7</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/ambriola-company-issues-recall-cheese-products-because-listeria-health-risk</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B601" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>NCC (ZA)</t>
         </is>
       </c>
       <c r="C601" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>Nestlé South Africa</t>
         </is>
       </c>
       <c r="D601" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>NAN Special Pro HA</t>
         </is>
       </c>
       <c r="E601" s="2" t="inlineStr">
         <is>
-          <t>Mint Leaf Date-sweetened Chocolate Bar (initial recall)</t>
+          <t>NAN Special Pro HA 0–12 infant formula (6 × 800 g)</t>
         </is>
       </c>
       <c r="F601" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G601" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Cereulide detected in supplied ingredient</t>
         </is>
       </c>
       <c r="H601" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I601" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="J601" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="K601" s="2" t="n">
@@ -38202,54 +38202,54 @@
       </c>
       <c r="M601" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-issues-voluntary-recall-mint-leaf-date-sweetened-chocolate-bar-due-possible</t>
+          <t>https://thencc.org.za/product-recall-nan-special-pro-ha-infant-formula-800g/</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B602" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C602" s="2" t="inlineStr">
         <is>
-          <t>Diva Fam Inc.</t>
+          <t>Loblaws Companies Limited</t>
         </is>
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>True Sea Moss</t>
+          <t>no name</t>
         </is>
       </c>
       <c r="E602" s="2" t="inlineStr">
         <is>
-          <t>Sea Moss Gel Superfood, 16 fl oz</t>
+          <t>Beef Burgers (1.36 kg)</t>
         </is>
       </c>
       <c r="F602" s="2" t="inlineStr">
         <is>
-          <t>Clostridium botulinum</t>
+          <t>E. coli O157:H7</t>
         </is>
       </c>
       <c r="G602" s="2" t="inlineStr">
         <is>
-          <t>Botulism risk — missing process authority</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H602" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I602" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J602" s="2" t="inlineStr">
@@ -38265,59 +38265,59 @@
       </c>
       <c r="M602" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/diva-fam-inc-announces-voluntary-recall-sea-moss-gel-superfood-products-due-possible-health-risk</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/no-name-brand-beef-burgers-recalled-due-e-coli-o157h7</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B603" s="2" t="inlineStr">
         <is>
-          <t>ANVISA (BR)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C603" s="2" t="inlineStr">
         <is>
-          <t>Nestlé Brasil Ltda</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="D603" s="2" t="inlineStr">
         <is>
-          <t>Nestogeno / Nan Supreme / Nanlac / Alfamino</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="E603" s="2" t="inlineStr">
         <is>
-          <t>Infant formulas — multiple lots, multiple brands</t>
+          <t>Mint Leaf Date-sweetened Chocolate Bar (initial recall)</t>
         </is>
       </c>
       <c r="F603" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G603" s="2" t="inlineStr">
         <is>
-          <t>Toxin contamination</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H603" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I603" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J603" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K603" s="2" t="n">
@@ -38328,14 +38328,14 @@
       </c>
       <c r="M603" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.br/anvisa/pt-br/assuntos/noticias-anvisa/2026/proibida-venda-de-formula-infantil-com-risco-de-contaminacao-por-toxina</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-issues-voluntary-recall-mint-leaf-date-sweetened-chocolate-bar-due-possible</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B604" s="2" t="inlineStr">
@@ -38345,27 +38345,27 @@
       </c>
       <c r="C604" s="2" t="inlineStr">
         <is>
-          <t>Primavera Nueva Inc.</t>
+          <t>Diva Fam Inc.</t>
         </is>
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>Primavera Nueva</t>
+          <t>True Sea Moss</t>
         </is>
       </c>
       <c r="E604" s="2" t="inlineStr">
         <is>
-          <t>4-count tamales</t>
+          <t>Sea Moss Gel Superfood, 16 fl oz</t>
         </is>
       </c>
       <c r="F604" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Clostridium botulinum</t>
         </is>
       </c>
       <c r="G604" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Botulism risk — missing process authority</t>
         </is>
       </c>
       <c r="H604" s="2" t="inlineStr">
@@ -38391,7 +38391,7 @@
       </c>
       <c r="M604" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/primavera-nueva-inc-issues-voluntary-recall-select-4-count-tamales-because-possible-health-risk-0</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/diva-fam-inc-announces-voluntary-recall-sea-moss-gel-superfood-products-due-possible-health-risk</t>
         </is>
       </c>
     </row>
@@ -38403,22 +38403,22 @@
       </c>
       <c r="B605" s="2" t="inlineStr">
         <is>
-          <t>ANMAT (AR)</t>
+          <t>ANVISA (BR)</t>
         </is>
       </c>
       <c r="C605" s="2" t="inlineStr">
         <is>
-          <t>Nestlé Argentina S.A.</t>
+          <t>Nestlé Brasil Ltda</t>
         </is>
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>Nestlé infant formulas</t>
+          <t>Nestogeno / Nan Supreme / Nanlac / Alfamino</t>
         </is>
       </c>
       <c r="E605" s="2" t="inlineStr">
         <is>
-          <t>Multiple lots of infant formula milk</t>
+          <t>Infant formulas — multiple lots, multiple brands</t>
         </is>
       </c>
       <c r="F605" s="2" t="inlineStr">
@@ -38428,17 +38428,17 @@
       </c>
       <c r="G605" s="2" t="inlineStr">
         <is>
-          <t>Possible cereulide presence in raw material — voluntary preventive withdrawal</t>
+          <t>Toxin contamination</t>
         </is>
       </c>
       <c r="H605" s="2" t="inlineStr">
         <is>
-          <t>Preventive withdrawal</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I605" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J605" s="2" t="inlineStr">
@@ -38454,59 +38454,59 @@
       </c>
       <c r="M605" s="2" t="inlineStr">
         <is>
-          <t>https://chequeado.com/el-explicador/la-anmat-ordeno-el-retiro-preventivo-de-leches-de-formula-para-bebes-cuales-son-los-lotes-afectados/</t>
+          <t>https://www.gov.br/anvisa/pt-br/assuntos/noticias-anvisa/2026/proibida-venda-de-formula-infantil-com-risco-de-contaminacao-por-toxina</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B606" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C606" s="2" t="inlineStr">
         <is>
-          <t>— (infant formula manufacturer)</t>
+          <t>Primavera Nueva Inc.</t>
         </is>
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Primavera Nueva</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
         <is>
-          <t>Powdered infant and young children formula (certain batches)</t>
+          <t>4-count tamales</t>
         </is>
       </c>
       <c r="F606" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G606" s="2" t="inlineStr">
         <is>
-          <t>Powdered infant formula recall</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H606" s="2" t="inlineStr">
         <is>
-          <t>Food Alert</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I606" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J606" s="2" t="inlineStr">
         <is>
-          <t>Asia-Pacific</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K606" s="2" t="n">
@@ -38517,34 +38517,34 @@
       </c>
       <c r="M606" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/whatsnew/whatsnew_fa/2026_610.html</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/primavera-nueva-inc-issues-voluntary-recall-select-4-count-tamales-because-possible-health-risk-0</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B607" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>ANMAT (AR)</t>
         </is>
       </c>
       <c r="C607" s="2" t="inlineStr">
         <is>
-          <t>Nestlé / Danone</t>
+          <t>Nestlé Argentina S.A.</t>
         </is>
       </c>
       <c r="D607" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>Nestlé infant formulas</t>
         </is>
       </c>
       <c r="E607" s="2" t="inlineStr">
         <is>
-          <t>SMA Infant Formula and Follow-On Formula</t>
+          <t>Multiple lots of infant formula milk</t>
         </is>
       </c>
       <c r="F607" s="2" t="inlineStr">
@@ -38554,22 +38554,22 @@
       </c>
       <c r="G607" s="2" t="inlineStr">
         <is>
-          <t>Toxin contamination — heat-stable cereulide</t>
+          <t>Possible cereulide presence in raw material — voluntary preventive withdrawal</t>
         </is>
       </c>
       <c r="H607" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Preventive withdrawal</t>
         </is>
       </c>
       <c r="I607" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J607" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K607" s="2" t="n">
@@ -38580,24 +38580,24 @@
       </c>
       <c r="M607" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026</t>
+          <t>https://chequeado.com/el-explicador/la-anmat-ordeno-el-retiro-preventivo-de-leches-de-formula-para-bebes-cuales-son-los-lotes-afectados/</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B608" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>CFS (HK)</t>
         </is>
       </c>
       <c r="C608" s="2" t="inlineStr">
         <is>
-          <t>Origin: Romania | Notifying: Italy | Distributed: Italy</t>
+          <t>— (infant formula manufacturer)</t>
         </is>
       </c>
       <c r="D608" s="2" t="inlineStr">
@@ -38607,32 +38607,32 @@
       </c>
       <c r="E608" s="2" t="inlineStr">
         <is>
-          <t>Chicken breast (petto di pollo / chicken breast)</t>
+          <t>Powdered infant and young children formula (certain batches)</t>
         </is>
       </c>
       <c r="F608" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Enteritidis</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G608" s="2" t="inlineStr">
         <is>
-          <t>Salmonella enteritidis detected in chicken breast of Romanian origin distributed in Italy</t>
+          <t>Powdered infant formula recall</t>
         </is>
       </c>
       <c r="H608" s="2" t="inlineStr">
         <is>
-          <t>Information notification for attention</t>
+          <t>Food Alert</t>
         </is>
       </c>
       <c r="I608" s="2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J608" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia-Pacific</t>
         </is>
       </c>
       <c r="K608" s="2" t="n">
@@ -38643,7 +38643,7 @@
       </c>
       <c r="M608" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/814607</t>
+          <t>https://www.cfs.gov.hk/english/whatsnew/whatsnew_fa/2026_610.html</t>
         </is>
       </c>
     </row>
@@ -38655,42 +38655,42 @@
       </c>
       <c r="B609" s="2" t="inlineStr">
         <is>
-          <t>NVWA</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C609" s="2" t="inlineStr">
         <is>
-          <t>Nestlé; Danone</t>
+          <t>Nestlé / Danone</t>
         </is>
       </c>
       <c r="D609" s="2" t="inlineStr">
         <is>
-          <t>Nutrilon</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="E609" s="2" t="inlineStr">
         <is>
-          <t>Infant formula (melkpoeder / zuigelingenvoeding)</t>
+          <t>SMA Infant Formula and Follow-On Formula</t>
         </is>
       </c>
       <c r="F609" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin)</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G609" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Toxin contamination — heat-stable cereulide</t>
         </is>
       </c>
       <c r="H609" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I609" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J609" s="2" t="inlineStr">
@@ -38706,59 +38706,59 @@
       </c>
       <c r="M609" s="2" t="inlineStr">
         <is>
-          <t>https://www.nvwa.nl/actueel/actuele-onderwerpen/5-vragen-over-cereulide-in-zuigelingenvoeding</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B610" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C610" s="2" t="inlineStr">
         <is>
-          <t>Si Ji Mei</t>
+          <t>Origin: Romania | Notifying: Italy | Distributed: Italy</t>
         </is>
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>Si Ji Mei</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E610" s="2" t="inlineStr">
         <is>
-          <t>Wuhan Egg Sheets with Glutinous Rice</t>
+          <t>Chicken breast (petto di pollo / chicken breast)</t>
         </is>
       </c>
       <c r="F610" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Salmonella Enteritidis</t>
         </is>
       </c>
       <c r="G610" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Salmonella enteritidis detected in chicken breast of Romanian origin distributed in Italy</t>
         </is>
       </c>
       <c r="H610" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Information notification for attention</t>
         </is>
       </c>
       <c r="I610" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="J610" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K610" s="2" t="n">
@@ -38769,68 +38769,194 @@
       </c>
       <c r="M610" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/si-ji-mei-brand-wuhan-egg-sheets-glutinous-rice-recalled-due-salmonella</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/814607</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
         <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>NVWA</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>Nestlé; Danone</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>Nutrilon</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>Infant formula (melkpoeder / zuigelingenvoeding)</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>Cereulide (B. cereus toxin)</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>Cereulide</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="I611" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K611" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L611" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nvwa.nl/actueel/actuele-onderwerpen/5-vragen-over-cereulide-in-zuigelingenvoeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>CFIA</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>Si Ji Mei</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>Si Ji Mei</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>Wuhan Egg Sheets with Glutinous Rice</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>Salmonella</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>Pathogen contamination</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>Class 2</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="K612" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L612" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M612" s="2" t="inlineStr">
+        <is>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/si-ji-mei-brand-wuhan-egg-sheets-glutinous-rice-recalled-due-salmonella</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
           <t>2026-01-02</t>
         </is>
       </c>
-      <c r="B611" s="2" t="inlineStr">
+      <c r="B613" s="2" t="inlineStr">
         <is>
           <t>RASFF (EU)</t>
         </is>
       </c>
-      <c r="C611" s="2" t="inlineStr">
+      <c r="C613" s="2" t="inlineStr">
         <is>
           <t>Origin: United Kingdom | Notifying: France | Distributed: Spain</t>
         </is>
       </c>
-      <c r="D611" s="2" t="inlineStr">
+      <c r="D613" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E611" s="2" t="inlineStr">
+      <c r="E613" s="2" t="inlineStr">
         <is>
           <t>Scallops</t>
         </is>
       </c>
-      <c r="F611" s="2" t="inlineStr">
+      <c r="F613" s="2" t="inlineStr">
         <is>
           <t>Lipophilic biotoxins (DSP)</t>
         </is>
       </c>
-      <c r="G611" s="2" t="inlineStr">
+      <c r="G613" s="2" t="inlineStr">
         <is>
           <t>Lipophilic toxins (DSP) detected in scallops of UK origin distributed in Spain — alert notification (border control - consignment released before detection)</t>
         </is>
       </c>
-      <c r="H611" s="2" t="inlineStr">
+      <c r="H613" s="2" t="inlineStr">
         <is>
           <t>Alert notification</t>
         </is>
       </c>
-      <c r="I611" s="2" t="inlineStr">
+      <c r="I613" s="2" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="J611" s="2" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="K611" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L611" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M611" s="2" t="inlineStr">
+      <c r="J613" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="K613" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L613" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M613" s="2" t="inlineStr">
         <is>
           <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/814459</t>
         </is>
@@ -38870,14 +38996,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-14 18:18 UTC</t>
+          <t>Generated: 2026-05-14 18:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Records: 610</t>
+          <t>Records: 612</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Escherichia coli STEC</t>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CHARCUTERIE PIERRE SCHMIDT Pierre Schmidt</t>
+          <t>Charcuterie Pierre Schmidt</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>RappelConso</t>
+          <t>Le Fromager des Halles Grand-Frais</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -39185,7 +39185,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-15 06:56 UTC</t>
+          <t>Generated: 2026-05-15 07:42 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -683,52 +683,52 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SARL Sarda</t>
+          <t>United Utensils Inc.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>SARL Sarda</t>
+          <t>Ghirardelli</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>White ham nuts or white ham heels (pork cuts)</t>
+          <t>Powdered beverage mixes — Premium Hot Cocoa Mix 907g (UPC 7 47599 62012 6, code S449250A04 BBD 063027); Perfectly Premium Frappé Mix Vanilla 1.36kg (UPC 7 47599 62105 5, code S594262 BBD 073127); Premium Frappé Mix Mocha 1.42kg (UPC 7 47599 66211 9, code S295262 BBD 063027); Premium Frappé Mix Frozen Hot Cocoa 1.42kg (UPC 7 47599 66213 3, code S393260 BBD 073127).</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Detection of Listeria monocytogenes</t>
+          <t>CFIA Food Recall Warning RA-82079 (CFIA ID 17375). United Utensils Inc. is recalling Ghirardelli brand powdered beverage mixes (four SKUs) due to possible Salmonella contamination. Recall triggered by a recall in another country (likely downstream of the California Dairies Inc. powdered milk Salmonella recall — non-fat dried milk powder is a typical ingredient in dairy-based powdered beverage mixes). Distribution: Online, Ontario, possibly other provinces and territories. No illnesses reported. CFIA food-safety investigation ongoing; further product recalls possible.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22265/Interne</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/ghirardelli-brand-powdered-beverage-mixes-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
@@ -756,17 +756,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AGRIBERIA SARL AGRIBERIA</t>
+          <t>SARL Sarda</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Ipanema</t>
+          <t>SARL Sarda</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ipanema cheese curds</t>
+          <t>White ham nuts or white ham heels (pork cuts)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes</t>
+          <t>Detection of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22249/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22265/Interne</t>
         </is>
       </c>
     </row>
@@ -819,27 +819,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PERODIS SA INTERMARCHE</t>
+          <t>AGRIBERIA SARL AGRIBERIA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Ipanema</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Marinated chicken kebab fillets</t>
+          <t>Ipanema cheese curds</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Presence of Salmonella</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22241/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22249/Interne</t>
         </is>
       </c>
     </row>
@@ -882,27 +882,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Dulci</t>
+          <t>PERODIS SA INTERMARCHE</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Dulci</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>pâte à tartiner dulci dubaï style 40 % pistache¤lot pt08</t>
+          <t>Marinated chicken kebab fillets</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Presence of Ochratoxin A above the regulatory threshold</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -921,14 +921,14 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22253/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22241/Interne</t>
         </is>
       </c>
     </row>
@@ -940,42 +940,42 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Origin: Spain | Notifying: France</t>
+          <t>Dulci</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>Dulci</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes in cheese</t>
+          <t>pâte à tartiner dulci dubaï style 40 % pistache¤lot pt08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes in cheese; risk: serious; category: milk and milk products</t>
+          <t>Presence of Ochratoxin A above the regulatory threshold</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -984,14 +984,14 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/844028</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22253/Interne</t>
         </is>
       </c>
     </row>
@@ -1003,42 +1003,42 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
+          <t>Origin: Spain | Notifying: France</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>fromage montagnard 450g</t>
+          <t>Presence of Listeria monocytogenes in cheese</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing E. coli (STEC)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>présence de escherichia coli stec</t>
+          <t>Presence of Listeria monocytogenes in cheese; risk: serious; category: milk and milk products</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22273/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/844028</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>fromage montagnard 450g</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22274/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22273/Interne</t>
         </is>
       </c>
     </row>
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Metro France</t>
+          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Metro Chef</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>oignon jaune epluche 2kg metro chef</t>
+          <t>reblochon de savoie fermier aop 450g</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>présence de listeria monocytogenes</t>
+          <t>présence de escherichia coli stec</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22264/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22274/Interne</t>
         </is>
       </c>
     </row>
@@ -1197,27 +1197,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
+          <t>Metro France</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Le farto de Thônes</t>
+          <t>Metro Chef</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Reblochon de Savoie fermier AOP 450g</t>
+          <t>oignon jaune epluche 2kg metro chef</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing E. coli (STEC)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>présence de escherichia coli stec</t>
+          <t>présence de listeria monocytogenes</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22275/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22264/Interne</t>
         </is>
       </c>
     </row>
@@ -1255,44 +1255,44 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Origin: Belgium | Notifying: France</t>
+          <t>Société Coopérative Agricole des Producteurs de Reblochons des Vallées de Thônes</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Le farto de Thônes</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Reblochon de Savoie fermier AOP 450g</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>présence de escherichia coli stec</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Voluntary</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Detection of Listeria monocytogenes in smoked salmon trimmings</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Listeria monocytogenes</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Detection of Listeria monocytogenes in smoked salmon trimmings; risk: serious; category: fish and fish products</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/844095</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22275/Interne</t>
         </is>
       </c>
     </row>
@@ -1323,39 +1323,39 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Origin: Netherlands | Notifying: Belgium</t>
+          <t>Origin: Belgium | Notifying: France</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Detection of Listeria monocytogenes in smoked salmon trimmings</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Listeria monocytogenes</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Detection of Listeria monocytogenes in smoked salmon trimmings; risk: serious; category: fish and fish products</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Listeria monocytogenes in cold-smoked salmon from the Netherlands</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Listeria monocytogenes</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Listeria monocytogenes in cold-smoked salmon from the Netherlands; risk: serious; category: fish and fish products</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -1369,34 +1369,34 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/843926</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/844095</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Charcuterie Pierre Schmidt</t>
+          <t>Origin: Netherlands | Notifying: Belgium</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Les Créations de Pierre</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>poitrine fumée 350g pierre schmidt</t>
+          <t>Listeria monocytogenes in cold-smoked salmon from the Netherlands</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Microbiological testing detected the presence of Listeria monocytogenes</t>
+          <t>Listeria monocytogenes in cold-smoked salmon from the Netherlands; risk: serious; category: fish and fish products</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22238/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/843926</t>
         </is>
       </c>
     </row>
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>METRO FRANCE</t>
+          <t>Charcuterie Pierre Schmidt</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Aro</t>
+          <t>Les Créations de Pierre</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>saumon fume atlantique pre tranche 600g / 900g aro</t>
+          <t>poitrine fumée 350g pierre schmidt</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes</t>
+          <t>Microbiological testing detected the presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22252/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22238/Interne</t>
         </is>
       </c>
     </row>
@@ -1507,42 +1507,42 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FSAI (IE)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Lidl</t>
+          <t>METRO FRANCE</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Lidl</t>
+          <t>Aro</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Free Range 100% Irish Chicken Breast Fillets and 100% Irish Diced Chicken Breast Fillets (FSAI Alert 2026.21, IE 803 EC)</t>
+          <t>saumon fume atlantique pre tranche 600g / 900g aro</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Presence of Salmonella in Lidl-branded chicken breast fillet products</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>volontaire (sans arrêté préfectoral)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-a-batch-of-free-range-100-irish-chicken</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22252/Interne</t>
         </is>
       </c>
     </row>
@@ -1575,17 +1575,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Western Brand</t>
+          <t>Lidl</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Lidl, Inishella</t>
+          <t>Lidl</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Various Western Brand chicken products (Lidl and Inishella brands)</t>
+          <t>Free Range 100% Irish Chicken Breast Fillets and 100% Irish Diced Chicken Breast Fillets (FSAI Alert 2026.21, IE 803 EC)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Presence of Salmonella in chicken products</t>
+          <t>Presence of Salmonella in Lidl-branded chicken breast fillet products</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-various-western-brand-chicken-products</t>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-a-batch-of-free-range-100-irish-chicken</t>
         </is>
       </c>
     </row>
@@ -1633,42 +1633,42 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AESAN</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Western Brand</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lidl, Inishella</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Raw goat's milk cheese</t>
+          <t>Various Western Brand chicken products (Lidl and Inishella brands)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Presence of Salmonella in chicken products</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>https://www.aesan.gob.es/AECOSAN/web/seguridad_alimentaria/alertas_alimentarias/2026_38.htm</t>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-various-western-brand-chicken-products</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FSAI</t>
+          <t>AESAN</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Manor Farm</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Manor Farm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>various Manor Farm chicken products (multiple retailers: Aldi, Dunnes Stores, Lidl, Centra, SuperValu, Tesco)</t>
+          <t>Raw goat's milk cheese</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-various-manor-farm-chicken-products</t>
+          <t>https://www.aesan.gob.es/AECOSAN/web/seguridad_alimentaria/alertas_alimentarias/2026_38.htm</t>
         </is>
       </c>
     </row>
@@ -39185,7 +39185,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-15 07:42 UTC</t>
+          <t>Generated: 2026-05-15 09:47 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -40886,7 +40886,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-19 19:13 UTC</t>
+          <t>Generated: 2026-05-19 19:25 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -50828,7 +50828,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 06:41 UTC</t>
+          <t>Generated: 2026-06-05 07:03 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>conserves pâté de foie pur porc¤120g / 200g / 280g / 1580g</t>
+          <t>conserves pâté de foie pur porc; 120g / 200g / 280g / 1580g</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>conserves jambonneau¤280g</t>
+          <t>conserves jambonneau; 280g</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>conserves dindonneau¤280g</t>
+          <t>conserves dindonneau; 280g</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>conserves pâté de foie de volaille¤120g / 200g / 280g / 1580g</t>
+          <t>conserves pâté de foie de volaille; 120g / 200g / 280g / 1580g</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>spaghetti carbonara emballé le 19/05/2026¤panzerotti aux cèpes et champignons emballé le 19/05/26¤croissant (jambon, fromage, champignons) emballé le 20/05/2026</t>
+          <t>spaghetti carbonara emballé le 19/05/2026; panzerotti aux cèpes et champignons emballé le 19/05/26; croissant (jambon, fromage, champignons) emballé le 20/05/2026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Foreign material (plastic)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>The presence of foreign matter (plastic).</t>
+          <t>Voluntary recall (FSANZ Recall Alert, published 2 June 2026). Presence of foreign matter (plastic). Food products containing plastic may cause illness or injury if consumed. Nationally distributed via Coles, Woolworths, independent retailers (incl. IGA), convenience &amp; petrol retailers. Date Marking 30/JUN/2027; Batch Numbers 6072T941, 6073T941, 6074T941, 6075T941, 6085T941, 6086T941, 6088T941.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>beurre de ferme doux 250 g¤beurre de ferme demi-sel 250 g</t>
+          <t>beurre de ferme doux 250 g; beurre de ferme demi-sel 250 g</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>aromatises ail et fines herbes¤echalote¤bruschetta</t>
+          <t>aromatises ail et fines herbes; echalote; bruschetta</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>préparation viande hachée x2¤préparation viande hachée vrac</t>
+          <t>préparation viande hachée x2; préparation viande hachée vrac</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2tartares 180g 5%mg sec.¤2tartares 150g 5%mg¤viande hachee 2kg 5%mg¤2tartare 180g  5%mg</t>
+          <t>2tartares 180g 5%mg sec.; 2tartares 150g 5%mg; viande hachee 2kg 5%mg; 2tartare 180g  5%mg</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>tarama 100g¤tarama 250g</t>
+          <t>tarama 100g; tarama 250g</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>lot g22014¤code barre 6936489101348</t>
+          <t>lot g22014; code barre 6936489101348</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>barf complete cat - 100 g ¤barf complete - 250 g ¤barf complete 1 kg ¤barf complete 500 g</t>
+          <t>barf complete cat - 100 g ; barf complete - 250 g ; barf complete 1 kg ; barf complete 500 g</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>pâte à tartiner dulci dubaï style 40 % pistache¤lot pt08</t>
+          <t>pâte à tartiner dulci dubaï style 40 % pistache; lot pt08</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -50828,7 +50828,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-05 07:03 UTC</t>
+          <t>Generated: 2026-06-05 07:49 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -54559,7 +54559,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-12 03:21 UTC</t>
+          <t>Generated: 2026-06-12 03:27 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FSAI</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FSAI</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FSA</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>FAVV</t>
+          <t>FAVV (BE)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>FAVV</t>
+          <t>FAVV (BE)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>FSA</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>BVL</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
@@ -18741,7 +18741,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr">
@@ -23655,7 +23655,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -23718,7 +23718,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
@@ -24222,7 +24222,7 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
@@ -24250,7 +24250,7 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>NVWA</t>
+          <t>NVWA (NL)</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr">
@@ -25356,7 +25356,7 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -29136,7 +29136,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
@@ -29199,7 +29199,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr">
@@ -29262,7 +29262,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr">
@@ -30018,7 +30018,7 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr">
@@ -32097,7 +32097,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -33735,7 +33735,7 @@
       </c>
       <c r="I528" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J528" s="2" t="inlineStr">
@@ -34617,7 +34617,7 @@
       </c>
       <c r="I542" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J542" s="2" t="inlineStr">
@@ -34680,7 +34680,7 @@
       </c>
       <c r="I543" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J543" s="2" t="inlineStr">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="I566" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J566" s="2" t="inlineStr">
@@ -37606,42 +37606,42 @@
       </c>
       <c r="B590" s="2" t="inlineStr">
         <is>
-          <t>FSAI (IE)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C590" s="2" t="inlineStr">
         <is>
-          <t>Good4U</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>Good4U</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
         <is>
-          <t>Super Sprouts Super Greens, 60 g (use-by 2026-04-22, 2026-04-26, 2026-04-29, 2026-04-30, 2026-05-03)</t>
+          <t>Ochratoxin A in dried figs from Türkiye</t>
         </is>
       </c>
       <c r="F590" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Bovismorbificans</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Bovismorbificans — multi-country outbreak (UK + Ireland + Finland: 48 confirmed cases, 5+ hospitalised; +10 cases in 4 other countries)</t>
+          <t>Ochratoxin A in dried figs from Türkiye; risk: potentially serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I590" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J590" s="2" t="inlineStr">
@@ -37650,14 +37650,14 @@
         </is>
       </c>
       <c r="K590" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L590" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M590" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-batches-of-good4u-super-sprouts-super-gr</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839329</t>
         </is>
       </c>
     </row>
@@ -37669,7 +37669,7 @@
       </c>
       <c r="B591" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C591" s="2" t="inlineStr">
@@ -37684,7 +37684,7 @@
       </c>
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>Super Sprouts Super Greens — specific batches</t>
+          <t>Super Sprouts Super Greens, 60 g (use-by 2026-04-22, 2026-04-26, 2026-04-29, 2026-04-30, 2026-05-03)</t>
         </is>
       </c>
       <c r="F591" s="2" t="inlineStr">
@@ -37704,7 +37704,7 @@
       </c>
       <c r="I591" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J591" s="2" t="inlineStr">
@@ -37720,7 +37720,7 @@
       </c>
       <c r="M591" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-20-2026</t>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-batches-of-good4u-super-sprouts-super-gr</t>
         </is>
       </c>
     </row>
@@ -37732,42 +37732,42 @@
       </c>
       <c r="B592" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C592" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Good4U</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Good4U</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Türkiye</t>
+          <t>Super Sprouts Super Greens — specific batches</t>
         </is>
       </c>
       <c r="F592" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Salmonella Bovismorbificans</t>
         </is>
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Türkiye; risk: potentially serious; category: fruits and vegetables</t>
+          <t>Salmonella Bovismorbificans — multi-country outbreak (UK + Ireland + Finland: 48 confirmed cases, 5+ hospitalised; +10 cases in 4 other countries)</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I592" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J592" s="2" t="inlineStr">
@@ -37776,14 +37776,14 @@
         </is>
       </c>
       <c r="K592" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L592" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M592" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839329</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-20-2026</t>
         </is>
       </c>
     </row>
@@ -38586,7 +38586,7 @@
       </c>
       <c r="I605" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J605" s="2" t="inlineStr">
@@ -39216,7 +39216,7 @@
       </c>
       <c r="I615" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J615" s="2" t="inlineStr">
@@ -39279,7 +39279,7 @@
       </c>
       <c r="I616" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J616" s="2" t="inlineStr">
@@ -39342,7 +39342,7 @@
       </c>
       <c r="I617" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J617" s="2" t="inlineStr">
@@ -39783,7 +39783,7 @@
       </c>
       <c r="I624" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J624" s="2" t="inlineStr">
@@ -40098,7 +40098,7 @@
       </c>
       <c r="I629" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="J629" s="2" t="inlineStr">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="I633" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J633" s="2" t="inlineStr">
@@ -42016,58 +42016,58 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>MPI (NZ)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>Southern Alp Sprouts</t>
+          <t>Origin: Brazil | Notifying: Netherlands</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>Southern Alp Sprouts</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E660" s="2" t="inlineStr">
         <is>
-          <t>Alfalfa &amp; Onion Sprouts (Southern Alp Sprouts) and Onion Sprouts Combo 120 g (Pams) — Batch J197 best-before 2026-04-21, J197 best-before 2026-04-23, J199 best-before 2026-04-23</t>
+          <t>Salmonella spp in poultry meat preparation from Brazil</t>
         </is>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G660" s="2" t="inlineStr">
         <is>
-          <t>Possible presence of Listeria monocytogenes</t>
+          <t>Salmonella spp in poultry meat preparation from Brazil; risk: serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H660" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I660" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J660" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K660" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L660" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M660" s="2" t="inlineStr">
         <is>
-          <t>https://www.mpi.govt.nz/news/media-releases/sprout-products-recalled-due-to-the-possible-presence-of-listeria</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837896</t>
         </is>
       </c>
     </row>
@@ -42079,22 +42079,22 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>MPI (NZ)</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>Origin: United Kingdom | Notifying: France</t>
+          <t>Southern Alp Sprouts</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Southern Alp Sprouts</t>
         </is>
       </c>
       <c r="E661" s="2" t="inlineStr">
         <is>
-          <t>Turkey Breast Pastrami in which Listeria monocytogenes has been detected</t>
+          <t>Alfalfa &amp; Onion Sprouts (Southern Alp Sprouts) and Onion Sprouts Combo 120 g (Pams) — Batch J197 best-before 2026-04-21, J197 best-before 2026-04-23, J199 best-before 2026-04-23</t>
         </is>
       </c>
       <c r="F661" s="2" t="inlineStr">
@@ -42104,22 +42104,22 @@
       </c>
       <c r="G661" s="2" t="inlineStr">
         <is>
-          <t>Turkey Breast Pastrami in which Listeria monocytogenes has been detected; risk: serious; category: poultry meat and poultry meat products</t>
+          <t>Possible presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H661" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I661" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="J661" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K661" s="2" t="n">
@@ -42130,7 +42130,7 @@
       </c>
       <c r="M661" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837996</t>
+          <t>https://www.mpi.govt.nz/news/media-releases/sprout-products-recalled-due-to-the-possible-presence-of-listeria</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>Origin: United States | Notifying: Germany</t>
+          <t>Origin: United Kingdom | Notifying: France</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
@@ -42157,43 +42157,43 @@
       </c>
       <c r="E662" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in peanuts from the United States</t>
+          <t>Turkey Breast Pastrami in which Listeria monocytogenes has been detected</t>
         </is>
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G662" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in peanuts from the United States; risk: serious; category: nuts, nut products and seeds</t>
+          <t>Turkey Breast Pastrami in which Listeria monocytogenes has been detected; risk: serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H662" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I662" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J662" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K662" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L662" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M662" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837942</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837996</t>
         </is>
       </c>
     </row>
@@ -42210,7 +42210,7 @@
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: United States | Notifying: Germany</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
@@ -42220,17 +42220,17 @@
       </c>
       <c r="E663" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Turkey</t>
+          <t>Aflatoxins in peanuts from the United States</t>
         </is>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G663" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Turkey; risk: potential risk; category: fruits and vegetables</t>
+          <t>Aflatoxins in peanuts from the United States; risk: serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H663" s="2" t="inlineStr">
@@ -42240,12 +42240,12 @@
       </c>
       <c r="I663" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J663" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K663" s="2" t="n">
@@ -42256,7 +42256,7 @@
       </c>
       <c r="M663" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837932</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837942</t>
         </is>
       </c>
     </row>
@@ -42273,7 +42273,7 @@
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>Origin: Poland | Notifying: Czechia</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -42283,27 +42283,27 @@
       </c>
       <c r="E664" s="2" t="inlineStr">
         <is>
-          <t>Salmonella enterica spp. enterica in chicken breast fillets from Poland</t>
+          <t>Ochratoxin A in dried figs from Turkey</t>
         </is>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G664" s="2" t="inlineStr">
         <is>
-          <t>Salmonella enterica spp. enterica in chicken breast fillets from Poland; risk: not serious; category: poultry meat and poultry meat products</t>
+          <t>Ochratoxin A in dried figs from Turkey; risk: potential risk; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H664" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I664" s="2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J664" s="2" t="inlineStr">
@@ -42319,7 +42319,7 @@
       </c>
       <c r="M664" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837926</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837932</t>
         </is>
       </c>
     </row>
@@ -42336,7 +42336,7 @@
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>Origin: Brazil | Notifying: Netherlands</t>
+          <t>Origin: Poland | Notifying: Czechia</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -42346,7 +42346,7 @@
       </c>
       <c r="E665" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp in poultry meat preparation from Brazil</t>
+          <t>Salmonella enterica spp. enterica in chicken breast fillets from Poland</t>
         </is>
       </c>
       <c r="F665" s="2" t="inlineStr">
@@ -42356,22 +42356,22 @@
       </c>
       <c r="G665" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp in poultry meat preparation from Brazil; risk: serious; category: poultry meat and poultry meat products</t>
+          <t>Salmonella enterica spp. enterica in chicken breast fillets from Poland; risk: not serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H665" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I665" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="J665" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K665" s="2" t="n">
@@ -42382,7 +42382,7 @@
       </c>
       <c r="M665" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837896</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837926</t>
         </is>
       </c>
     </row>
@@ -43213,47 +43213,47 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>Carnis Vertriebs GmbH</t>
+          <t>Origin: Brazil | Notifying: Netherlands</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>K Classic</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E679" s="2" t="inlineStr">
         <is>
-          <t>K Classic Delikatess Salami 1A fettreduziert, 100 g pack (best-before 2026-04-17, 2026-04-24, 2026-05-01)</t>
+          <t>Salmonella spp in poultry meat preparation from Brazil</t>
         </is>
       </c>
       <c r="F679" s="2" t="inlineStr">
         <is>
-          <t>E. coli</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G679" s="2" t="inlineStr">
         <is>
-          <t>Positive E. coli test result during routine inspection</t>
+          <t>Salmonella spp in poultry meat preparation from Brazil; risk: serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H679" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I679" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J679" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K679" s="2" t="n">
@@ -43264,7 +43264,7 @@
       </c>
       <c r="M679" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260416_17_BW_Salami_1A/260416_17_BW_Salami_1A_Meldung.html</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837740</t>
         </is>
       </c>
     </row>
@@ -43276,47 +43276,47 @@
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>Origin: Brazil | Notifying: Netherlands</t>
+          <t>Carnis Vertriebs GmbH</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>K Classic</t>
         </is>
       </c>
       <c r="E680" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp in poultry meat preparation from Brazil</t>
+          <t>K Classic Delikatess Salami 1A fettreduziert, 100 g pack (best-before 2026-04-17, 2026-04-24, 2026-05-01)</t>
         </is>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>E. coli</t>
         </is>
       </c>
       <c r="G680" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp in poultry meat preparation from Brazil; risk: serious; category: poultry meat and poultry meat products</t>
+          <t>Positive E. coli test result during routine inspection</t>
         </is>
       </c>
       <c r="H680" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I680" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J680" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K680" s="2" t="n">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="M680" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837740</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260416_17_BW_Salami_1A/260416_17_BW_Salami_1A_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -43563,7 +43563,7 @@
       </c>
       <c r="I684" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J684" s="2" t="inlineStr">
@@ -46615,42 +46615,42 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>FSAI (IE)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>Pettitt's</t>
+          <t>Origin: Spain | Notifying: Netherlands</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
         <is>
-          <t>Pettitt's</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E733" s="2" t="inlineStr">
         <is>
-          <t>Cook at Home Basil &amp; Pesto Chicken Fillets, 380 g pack (use-by 2026-03-30)</t>
+          <t>Aflatoxin in almonds from Spain</t>
         </is>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G733" s="2" t="inlineStr">
         <is>
-          <t>Salmonella contamination</t>
+          <t>Aflatoxin in almonds from Spain; risk: serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H733" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I733" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="J733" s="2" t="inlineStr">
@@ -46659,14 +46659,14 @@
         </is>
       </c>
       <c r="K733" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L733" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M733" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-a-batch-of-pettitt-s-basil-pesto-chicken</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835258</t>
         </is>
       </c>
     </row>
@@ -46678,42 +46678,42 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>The Curing Barn</t>
+          <t>Pettitt's</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
         <is>
-          <t>The Curing Barn</t>
+          <t>Pettitt's</t>
         </is>
       </c>
       <c r="E734" s="2" t="inlineStr">
         <is>
-          <t>British Bresaola</t>
+          <t>Cook at Home Basil &amp; Pesto Chicken Fillets, 380 g pack (use-by 2026-03-30)</t>
         </is>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G734" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Salmonella contamination</t>
         </is>
       </c>
       <c r="H734" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I734" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J734" s="2" t="inlineStr">
@@ -46729,7 +46729,7 @@
       </c>
       <c r="M734" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-15-2026</t>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-a-batch-of-pettitt-s-basil-pesto-chicken</t>
         </is>
       </c>
     </row>
@@ -46741,22 +46741,22 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>EFET (GR)</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>ΝΙΚΟΛΑΟΣ ΤΣΑΤΣΟΥΛΗΣ &amp; ΥΙΟΙ Ο.Ε.</t>
+          <t>The Curing Barn</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
         <is>
-          <t>ΦΕΤΑ ΒΥΤΙΝΑΣ Π.Ο.Π. ΒΑΡΕΛΙ</t>
+          <t>The Curing Barn</t>
         </is>
       </c>
       <c r="E735" s="2" t="inlineStr">
         <is>
-          <t>Feta PDO in barrel (batch ΦΕ-2751, produced 2026-01-24, use-by 2027-07-24)</t>
+          <t>British Bresaola</t>
         </is>
       </c>
       <c r="F735" s="2" t="inlineStr">
@@ -46766,17 +46766,17 @@
       </c>
       <c r="G735" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes — emergency EFET Attiki inspection following EODY notification of listeriosis cluster</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H735" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I735" s="2" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J735" s="2" t="inlineStr">
@@ -46788,11 +46788,11 @@
         <v>1</v>
       </c>
       <c r="L735" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M735" s="2" t="inlineStr">
         <is>
-          <t>https://www.efet.gr/index.php/el/enimerosi/deltia-typou/anakleiseis-cat/item/5379-deltio-typou-anaklisi-mi-asfaloys-proiontos-tyri-feta-logo-parousias-listeria</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-15-2026</t>
         </is>
       </c>
     </row>
@@ -46804,22 +46804,22 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>EFET (GR)</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>Origin: United Kingdom | Notifying: France</t>
+          <t>ΝΙΚΟΛΑΟΣ ΤΣΑΤΣΟΥΛΗΣ &amp; ΥΙΟΙ Ο.Ε.</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ΦΕΤΑ ΒΥΤΙΝΑΣ Π.Ο.Π. ΒΑΡΕΛΙ</t>
         </is>
       </c>
       <c r="E736" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes in grated cheese from the United Kingdom</t>
+          <t>Feta PDO in barrel (batch ΦΕ-2751, produced 2026-01-24, use-by 2027-07-24)</t>
         </is>
       </c>
       <c r="F736" s="2" t="inlineStr">
@@ -46829,17 +46829,17 @@
       </c>
       <c r="G736" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes in grated cheese from the United Kingdom; risk: serious; category: milk and milk products</t>
+          <t>Presence of Listeria monocytogenes — emergency EFET Attiki inspection following EODY notification of listeriosis cluster</t>
         </is>
       </c>
       <c r="H736" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I736" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="J736" s="2" t="inlineStr">
@@ -46851,11 +46851,11 @@
         <v>1</v>
       </c>
       <c r="L736" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M736" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836500</t>
+          <t>https://www.efet.gr/index.php/el/enimerosi/deltia-typou/anakleiseis-cat/item/5379-deltio-typou-anaklisi-mi-asfaloys-proiontos-tyri-feta-logo-parousias-listeria</t>
         </is>
       </c>
     </row>
@@ -46872,7 +46872,7 @@
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>Origin: Poland | Notifying: Czechia</t>
+          <t>Origin: United Kingdom | Notifying: France</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -46882,17 +46882,17 @@
       </c>
       <c r="E737" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Agona in chilled turkey breast fillet from Poland</t>
+          <t>Presence of Listeria monocytogenes in grated cheese from the United Kingdom</t>
         </is>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G737" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Agona in chilled turkey breast fillet from Poland; risk: serious; category: poultry meat and poultry meat products</t>
+          <t>Presence of Listeria monocytogenes in grated cheese from the United Kingdom; risk: serious; category: milk and milk products</t>
         </is>
       </c>
       <c r="H737" s="2" t="inlineStr">
@@ -46902,7 +46902,7 @@
       </c>
       <c r="I737" s="2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J737" s="2" t="inlineStr">
@@ -46911,14 +46911,14 @@
         </is>
       </c>
       <c r="K737" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L737" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M737" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836418</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836500</t>
         </is>
       </c>
     </row>
@@ -46935,7 +46935,7 @@
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Bulgaria</t>
+          <t>Origin: Poland | Notifying: Czechia</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -46945,27 +46945,27 @@
       </c>
       <c r="E738" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Türkiye</t>
+          <t>Salmonella Agona in chilled turkey breast fillet from Poland</t>
         </is>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G738" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
+          <t>Salmonella Agona in chilled turkey breast fillet from Poland; risk: serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H738" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I738" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="J738" s="2" t="inlineStr">
@@ -46981,7 +46981,7 @@
       </c>
       <c r="M738" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836380</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836418</t>
         </is>
       </c>
     </row>
@@ -47008,17 +47008,17 @@
       </c>
       <c r="E739" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Türkiye</t>
+          <t>Aflatoxins in dried figs from Türkiye</t>
         </is>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G739" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
+          <t>Aflatoxins in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H739" s="2" t="inlineStr">
@@ -47044,7 +47044,7 @@
       </c>
       <c r="M739" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836376</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836380</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>Origin: Spain | Notifying: Netherlands</t>
+          <t>Origin: Türkiye | Notifying: Bulgaria</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -47071,27 +47071,27 @@
       </c>
       <c r="E740" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin in almonds from Spain</t>
+          <t>Ochratoxin A in dried figs from Türkiye</t>
         </is>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G740" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin in almonds from Spain; risk: serious; category: nuts, nut products and seeds</t>
+          <t>Ochratoxin A in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H740" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I740" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J740" s="2" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="M740" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835258</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836376</t>
         </is>
       </c>
     </row>
@@ -48288,7 +48288,7 @@
       </c>
       <c r="I759" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J759" s="2" t="inlineStr">
@@ -50342,12 +50342,12 @@
       </c>
       <c r="D792" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio</t>
+          <t>Unknown (LUNA FOOD multi-brand recall)</t>
         </is>
       </c>
       <c r="E792" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Ready meal / sandwich (SKU not extractable)</t>
         </is>
       </c>
       <c r="F792" s="2" t="inlineStr">
@@ -50383,7 +50383,7 @@
       </c>
       <c r="M792" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21935/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21905/Interne</t>
         </is>
       </c>
     </row>
@@ -50405,12 +50405,12 @@
       </c>
       <c r="D793" s="2" t="inlineStr">
         <is>
-          <t>French Kitchen</t>
+          <t>Luisa e basilio</t>
         </is>
       </c>
       <c r="E793" s="2" t="inlineStr">
         <is>
-          <t>Sautéed Chicken, Thyme Potatoes, Mustard Sauce (GTIN 3760373401534)</t>
+          <t>Luisa e basilio ready meal</t>
         </is>
       </c>
       <c r="F793" s="2" t="inlineStr">
@@ -50446,7 +50446,7 @@
       </c>
       <c r="M793" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21933/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21935/Interne</t>
         </is>
       </c>
     </row>
@@ -50473,7 +50473,7 @@
       </c>
       <c r="E794" s="2" t="inlineStr">
         <is>
-          <t>French Kitchen ready meal</t>
+          <t>Sautéed Chicken, Thyme Potatoes, Mustard Sauce (GTIN 3760373401534)</t>
         </is>
       </c>
       <c r="F794" s="2" t="inlineStr">
@@ -50509,7 +50509,7 @@
       </c>
       <c r="M794" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21932/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21933/Interne</t>
         </is>
       </c>
     </row>
@@ -50531,12 +50531,12 @@
       </c>
       <c r="D795" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen</t>
+          <t>French Kitchen</t>
         </is>
       </c>
       <c r="E795" s="2" t="inlineStr">
         <is>
-          <t>Beef Fried Rice (GTIN 3760373402203)</t>
+          <t>French Kitchen ready meal</t>
         </is>
       </c>
       <c r="F795" s="2" t="inlineStr">
@@ -50572,7 +50572,7 @@
       </c>
       <c r="M795" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21931/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21932/Interne</t>
         </is>
       </c>
     </row>
@@ -50599,7 +50599,7 @@
       </c>
       <c r="E796" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen ready meal</t>
+          <t>Beef Fried Rice (GTIN 3760373402203)</t>
         </is>
       </c>
       <c r="F796" s="2" t="inlineStr">
@@ -50635,7 +50635,7 @@
       </c>
       <c r="M796" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21930/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21931/Interne</t>
         </is>
       </c>
     </row>
@@ -50698,7 +50698,7 @@
       </c>
       <c r="M797" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21929/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21930/Interne</t>
         </is>
       </c>
     </row>
@@ -50761,7 +50761,7 @@
       </c>
       <c r="M798" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21928/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21929/Interne</t>
         </is>
       </c>
     </row>
@@ -50783,12 +50783,12 @@
       </c>
       <c r="D799" s="2" t="inlineStr">
         <is>
-          <t>Bim bang</t>
+          <t>Chinese Kitchen</t>
         </is>
       </c>
       <c r="E799" s="2" t="inlineStr">
         <is>
-          <t>Caramel Pork with White Rice (GTIN 3760373400858)</t>
+          <t>Chinese Kitchen ready meal</t>
         </is>
       </c>
       <c r="F799" s="2" t="inlineStr">
@@ -50824,7 +50824,7 @@
       </c>
       <c r="M799" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21927/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21928/Interne</t>
         </is>
       </c>
     </row>
@@ -50851,7 +50851,7 @@
       </c>
       <c r="E800" s="2" t="inlineStr">
         <is>
-          <t>Bim bang Asian-style ready meal / kimbap</t>
+          <t>Caramel Pork with White Rice (GTIN 3760373400858)</t>
         </is>
       </c>
       <c r="F800" s="2" t="inlineStr">
@@ -50887,7 +50887,7 @@
       </c>
       <c r="M800" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21926/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21927/Interne</t>
         </is>
       </c>
     </row>
@@ -50950,7 +50950,7 @@
       </c>
       <c r="M801" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21925/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21926/Interne</t>
         </is>
       </c>
     </row>
@@ -51013,7 +51013,7 @@
       </c>
       <c r="M802" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21924/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21925/Interne</t>
         </is>
       </c>
     </row>
@@ -51035,12 +51035,12 @@
       </c>
       <c r="D803" s="2" t="inlineStr">
         <is>
-          <t>The bread Bandits</t>
+          <t>Bim bang</t>
         </is>
       </c>
       <c r="E803" s="2" t="inlineStr">
         <is>
-          <t>Salmon Yuzu Duo Baguette (GTIN 3760373403781)</t>
+          <t>Bim bang Asian-style ready meal / kimbap</t>
         </is>
       </c>
       <c r="F803" s="2" t="inlineStr">
@@ -51076,7 +51076,7 @@
       </c>
       <c r="M803" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21923/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21924/Interne</t>
         </is>
       </c>
     </row>
@@ -51103,7 +51103,7 @@
       </c>
       <c r="E804" s="2" t="inlineStr">
         <is>
-          <t>The bread Bandits sandwich/snack</t>
+          <t>Salmon Yuzu Duo Baguette (GTIN 3760373403781)</t>
         </is>
       </c>
       <c r="F804" s="2" t="inlineStr">
@@ -51139,7 +51139,7 @@
       </c>
       <c r="M804" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21922/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21923/Interne</t>
         </is>
       </c>
     </row>
@@ -51161,12 +51161,12 @@
       </c>
       <c r="D805" s="2" t="inlineStr">
         <is>
-          <t>Unknown (LUNA FOOD multi-brand recall)</t>
+          <t>The bread Bandits</t>
         </is>
       </c>
       <c r="E805" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>The bread Bandits sandwich/snack</t>
         </is>
       </c>
       <c r="F805" s="2" t="inlineStr">
@@ -51202,7 +51202,7 @@
       </c>
       <c r="M805" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21921/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21922/Interne</t>
         </is>
       </c>
     </row>
@@ -51265,7 +51265,7 @@
       </c>
       <c r="M806" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21920/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21921/Interne</t>
         </is>
       </c>
     </row>
@@ -51328,7 +51328,7 @@
       </c>
       <c r="M807" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21919/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21920/Interne</t>
         </is>
       </c>
     </row>
@@ -51391,7 +51391,7 @@
       </c>
       <c r="M808" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21918/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21919/Interne</t>
         </is>
       </c>
     </row>
@@ -51418,7 +51418,7 @@
       </c>
       <c r="E809" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (specific SKU not extractable from broken scraper data)</t>
+          <t>Ready meal / sandwich (SKU not extractable)</t>
         </is>
       </c>
       <c r="F809" s="2" t="inlineStr">
@@ -51454,7 +51454,7 @@
       </c>
       <c r="M809" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21917/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21918/Interne</t>
         </is>
       </c>
     </row>
@@ -51481,7 +51481,7 @@
       </c>
       <c r="E810" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (specific SKU not extractable from broken scraper data)</t>
         </is>
       </c>
       <c r="F810" s="2" t="inlineStr">
@@ -51517,7 +51517,7 @@
       </c>
       <c r="M810" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21916/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21917/Interne</t>
         </is>
       </c>
     </row>
@@ -51580,7 +51580,7 @@
       </c>
       <c r="M811" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21915/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21916/Interne</t>
         </is>
       </c>
     </row>
@@ -51643,7 +51643,7 @@
       </c>
       <c r="M812" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21914/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21915/Interne</t>
         </is>
       </c>
     </row>
@@ -51706,7 +51706,7 @@
       </c>
       <c r="M813" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21913/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21914/Interne</t>
         </is>
       </c>
     </row>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="M814" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21912/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21913/Interne</t>
         </is>
       </c>
     </row>
@@ -51832,7 +51832,7 @@
       </c>
       <c r="M815" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21911/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21912/Interne</t>
         </is>
       </c>
     </row>
@@ -51895,7 +51895,7 @@
       </c>
       <c r="M816" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21910/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21911/Interne</t>
         </is>
       </c>
     </row>
@@ -51958,7 +51958,7 @@
       </c>
       <c r="M817" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21909/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21910/Interne</t>
         </is>
       </c>
     </row>
@@ -52021,7 +52021,7 @@
       </c>
       <c r="M818" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21908/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21909/Interne</t>
         </is>
       </c>
     </row>
@@ -52084,7 +52084,7 @@
       </c>
       <c r="M819" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21907/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21908/Interne</t>
         </is>
       </c>
     </row>
@@ -52147,7 +52147,7 @@
       </c>
       <c r="M820" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21906/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21907/Interne</t>
         </is>
       </c>
     </row>
@@ -52210,7 +52210,7 @@
       </c>
       <c r="M821" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21905/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21906/Interne</t>
         </is>
       </c>
     </row>
@@ -54273,7 +54273,7 @@
       </c>
       <c r="I854" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J854" s="2" t="inlineStr">
@@ -54840,7 +54840,7 @@
       </c>
       <c r="I863" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J863" s="2" t="inlineStr">
@@ -58998,7 +58998,7 @@
       </c>
       <c r="I929" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J929" s="2" t="inlineStr">
@@ -59061,7 +59061,7 @@
       </c>
       <c r="I930" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J930" s="2" t="inlineStr">
@@ -59187,7 +59187,7 @@
       </c>
       <c r="I932" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J932" s="2" t="inlineStr">
@@ -59880,7 +59880,7 @@
       </c>
       <c r="I943" s="2" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="J943" s="2" t="inlineStr">
@@ -60384,7 +60384,7 @@
       </c>
       <c r="I951" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J951" s="2" t="inlineStr">
@@ -60447,7 +60447,7 @@
       </c>
       <c r="I952" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J952" s="2" t="inlineStr">
@@ -60825,7 +60825,7 @@
       </c>
       <c r="I958" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J958" s="2" t="inlineStr">
@@ -61077,7 +61077,7 @@
       </c>
       <c r="I962" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J962" s="2" t="inlineStr">
@@ -61329,7 +61329,7 @@
       </c>
       <c r="I966" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J966" s="2" t="inlineStr">
@@ -61392,7 +61392,7 @@
       </c>
       <c r="I967" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J967" s="2" t="inlineStr">
@@ -61707,7 +61707,7 @@
       </c>
       <c r="I972" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J972" s="2" t="inlineStr">
@@ -62148,7 +62148,7 @@
       </c>
       <c r="I979" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J979" s="2" t="inlineStr">
@@ -62176,7 +62176,7 @@
       </c>
       <c r="B980" s="2" t="inlineStr">
         <is>
-          <t>NVWA</t>
+          <t>NVWA (NL)</t>
         </is>
       </c>
       <c r="C980" s="2" t="inlineStr">
@@ -62463,7 +62463,7 @@
       </c>
       <c r="I984" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J984" s="2" t="inlineStr">
@@ -62778,7 +62778,7 @@
       </c>
       <c r="I989" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J989" s="2" t="inlineStr">
@@ -63093,7 +63093,7 @@
       </c>
       <c r="I994" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J994" s="2" t="inlineStr">
@@ -63219,7 +63219,7 @@
       </c>
       <c r="I996" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J996" s="2" t="inlineStr">
@@ -63345,7 +63345,7 @@
       </c>
       <c r="I998" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J998" s="2" t="inlineStr">
@@ -63471,7 +63471,7 @@
       </c>
       <c r="I1000" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1000" s="2" t="inlineStr">
@@ -63660,7 +63660,7 @@
       </c>
       <c r="I1003" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1003" s="2" t="inlineStr">
@@ -63723,7 +63723,7 @@
       </c>
       <c r="I1004" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1004" s="2" t="inlineStr">
@@ -63849,7 +63849,7 @@
       </c>
       <c r="I1006" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1006" s="2" t="inlineStr">
@@ -64129,7 +64129,7 @@
       </c>
       <c r="B1011" s="2" t="inlineStr">
         <is>
-          <t>NVWA</t>
+          <t>NVWA (NL)</t>
         </is>
       </c>
       <c r="C1011" s="2" t="inlineStr">
@@ -64344,7 +64344,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-01 07:29 UTC</t>
+          <t>Generated: 2026-07-01 07:53 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -877,42 +877,42 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Axel et Paul</t>
+          <t>O’Brien Fine Foods (Brady Family / Deluxe)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Axel et Paul</t>
+          <t>Brady Family; Deluxe (Lidl)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>lot n° 312</t>
+          <t>Sliced ham products sold in Northern Ireland (Brady Family Hand Crumbed Real Irish Ham 80g; Deluxe Honey Roast &amp; Triple Oak Smoked Carved Ham 130g) — best-before 16/07/2026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Zearalenone, T-2 toxin, HT-2 toxin</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>La teneur en zéaralénone et la somme de t-2 toxine et de ht-2 toxine</t>
+          <t>FSA UK recall (PRIN-32-2026): possible Listeria monocytogenes in O’Brien Fine Foods ham products sold in Northern Ireland. Separate UK notice; FSAI Ireland is the primary recall. Listeria always Tier 1.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -921,14 +921,14 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22705/Interne</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-32-2026</t>
         </is>
       </c>
     </row>
@@ -945,27 +945,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Fabriqué sur Place</t>
+          <t>Axel et Paul</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Fabriqué sur Place</t>
+          <t>Axel et Paul</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>croissant au jambon x2 pour le libre-service ou à l'unité pour le rayon traditionnel.</t>
+          <t>lot n° 312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Zearalenone, T-2 toxin, HT-2 toxin</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Mise en évidence de la présence de Listeria monocytogenes</t>
+          <t>La teneur en zéaralénone et la somme de t-2 toxine et de ht-2 toxine</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -984,14 +984,14 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22706/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22705/Interne</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>O’Brien Fine Foods (Brady Family / Tesco Finest / Deluxe)</t>
+          <t>Fabriqué sur Place</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Brady Family; Tesco Finest; Deluxe (Lidl)</t>
+          <t>Fabriqué sur Place</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Sliced/cooked ham products (Brady Family Wood Smoked &amp; Hand Crumbed Real Irish Ham; Deluxe Triple Oak &amp; Honey Roast Carved Ham) — best-before 16/07/2026</t>
+          <t>croissant au jambon x2 pour le libre-service ou à l'unité pour le rayon traditionnel.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>FSA/FSAI recall (PRIN-32-2026): possible Listeria monocytogenes in O’Brien Fine Foods ham products. Listeria always Tier 1.</t>
+          <t>Mise en évidence de la présence de Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-32-2026</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22706/Interne</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-specific-batches-of-various-cooked-ham-p</t>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-specific-batches-of-various-cooked-ham-products</t>
         </is>
       </c>
     </row>
@@ -37102,42 +37102,42 @@
       </c>
       <c r="B582" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C582" s="2" t="inlineStr">
         <is>
-          <t>Star Impex</t>
+          <t>ETABLISSEMENTS J. CHENE ET FILS Ets Chêne &amp; Fils</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>Casabor</t>
+          <t>Patifrais (fabriqué par Ets Chêne &amp; Fils)</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
         <is>
-          <t>Blue Swimming Crab Cut U/10 12x1, China origin (Casabor brand crab meat)</t>
+          <t>Beef-snout salad — 500 g modified-atmosphere tray (GTIN 3537949991436, Lot 163, use-by 2026-05-05 and 2026-05-07)</t>
         </is>
       </c>
       <c r="F582" s="2" t="inlineStr">
         <is>
-          <t>PFOA / PFAS</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G582" s="2" t="inlineStr">
         <is>
-          <t>PFOA (perfluorooctanoic acid) levels above the regulatory limit detected in lab tests</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H582" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I582" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J582" s="2" t="inlineStr">
@@ -37146,14 +37146,14 @@
         </is>
       </c>
       <c r="K582" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L582" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M582" s="2" t="inlineStr">
         <is>
-          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-pfoa-star-impex-ruft-blaukrabben-zurueck/37833</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22096/Interne</t>
         </is>
       </c>
     </row>
@@ -37165,22 +37165,22 @@
       </c>
       <c r="B583" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C583" s="2" t="inlineStr">
         <is>
-          <t>Asia Express Food (Green Box Limited)</t>
+          <t>Teba 44</t>
         </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E583" s="2" t="inlineStr">
         <is>
-          <t>Enoki-Pilzen</t>
+          <t>Pork rillettes — vacuum packs ~200 g (Lot 550326100002, use-by 2026-05-04)</t>
         </is>
       </c>
       <c r="F583" s="2" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="G583" s="2" t="inlineStr">
         <is>
-          <t>Der Großhändler Asia Express Food ruft Enoki-Pilze der Marke Green Box Limited zurück. Im Rahmen einer Kontrolle wurde das Bakterium Listeria monocytogenes nachgewiesen, und vom Verzehr wird dringend abgeraten.</t>
+          <t>Listeria detected</t>
         </is>
       </c>
       <c r="H583" s="2" t="inlineStr">
@@ -37200,7 +37200,7 @@
       </c>
       <c r="I583" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J583" s="2" t="inlineStr">
@@ -37216,7 +37216,7 @@
       </c>
       <c r="M583" s="2" t="inlineStr">
         <is>
-          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-listerien-in-enoki-pilzen-der-marke-green-box-limited/37823</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22101/Interne</t>
         </is>
       </c>
     </row>
@@ -37233,27 +37233,27 @@
       </c>
       <c r="C584" s="2" t="inlineStr">
         <is>
-          <t>REWE Dortmund</t>
+          <t>Star Impex</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Casabor</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
         <is>
-          <t>Schinken-Zwiebelmettwurst</t>
+          <t>Blue Swimming Crab Cut U/10 12x1, China origin (Casabor brand crab meat)</t>
         </is>
       </c>
       <c r="F584" s="2" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing E. coli (STEC)</t>
+          <t>PFOA / PFAS</t>
         </is>
       </c>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>Die REWE Dortmund ruft vier verschiedene Schinken-Zwiebelmettwurst Artikel zurück. In einer einzelnen Probe wurden Shigatoxin-bildende Escherichia coli (STEC) nachgewiesen, weshalb vom Verzehr dringend abgeraten wird.</t>
+          <t>PFOA (perfluorooctanoic acid) levels above the regulatory limit detected in lab tests</t>
         </is>
       </c>
       <c r="H584" s="2" t="inlineStr">
@@ -37272,14 +37272,14 @@
         </is>
       </c>
       <c r="K584" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L584" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M584" s="2" t="inlineStr">
         <is>
-          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-ecoli-rewe-dortmund-ruft-schinken-zwiebelmettwurst-zurueck/37840</t>
+          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-pfoa-star-impex-ruft-blaukrabben-zurueck/37833</t>
         </is>
       </c>
     </row>
@@ -37296,27 +37296,27 @@
       </c>
       <c r="C585" s="2" t="inlineStr">
         <is>
-          <t>Orienta Foods GmbH</t>
+          <t>Asia Express Food (Green Box Limited)</t>
         </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>Rino</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr">
         <is>
-          <t>Red chili powder 250 g and 500 g (best-before E2028/1/1, lot P2026/1/2)</t>
+          <t>Enoki-Pilzen</t>
         </is>
       </c>
       <c r="F585" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G585" s="2" t="inlineStr">
         <is>
-          <t>Health-hazardous aflatoxins detected during food inspection</t>
+          <t>Der Großhändler Asia Express Food ruft Enoki-Pilze der Marke Green Box Limited zurück. Im Rahmen einer Kontrolle wurde das Bakterium Listeria monocytogenes nachgewiesen, und vom Verzehr wird dringend abgeraten.</t>
         </is>
       </c>
       <c r="H585" s="2" t="inlineStr">
@@ -37335,14 +37335,14 @@
         </is>
       </c>
       <c r="K585" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L585" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M585" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260423_24_ST_Rotes_Chilipulver/260423_ST_Rotes_Chilipulver_Meldung.html</t>
+          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-listerien-in-enoki-pilzen-der-marke-green-box-limited/37823</t>
         </is>
       </c>
     </row>
@@ -37354,12 +37354,12 @@
       </c>
       <c r="B586" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C586" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: France</t>
+          <t>REWE Dortmund</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
@@ -37369,27 +37369,27 @@
       </c>
       <c r="E586" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkiye</t>
+          <t>Schinken-Zwiebelmettwurst</t>
         </is>
       </c>
       <c r="F586" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
         </is>
       </c>
       <c r="G586" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkiye; risk: serious; category: fruits and vegetables</t>
+          <t>Die REWE Dortmund ruft vier verschiedene Schinken-Zwiebelmettwurst Artikel zurück. In einer einzelnen Probe wurden Shigatoxin-bildende Escherichia coli (STEC) nachgewiesen, weshalb vom Verzehr dringend abgeraten wird.</t>
         </is>
       </c>
       <c r="H586" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I586" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J586" s="2" t="inlineStr">
@@ -37398,14 +37398,14 @@
         </is>
       </c>
       <c r="K586" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L586" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M586" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839681</t>
+          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-ecoli-rewe-dortmund-ruft-schinken-zwiebelmettwurst-zurueck/37840</t>
         </is>
       </c>
     </row>
@@ -37417,58 +37417,58 @@
       </c>
       <c r="B587" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C587" s="2" t="inlineStr">
         <is>
-          <t>Origin: Brazil | Notifying: Lithuania</t>
+          <t>Orienta Foods GmbH</t>
         </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rino</t>
         </is>
       </c>
       <c r="E587" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in frozen chicken breast fillets from Brazil</t>
+          <t>Red chili powder 250 g and 500 g (best-before E2028/1/1, lot P2026/1/2)</t>
         </is>
       </c>
       <c r="F587" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in frozen chicken breast fillets from Brazil; risk: not serious; category: poultry meat and poultry meat products</t>
+          <t>Health-hazardous aflatoxins detected during food inspection</t>
         </is>
       </c>
       <c r="H587" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I587" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J587" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K587" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L587" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M587" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839649</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260423_24_ST_Rotes_Chilipulver/260423_ST_Rotes_Chilipulver_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -37485,7 +37485,7 @@
       </c>
       <c r="C588" s="2" t="inlineStr">
         <is>
-          <t>Origin: Vietnam | Notifying: Germany</t>
+          <t>Origin: Türkiye | Notifying: France</t>
         </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
@@ -37495,7 +37495,7 @@
       </c>
       <c r="E588" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands</t>
+          <t>Aflatoxins in dried figs from Turkiye</t>
         </is>
       </c>
       <c r="F588" s="2" t="inlineStr">
@@ -37505,22 +37505,22 @@
       </c>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands; risk: serious; category: fruits and vegetables</t>
+          <t>Aflatoxins in dried figs from Turkiye; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H588" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I588" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J588" s="2" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K588" s="2" t="n">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="M588" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839480</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839681</t>
         </is>
       </c>
     </row>
@@ -37548,7 +37548,7 @@
       </c>
       <c r="C589" s="2" t="inlineStr">
         <is>
-          <t>Origin: United States | Notifying: Italy</t>
+          <t>Origin: Brazil | Notifying: Lithuania</t>
         </is>
       </c>
       <c r="D589" s="2" t="inlineStr">
@@ -37558,32 +37558,32 @@
       </c>
       <c r="E589" s="2" t="inlineStr">
         <is>
-          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin</t>
+          <t>Salmonella detected in frozen chicken breast fillets from Brazil</t>
         </is>
       </c>
       <c r="F589" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G589" s="2" t="inlineStr">
         <is>
-          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin; risk: serious; category: nuts, nut products and seeds</t>
+          <t>Salmonella detected in frozen chicken breast fillets from Brazil; risk: not serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H589" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I589" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J589" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K589" s="2" t="n">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="M589" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839423</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839649</t>
         </is>
       </c>
     </row>
@@ -37611,7 +37611,7 @@
       </c>
       <c r="C590" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: Vietnam | Notifying: Germany</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
@@ -37621,7 +37621,7 @@
       </c>
       <c r="E590" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in roasted and salted pistachios from Turkey</t>
+          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands</t>
         </is>
       </c>
       <c r="F590" s="2" t="inlineStr">
@@ -37631,22 +37631,22 @@
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in roasted and salted pistachios from Turkey; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H590" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I590" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="J590" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="K590" s="2" t="n">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="M590" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839296</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839480</t>
         </is>
       </c>
     </row>
@@ -37674,7 +37674,7 @@
       </c>
       <c r="C591" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: United States | Notifying: Italy</t>
         </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
@@ -37684,32 +37684,32 @@
       </c>
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus in tomatoes from Türkiye</t>
+          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin</t>
         </is>
       </c>
       <c r="F591" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus in tomatoes from Türkiye; risk: potential risk; category: fruits and vegetables</t>
+          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin; risk: serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H591" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I591" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J591" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K591" s="2" t="n">
@@ -37720,7 +37720,7 @@
       </c>
       <c r="M591" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838854</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839423</t>
         </is>
       </c>
     </row>
@@ -37737,53 +37737,53 @@
       </c>
       <c r="C592" s="2" t="inlineStr">
         <is>
-          <t>Origin: China | Notifying: Germany | Distributed: Germany, Hungary, multi-EU</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>Green Box Limited</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>Fresh enoki mushrooms (chilled, packaged), Green Box Limited brand</t>
+          <t>Aflatoxins in roasted and salted pistachios from Turkey</t>
         </is>
       </c>
       <c r="F592" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes detected in chilled packaged enoki mushrooms (Chinese origin); recall by German wholesaler Asia Express Food, distributed across multiple EU member states including Hungary</t>
+          <t>Aflatoxins in roasted and salted pistachios from Turkey; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H592" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I592" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J592" s="2" t="inlineStr">
         <is>
-          <t>Asia (origin) / Europe (distribution)</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K592" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L592" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M592" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838838</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839296</t>
         </is>
       </c>
     </row>
@@ -37800,7 +37800,7 @@
       </c>
       <c r="C593" s="2" t="inlineStr">
         <is>
-          <t>Origin: Italy | Notifying: Switzerland</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D593" s="2" t="inlineStr">
@@ -37810,17 +37810,17 @@
       </c>
       <c r="E593" s="2" t="inlineStr">
         <is>
-          <t>Listeria in frozen sugar snap peas</t>
+          <t>Bacillus cereus in tomatoes from Türkiye</t>
         </is>
       </c>
       <c r="F593" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Bacillus cereus</t>
         </is>
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>Listeria in frozen sugar snap peas; risk: not serious; category: fruits and vegetables</t>
+          <t>Bacillus cereus in tomatoes from Türkiye; risk: potential risk; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H593" s="2" t="inlineStr">
@@ -37830,7 +37830,7 @@
       </c>
       <c r="I593" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J593" s="2" t="inlineStr">
@@ -37839,14 +37839,14 @@
         </is>
       </c>
       <c r="K593" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L593" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M593" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837117</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838854</t>
         </is>
       </c>
     </row>
@@ -37863,17 +37863,17 @@
       </c>
       <c r="C594" s="2" t="inlineStr">
         <is>
-          <t>Origin: Italy | Notifying: Switzerland</t>
+          <t>Origin: China | Notifying: Germany | Distributed: Germany, Hungary, multi-EU</t>
         </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Green Box Limited</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
         <is>
-          <t>Listeria in frozen Edamame Soybeans</t>
+          <t>Fresh enoki mushrooms (chilled, packaged), Green Box Limited brand</t>
         </is>
       </c>
       <c r="F594" s="2" t="inlineStr">
@@ -37883,22 +37883,22 @@
       </c>
       <c r="G594" s="2" t="inlineStr">
         <is>
-          <t>Listeria in frozen Edamame Soybeans; risk: not serious; category: fruits and vegetables</t>
+          <t>Listeria monocytogenes detected in chilled packaged enoki mushrooms (Chinese origin); recall by German wholesaler Asia Express Food, distributed across multiple EU member states including Hungary</t>
         </is>
       </c>
       <c r="H594" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I594" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>China</t>
         </is>
       </c>
       <c r="J594" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia (origin) / Europe (distribution)</t>
         </is>
       </c>
       <c r="K594" s="2" t="n">
@@ -37909,7 +37909,7 @@
       </c>
       <c r="M594" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837094</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838838</t>
         </is>
       </c>
     </row>
@@ -37926,7 +37926,7 @@
       </c>
       <c r="C595" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Malta</t>
+          <t>Origin: Italy | Notifying: Switzerland</t>
         </is>
       </c>
       <c r="D595" s="2" t="inlineStr">
@@ -37936,27 +37936,27 @@
       </c>
       <c r="E595" s="2" t="inlineStr">
         <is>
-          <t>Presence of Ochratoxin A in dried figs from Turkey</t>
+          <t>Listeria in frozen sugar snap peas</t>
         </is>
       </c>
       <c r="F595" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G595" s="2" t="inlineStr">
         <is>
-          <t>Presence of Ochratoxin A in dried figs from Turkey; risk: potential risk; category: fruits and vegetables</t>
+          <t>Listeria in frozen sugar snap peas; risk: not serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H595" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I595" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="J595" s="2" t="inlineStr">
@@ -37965,14 +37965,14 @@
         </is>
       </c>
       <c r="K595" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L595" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M595" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/820697</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837117</t>
         </is>
       </c>
     </row>
@@ -37984,22 +37984,22 @@
       </c>
       <c r="B596" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C596" s="2" t="inlineStr">
         <is>
-          <t>PALMITA II super u</t>
+          <t>Origin: Italy | Notifying: Switzerland</t>
         </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>Belle Henriette</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
         <is>
-          <t>Chicken-and-roast-chicken tabbouleh (GTIN 3342280891952, Lot 609031, use-by 2026-04-26)</t>
+          <t>Listeria in frozen Edamame Soybeans</t>
         </is>
       </c>
       <c r="F596" s="2" t="inlineStr">
@@ -38009,17 +38009,17 @@
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes detected</t>
+          <t>Listeria in frozen Edamame Soybeans; risk: not serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H596" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I596" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="J596" s="2" t="inlineStr">
@@ -38035,7 +38035,7 @@
       </c>
       <c r="M596" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22114/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/837094</t>
         </is>
       </c>
     </row>
@@ -38047,12 +38047,12 @@
       </c>
       <c r="B597" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C597" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: France</t>
+          <t>Origin: Türkiye | Notifying: Malta</t>
         </is>
       </c>
       <c r="D597" s="2" t="inlineStr">
@@ -38062,27 +38062,27 @@
       </c>
       <c r="E597" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>Presence of Ochratoxin A in dried figs from Turkey</t>
         </is>
       </c>
       <c r="F597" s="2" t="inlineStr">
         <is>
-          <t>Histamine / scombrotoxin</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkiye; risk: serious; category: fruits and vegetables</t>
+          <t>Presence of Ochratoxin A in dried figs from Turkey; risk: potential risk; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H597" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I597" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J597" s="2" t="inlineStr">
@@ -38091,14 +38091,14 @@
         </is>
       </c>
       <c r="K597" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L597" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M597" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22113/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/820697</t>
         </is>
       </c>
     </row>
@@ -38115,17 +38115,17 @@
       </c>
       <c r="C598" s="2" t="inlineStr">
         <is>
-          <t>Teba 44</t>
+          <t>PALMITA II super u</t>
         </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Belle Henriette</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
         <is>
-          <t>Pork rillettes — vacuum packs ~200 g (Lot 550326100002, use-by 2026-05-04)</t>
+          <t>Chicken-and-roast-chicken tabbouleh (GTIN 3342280891952, Lot 609031, use-by 2026-04-26)</t>
         </is>
       </c>
       <c r="F598" s="2" t="inlineStr">
@@ -38135,7 +38135,7 @@
       </c>
       <c r="G598" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected</t>
+          <t>Listeria monocytogenes detected</t>
         </is>
       </c>
       <c r="H598" s="2" t="inlineStr">
@@ -38161,7 +38161,7 @@
       </c>
       <c r="M598" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22101/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22114/Interne</t>
         </is>
       </c>
     </row>
@@ -38178,27 +38178,27 @@
       </c>
       <c r="C599" s="2" t="inlineStr">
         <is>
-          <t>ETABLISSEMENTS J. CHENE ET FILS Ets Chêne &amp; Fils</t>
+          <t>Origin: Türkiye | Notifying: France</t>
         </is>
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>Patifrais (fabriqué par Ets Chêne &amp; Fils)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E599" s="2" t="inlineStr">
         <is>
-          <t>Beef-snout salad — 500 g modified-atmosphere tray (GTIN 3537949991436, Lot 163, use-by 2026-05-05 and 2026-05-07)</t>
+          <t>produits de la pêche et d'aquaculture</t>
         </is>
       </c>
       <c r="F599" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Histamine / scombrotoxin</t>
         </is>
       </c>
       <c r="G599" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Aflatoxins in dried figs from Turkiye; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H599" s="2" t="inlineStr">
@@ -38217,14 +38217,14 @@
         </is>
       </c>
       <c r="K599" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L599" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M599" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22096/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22113/Interne</t>
         </is>
       </c>
     </row>
@@ -41764,58 +41764,58 @@
       </c>
       <c r="B656" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>Gomez Shellfish, LLC (WA-1724-SS)</t>
+          <t>Color Foods</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SUNCHEFS</t>
         </is>
       </c>
       <c r="E656" s="2" t="inlineStr">
         <is>
-          <t>Recalled shellfish — all species of shellstock (oysters, clams) harvested 2026-03-22 through 2026-04-09 from a portion of Hammersley Inlet, WA. Distributed to restaurants and retailers in CA, OR, TX, WA — possibly further distributed.</t>
+          <t>Roasted salted sunflower seeds 500 g SUNCHEFS (GTIN 3068230019145, Lot 510085)</t>
         </is>
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Alternaria toxins (mycotoxin)</t>
         </is>
       </c>
       <c r="G656" s="2" t="inlineStr">
         <is>
-          <t>Potential norovirus contamination — norovirus-like illnesses associated with raw oyster consumption; recall initiated by Washington State Department of Health 2026-04-10; FDA safety alert published 2026-04-17 advising no eat/serve/sell</t>
+          <t>Exceedance of indicative levels for Alternaria toxins</t>
         </is>
       </c>
       <c r="H656" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I656" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J656" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K656" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L656" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M656" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/food/alerts-advisories-safety-information/fda-advises-restaurants-and-retailers-not-serve-or-sell-and-consumers-not-eat-recalled-shellfish</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22053/Interne</t>
         </is>
       </c>
     </row>
@@ -41827,58 +41827,58 @@
       </c>
       <c r="B657" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C657" s="2" t="inlineStr">
         <is>
-          <t>Rossmann</t>
+          <t>Origin: Georgia | Notifying: Germany</t>
         </is>
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>Foodloose</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E657" s="2" t="inlineStr">
         <is>
-          <t>White Delights-Pistazie</t>
+          <t>Aflatoxins in hazelnut flour from Georgia</t>
         </is>
       </c>
       <c r="F657" s="2" t="inlineStr">
         <is>
-          <t>Physical/foreign-body contamination</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G657" s="2" t="inlineStr">
         <is>
-          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
+          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H657" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I657" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="J657" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K657" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L657" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M657" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-rossmann-foodloose.pdf.download.pdf/R%C3%BCckruf%20Aushang_Foodloose_16.04.2026_aktualisiert.pdf</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838092</t>
         </is>
       </c>
     </row>
@@ -41890,32 +41890,32 @@
       </c>
       <c r="B658" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>Phag GmbH</t>
+          <t>Gomez Shellfish, LLC (WA-1724-SS)</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
         <is>
-          <t>Foodloose</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E658" s="2" t="inlineStr">
         <is>
-          <t>White Delights-Pistazie</t>
+          <t>Recalled shellfish — all species of shellstock (oysters, clams) harvested 2026-03-22 through 2026-04-09 from a portion of Hammersley Inlet, WA. Distributed to restaurants and retailers in CA, OR, TX, WA — possibly further distributed.</t>
         </is>
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>Physical/foreign-body contamination</t>
+          <t>Norovirus</t>
         </is>
       </c>
       <c r="G658" s="2" t="inlineStr">
         <is>
-          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
+          <t>Potential norovirus contamination — norovirus-like illnesses associated with raw oyster consumption; recall initiated by Washington State Department of Health 2026-04-10; FDA safety alert published 2026-04-17 advising no eat/serve/sell</t>
         </is>
       </c>
       <c r="H658" s="2" t="inlineStr">
@@ -41925,23 +41925,23 @@
       </c>
       <c r="I658" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J658" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K658" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L658" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M658" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-phag-gmbh-foodloose.pdf.download.pdf/Marktaushang%20R%C3%BCckruf%20(erweitert).pdf</t>
+          <t>https://www.fda.gov/food/alerts-advisories-safety-information/fda-advises-restaurants-and-retailers-not-serve-or-sell-and-consumers-not-eat-recalled-shellfish</t>
         </is>
       </c>
     </row>
@@ -41953,42 +41953,42 @@
       </c>
       <c r="B659" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C659" s="2" t="inlineStr">
         <is>
-          <t>Origin: Slovakia | Notifying: France</t>
+          <t>Rossmann</t>
         </is>
       </c>
       <c r="D659" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Foodloose</t>
         </is>
       </c>
       <c r="E659" s="2" t="inlineStr">
         <is>
-          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken</t>
+          <t>White Delights-Pistazie</t>
         </is>
       </c>
       <c r="F659" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Physical/foreign-body contamination</t>
         </is>
       </c>
       <c r="G659" s="2" t="inlineStr">
         <is>
-          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken; risk: serious; category: poultry meat and poultry meat products</t>
+          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
         </is>
       </c>
       <c r="H659" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I659" s="2" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J659" s="2" t="inlineStr">
@@ -41997,14 +41997,14 @@
         </is>
       </c>
       <c r="K659" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L659" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M659" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838436</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-rossmann-foodloose.pdf.download.pdf/R%C3%BCckruf%20Aushang_Foodloose_16.04.2026_aktualisiert.pdf</t>
         </is>
       </c>
     </row>
@@ -42016,58 +42016,58 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>Origin: Georgia | Notifying: Germany</t>
+          <t>Phag GmbH</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Foodloose</t>
         </is>
       </c>
       <c r="E660" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia</t>
+          <t>White Delights-Pistazie</t>
         </is>
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Physical/foreign-body contamination</t>
         </is>
       </c>
       <c r="G660" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
         </is>
       </c>
       <c r="H660" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I660" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J660" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K660" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L660" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M660" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838360</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-phag-gmbh-foodloose.pdf.download.pdf/Marktaushang%20R%C3%BCckruf%20(erweitert).pdf</t>
         </is>
       </c>
     </row>
@@ -42084,7 +42084,7 @@
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>Origin: Chile | Notifying: Sweden</t>
+          <t>Origin: Slovakia | Notifying: France</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="E661" s="2" t="inlineStr">
         <is>
-          <t>Lack of guarantee concerning salmonella in pork</t>
+          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken</t>
         </is>
       </c>
       <c r="F661" s="2" t="inlineStr">
@@ -42104,22 +42104,22 @@
       </c>
       <c r="G661" s="2" t="inlineStr">
         <is>
-          <t>Lack of guarantee concerning salmonella in pork; risk: potentially serious; category: meat and meat products (other than poultry)</t>
+          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken; risk: serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H661" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I661" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="J661" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K661" s="2" t="n">
@@ -42130,7 +42130,7 @@
       </c>
       <c r="M661" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838294</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838436</t>
         </is>
       </c>
     </row>
@@ -42157,7 +42157,7 @@
       </c>
       <c r="E662" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnuts from Georgia</t>
+          <t>Aflatoxins in hazelnut flour from Georgia</t>
         </is>
       </c>
       <c r="F662" s="2" t="inlineStr">
@@ -42167,7 +42167,7 @@
       </c>
       <c r="G662" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnuts from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H662" s="2" t="inlineStr">
@@ -42193,7 +42193,7 @@
       </c>
       <c r="M662" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838265</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838360</t>
         </is>
       </c>
     </row>
@@ -42210,7 +42210,7 @@
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>Origin: Georgia | Notifying: Germany</t>
+          <t>Origin: Chile | Notifying: Sweden</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
@@ -42220,32 +42220,32 @@
       </c>
       <c r="E663" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia</t>
+          <t>Lack of guarantee concerning salmonella in pork</t>
         </is>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G663" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Lack of guarantee concerning salmonella in pork; risk: potentially serious; category: meat and meat products (other than poultry)</t>
         </is>
       </c>
       <c r="H663" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I663" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J663" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K663" s="2" t="n">
@@ -42256,7 +42256,7 @@
       </c>
       <c r="M663" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838234</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838294</t>
         </is>
       </c>
     </row>
@@ -42273,7 +42273,7 @@
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: Georgia | Notifying: Germany</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -42283,17 +42283,17 @@
       </c>
       <c r="E664" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Turkey</t>
+          <t>Aflatoxins in hazelnuts from Georgia</t>
         </is>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G664" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Turkey; risk: potentially serious; category: fruits and vegetables</t>
+          <t>Aflatoxins in hazelnuts from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H664" s="2" t="inlineStr">
@@ -42303,12 +42303,12 @@
       </c>
       <c r="I664" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="J664" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K664" s="2" t="n">
@@ -42319,7 +42319,7 @@
       </c>
       <c r="M664" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838225</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838265</t>
         </is>
       </c>
     </row>
@@ -42336,7 +42336,7 @@
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: Georgia | Notifying: Germany</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -42346,17 +42346,17 @@
       </c>
       <c r="E665" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Türkiye</t>
+          <t>Aflatoxins in hazelnut flour from Georgia</t>
         </is>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G665" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A in dried figs from Türkiye; risk: potentially serious; category: fruits and vegetables</t>
+          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H665" s="2" t="inlineStr">
@@ -42366,12 +42366,12 @@
       </c>
       <c r="I665" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="J665" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K665" s="2" t="n">
@@ -42382,7 +42382,7 @@
       </c>
       <c r="M665" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838212</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838234</t>
         </is>
       </c>
     </row>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>Origin: Iran | Notifying: Germany</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -42409,17 +42409,17 @@
       </c>
       <c r="E666" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in pistachio kernels from Iran</t>
+          <t>Ochratoxin A in dried figs from Turkey</t>
         </is>
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G666" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in pistachio kernels from Iran; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Ochratoxin A in dried figs from Turkey; risk: potentially serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H666" s="2" t="inlineStr">
@@ -42429,12 +42429,12 @@
       </c>
       <c r="I666" s="2" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J666" s="2" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K666" s="2" t="n">
@@ -42445,7 +42445,7 @@
       </c>
       <c r="M666" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838210</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838225</t>
         </is>
       </c>
     </row>
@@ -42472,7 +42472,7 @@
       </c>
       <c r="E667" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A contamination in dried figs from Turkey</t>
+          <t>Ochratoxin A in dried figs from Türkiye</t>
         </is>
       </c>
       <c r="F667" s="2" t="inlineStr">
@@ -42482,7 +42482,7 @@
       </c>
       <c r="G667" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A contamination in dried figs from Turkey; risk: potentially serious; category: fruits and vegetables</t>
+          <t>Ochratoxin A in dried figs from Türkiye; risk: potentially serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H667" s="2" t="inlineStr">
@@ -42508,7 +42508,7 @@
       </c>
       <c r="M667" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838199</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838212</t>
         </is>
       </c>
     </row>
@@ -42525,7 +42525,7 @@
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>Origin: Georgia | Notifying: Germany</t>
+          <t>Origin: Iran | Notifying: Germany</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -42535,7 +42535,7 @@
       </c>
       <c r="E668" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia</t>
+          <t>Aflatoxins in pistachio kernels from Iran</t>
         </is>
       </c>
       <c r="F668" s="2" t="inlineStr">
@@ -42545,7 +42545,7 @@
       </c>
       <c r="G668" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Aflatoxins in pistachio kernels from Iran; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H668" s="2" t="inlineStr">
@@ -42555,12 +42555,12 @@
       </c>
       <c r="I668" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="J668" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="K668" s="2" t="n">
@@ -42571,7 +42571,7 @@
       </c>
       <c r="M668" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838092</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838210</t>
         </is>
       </c>
     </row>
@@ -42583,42 +42583,42 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>Color Foods</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>SUNCHEFS</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E669" s="2" t="inlineStr">
         <is>
-          <t>Roasted salted sunflower seeds 500 g SUNCHEFS (GTIN 3068230019145, Lot 510085)</t>
+          <t>Ochratoxin A contamination in dried figs from Turkey</t>
         </is>
       </c>
       <c r="F669" s="2" t="inlineStr">
         <is>
-          <t>Alternaria toxins (mycotoxin)</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G669" s="2" t="inlineStr">
         <is>
-          <t>Exceedance of indicative levels for Alternaria toxins</t>
+          <t>Ochratoxin A contamination in dried figs from Turkey; risk: potentially serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H669" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I669" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J669" s="2" t="inlineStr">
@@ -42634,7 +42634,7 @@
       </c>
       <c r="M669" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22053/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838199</t>
         </is>
       </c>
     </row>
@@ -46111,47 +46111,47 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>MAPAQ QC</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>chocoStyle 440</t>
+          <t>Luna Food</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
         <is>
-          <t>chocoStyle 440</t>
+          <t>Foodles</t>
         </is>
       </c>
       <c r="E725" s="2" t="inlineStr">
         <is>
-          <t>Pistachio chocolate bars and pistachio chocolate bites</t>
+          <t>Cooked salmon poke (GTIN 3760424624356, use-by 2026-04-02 to 2026-04-04)</t>
         </is>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G725" s="2" t="inlineStr">
         <is>
-          <t>Possible Salmonella contamination — linked to national pistachio outbreak investigation</t>
+          <t>Listeria detected in the manufacturing environment</t>
         </is>
       </c>
       <c r="H725" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I725" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J725" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K725" s="2" t="n">
@@ -46162,7 +46162,7 @@
       </c>
       <c r="M725" s="2" t="inlineStr">
         <is>
-          <t>https://www.quebec.ca/nouvelles/actualites/details/mise-en-garde-a-la-population-presence-possible-de-salmonelle-dans-les-barres-de-chocolat-aux-pistaches-et-les-bouchees-de-chocolat-aux-pistaches-preparees-et-vendues-par-lentreprise-chocostyle-440-69727</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21993/Interne</t>
         </is>
       </c>
     </row>
@@ -46174,42 +46174,42 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>foodloose</t>
+          <t>Luna Food</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
         <is>
-          <t>foodloose</t>
+          <t>Foodles</t>
         </is>
       </c>
       <c r="E726" s="2" t="inlineStr">
         <is>
-          <t>Bio-Dattel-Kugeln White Delight Pistazie (best-before 2026-10-04, batch J49B0)</t>
+          <t>Kimbap with kimchi and vegetables (GTIN 3760373402043, use-by 2026-04-02 to 2026-04-04)</t>
         </is>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>Physical/foreign-body contamination</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G726" s="2" t="inlineStr">
         <is>
-          <t>Foreign-body contamination posing injury risk cannot be excluded in individual packages</t>
+          <t>Listeria detected in the manufacturing environment</t>
         </is>
       </c>
       <c r="H726" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I726" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J726" s="2" t="inlineStr">
@@ -46218,14 +46218,14 @@
         </is>
       </c>
       <c r="K726" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L726" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M726" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_12_HH_Suessware_Pistazie/260410_12_HH_Suessware_Pistazie_Meldung.html</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21994/Interne</t>
         </is>
       </c>
     </row>
@@ -46237,22 +46237,22 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>MAPAQ QC</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>Sächsische und Dresdner Back- und Süßwaren GmbH</t>
+          <t>chocoStyle 440</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
         <is>
-          <t>Nudossi</t>
+          <t>chocoStyle 440</t>
         </is>
       </c>
       <c r="E727" s="2" t="inlineStr">
         <is>
-          <t>Nudossi Hazelnut-Nougat-Crème, 300 g jar (specific batches affected)</t>
+          <t>Pistachio chocolate bars and pistachio chocolate bites</t>
         </is>
       </c>
       <c r="F727" s="2" t="inlineStr">
@@ -46262,22 +46262,22 @@
       </c>
       <c r="G727" s="2" t="inlineStr">
         <is>
-          <t>Positive Salmonella test result in specific batches</t>
+          <t>Possible Salmonella contamination — linked to national pistachio outbreak investigation</t>
         </is>
       </c>
       <c r="H727" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I727" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J727" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K727" s="2" t="n">
@@ -46288,7 +46288,7 @@
       </c>
       <c r="M727" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_10_SN_Nuss-Nougat-Creme/260410_10_SN_Nuss-Nougat-Creme_Meldung.html</t>
+          <t>https://www.quebec.ca/nouvelles/actualites/details/mise-en-garde-a-la-population-presence-possible-de-salmonelle-dans-les-barres-de-chocolat-aux-pistaches-et-les-bouchees-de-chocolat-aux-pistaches-preparees-et-vendues-par-lentreprise-chocostyle-440-69727</t>
         </is>
       </c>
     </row>
@@ -46300,47 +46300,47 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>Origin: Uzbekistan | Notifying: Denmark</t>
+          <t>foodloose</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>foodloose</t>
         </is>
       </c>
       <c r="E728" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany</t>
+          <t>Bio-Dattel-Kugeln White Delight Pistazie (best-before 2026-10-04, batch J49B0)</t>
         </is>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Physical/foreign-body contamination</t>
         </is>
       </c>
       <c r="G728" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany; risk: serious; category: fruits and vegetables</t>
+          <t>Foreign-body contamination posing injury risk cannot be excluded in individual packages</t>
         </is>
       </c>
       <c r="H728" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I728" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J728" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K728" s="2" t="n">
@@ -46351,7 +46351,7 @@
       </c>
       <c r="M728" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836889</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_12_HH_Suessware_Pistazie/260410_12_HH_Suessware_Pistazie_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -46363,42 +46363,42 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>Origin: Netherlands | Notifying: Belgium</t>
+          <t>Sächsische und Dresdner Back- und Süßwaren GmbH</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nudossi</t>
         </is>
       </c>
       <c r="E729" s="2" t="inlineStr">
         <is>
-          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands</t>
+          <t>Nudossi Hazelnut-Nougat-Crème, 300 g jar (specific batches affected)</t>
         </is>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G729" s="2" t="inlineStr">
         <is>
-          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands; risk: potentially serious; category: bivalve molluscs and products thereof</t>
+          <t>Positive Salmonella test result in specific batches</t>
         </is>
       </c>
       <c r="H729" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I729" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J729" s="2" t="inlineStr">
@@ -46407,14 +46407,14 @@
         </is>
       </c>
       <c r="K729" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L729" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M729" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836765</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_10_SN_Nuss-Nougat-Creme/260410_10_SN_Nuss-Nougat-Creme_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -46431,7 +46431,7 @@
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>Origin: Brazil | Notifying: Croatia</t>
+          <t>Origin: Uzbekistan | Notifying: Denmark</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
@@ -46441,32 +46441,32 @@
       </c>
       <c r="E730" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp. in frozen poultry meat from Brazil</t>
+          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany</t>
         </is>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G730" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp. in frozen poultry meat from Brazil; risk: potential risk; category: poultry meat and poultry meat products</t>
+          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H730" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I730" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="J730" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K730" s="2" t="n">
@@ -46477,7 +46477,7 @@
       </c>
       <c r="M730" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836741</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836889</t>
         </is>
       </c>
     </row>
@@ -46494,7 +46494,7 @@
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>Origin: Turkey | Notifying: Germany | Distributed: Germany</t>
+          <t>Origin: Netherlands | Notifying: Belgium</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -46504,17 +46504,17 @@
       </c>
       <c r="E731" s="2" t="inlineStr">
         <is>
-          <t>Dry figs from Turkey</t>
+          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands</t>
         </is>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A</t>
+          <t>Norovirus</t>
         </is>
       </c>
       <c r="G731" s="2" t="inlineStr">
         <is>
-          <t>High level of Ochratoxin A detected in dry figs from Turkey distributed in Germany</t>
+          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands; risk: potentially serious; category: bivalve molluscs and products thereof</t>
         </is>
       </c>
       <c r="H731" s="2" t="inlineStr">
@@ -46524,7 +46524,7 @@
       </c>
       <c r="I731" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="J731" s="2" t="inlineStr">
@@ -46540,7 +46540,7 @@
       </c>
       <c r="M731" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836362</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836765</t>
         </is>
       </c>
     </row>
@@ -46557,7 +46557,7 @@
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>Origin: Turkey | Notifying: unknown | Distributed: EU (multi)</t>
+          <t>Origin: Brazil | Notifying: Croatia</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -46567,32 +46567,32 @@
       </c>
       <c r="E732" s="2" t="inlineStr">
         <is>
-          <t>Dry figs from Turkey</t>
+          <t>Salmonella spp. in frozen poultry meat from Brazil</t>
         </is>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G732" s="2" t="inlineStr">
         <is>
-          <t>High level of Ochratoxin A detected in dry figs from Turkey</t>
+          <t>Salmonella spp. in frozen poultry meat from Brazil; risk: potential risk; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H732" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I732" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J732" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K732" s="2" t="n">
@@ -46603,7 +46603,7 @@
       </c>
       <c r="M732" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836354</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836741</t>
         </is>
       </c>
     </row>
@@ -46615,58 +46615,58 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>Sultan Fine Foods</t>
+          <t>Origin: Turkey | Notifying: Germany | Distributed: Germany</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
         <is>
-          <t>Sultan Fine Foods</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E733" s="2" t="inlineStr">
         <is>
-          <t>Pistachio Kernel, 10 kg (Lot TME20250825PK, best-before AUG 2027)</t>
+          <t>Dry figs from Turkey</t>
         </is>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Ochratoxin A</t>
         </is>
       </c>
       <c r="G733" s="2" t="inlineStr">
         <is>
-          <t>Salmonella contamination — precautionary recall (linked to ongoing Iranian pistachio outbreak investigation; no illnesses tied to this specific Sultan product per CFIA page)</t>
+          <t>High level of Ochratoxin A detected in dry figs from Turkey distributed in Germany</t>
         </is>
       </c>
       <c r="H733" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I733" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J733" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K733" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L733" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M733" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/pistachio-kernel-recalled-due-salmonella-0</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836362</t>
         </is>
       </c>
     </row>
@@ -46678,58 +46678,58 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>Fresh Start Foods</t>
+          <t>Origin: Turkey | Notifying: unknown | Distributed: EU (multi)</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
         <is>
-          <t>Fresh Start Foods</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E734" s="2" t="inlineStr">
         <is>
-          <t>Salads (BC)</t>
+          <t>Dry figs from Turkey</t>
         </is>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Ochratoxin A</t>
         </is>
       </c>
       <c r="G734" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>High level of Ochratoxin A detected in dry figs from Turkey</t>
         </is>
       </c>
       <c r="H734" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I734" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J734" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K734" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L734" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M734" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/fresh-start-foods-brand-salads-recalled-due-listeria-monocytogenes</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836354</t>
         </is>
       </c>
     </row>
@@ -46741,58 +46741,58 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>Freres Bluteau</t>
+          <t>Sultan Fine Foods</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
         <is>
-          <t>La ferme de la thibauderie</t>
+          <t>Sultan Fine Foods</t>
         </is>
       </c>
       <c r="E735" s="2" t="inlineStr">
         <is>
-          <t>Fresh raw-milk goat cheese (round)</t>
+          <t>Pistachio Kernel, 10 kg (Lot TME20250825PK, best-before AUG 2027)</t>
         </is>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
-          <t>Staphylococcus enterotoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G735" s="2" t="inlineStr">
         <is>
-          <t>Staphylococcus enterotoxin contamination</t>
+          <t>Salmonella contamination — precautionary recall (linked to ongoing Iranian pistachio outbreak investigation; no illnesses tied to this specific Sultan product per CFIA page)</t>
         </is>
       </c>
       <c r="H735" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I735" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J735" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K735" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L735" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M735" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22009/Interne</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/pistachio-kernel-recalled-due-salmonella-0</t>
         </is>
       </c>
     </row>
@@ -46804,22 +46804,22 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>DROME ARDECHE TRADITION Drôme Ardèche Tradition</t>
+          <t>Fresh Start Foods</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
         <is>
-          <t>Jules Courtial</t>
+          <t>Fresh Start Foods</t>
         </is>
       </c>
       <c r="E736" s="2" t="inlineStr">
         <is>
-          <t>SAUCISSON KIKISSON ~200 g (GTIN 3327780200701, Lot 126005, best-before 2026-04-09 to 2026-05-25)</t>
+          <t>Salads (BC)</t>
         </is>
       </c>
       <c r="F736" s="2" t="inlineStr">
@@ -46829,22 +46829,22 @@
       </c>
       <c r="G736" s="2" t="inlineStr">
         <is>
-          <t>Suspicion of Listeria monocytogenes</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H736" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I736" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J736" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K736" s="2" t="n">
@@ -46855,7 +46855,7 @@
       </c>
       <c r="M736" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22006/Interne</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/fresh-start-foods-brand-salads-recalled-due-listeria-monocytogenes</t>
         </is>
       </c>
     </row>
@@ -46872,27 +46872,27 @@
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>DROME ARDECHE TRADITION Drôme Ardèche Tradition</t>
+          <t>Freres Bluteau</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>La ferme de la thibauderie</t>
         </is>
       </c>
       <c r="E737" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>Fresh raw-milk goat cheese (round)</t>
         </is>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Staphylococcus enterotoxin</t>
         </is>
       </c>
       <c r="G737" s="2" t="inlineStr">
         <is>
-          <t>Suspicion of Listeria monocytogenes</t>
+          <t>Staphylococcus enterotoxin contamination</t>
         </is>
       </c>
       <c r="H737" s="2" t="inlineStr">
@@ -46918,7 +46918,7 @@
       </c>
       <c r="M737" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22005/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22009/Interne</t>
         </is>
       </c>
     </row>
@@ -46945,7 +46945,7 @@
       </c>
       <c r="E738" s="2" t="inlineStr">
         <is>
-          <t>SAUCISSON TRADITION VPF (lot details per fiche — fetch deferred for batch speed)</t>
+          <t>SAUCISSON KIKISSON ~200 g (GTIN 3327780200701, Lot 126005, best-before 2026-04-09 to 2026-05-25)</t>
         </is>
       </c>
       <c r="F738" s="2" t="inlineStr">
@@ -46981,7 +46981,7 @@
       </c>
       <c r="M738" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22004/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22006/Interne</t>
         </is>
       </c>
     </row>
@@ -47003,12 +47003,12 @@
       </c>
       <c r="D739" s="2" t="inlineStr">
         <is>
-          <t>Jules Courtial</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E739" s="2" t="inlineStr">
         <is>
-          <t>SAUCISSON DE L'ARDECHE IGP VPF (lot details per fiche — fetch deferred for batch speed)</t>
+          <t>produits de la pêche et d'aquaculture</t>
         </is>
       </c>
       <c r="F739" s="2" t="inlineStr">
@@ -47037,14 +47037,14 @@
         </is>
       </c>
       <c r="K739" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L739" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M739" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22002/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22005/Interne</t>
         </is>
       </c>
     </row>
@@ -47071,7 +47071,7 @@
       </c>
       <c r="E740" s="2" t="inlineStr">
         <is>
-          <t>SAUCISSON SEC 250 g VPF (lot details per fiche — fetch deferred for batch speed)</t>
+          <t>SAUCISSON TRADITION VPF (lot details per fiche — fetch deferred for batch speed)</t>
         </is>
       </c>
       <c r="F740" s="2" t="inlineStr">
@@ -47107,7 +47107,7 @@
       </c>
       <c r="M740" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/22001/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22004/Interne</t>
         </is>
       </c>
     </row>
@@ -47124,17 +47124,17 @@
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>Luna Food</t>
+          <t>DROME ARDECHE TRADITION Drôme Ardèche Tradition</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
         <is>
-          <t>Foodles</t>
+          <t>Jules Courtial</t>
         </is>
       </c>
       <c r="E741" s="2" t="inlineStr">
         <is>
-          <t>Kimbap with kimchi and vegetables (GTIN 3760373402043, use-by 2026-04-02 to 2026-04-04)</t>
+          <t>SAUCISSON DE L'ARDECHE IGP VPF (lot details per fiche — fetch deferred for batch speed)</t>
         </is>
       </c>
       <c r="F741" s="2" t="inlineStr">
@@ -47144,12 +47144,12 @@
       </c>
       <c r="G741" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected in the manufacturing environment</t>
+          <t>Suspicion of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H741" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I741" s="2" t="inlineStr">
@@ -47170,7 +47170,7 @@
       </c>
       <c r="M741" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21994/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22002/Interne</t>
         </is>
       </c>
     </row>
@@ -47187,17 +47187,17 @@
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>Luna Food</t>
+          <t>DROME ARDECHE TRADITION Drôme Ardèche Tradition</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>Foodles</t>
+          <t>Jules Courtial</t>
         </is>
       </c>
       <c r="E742" s="2" t="inlineStr">
         <is>
-          <t>Cooked salmon poke (GTIN 3760424624356, use-by 2026-04-02 to 2026-04-04)</t>
+          <t>SAUCISSON SEC 250 g VPF (lot details per fiche — fetch deferred for batch speed)</t>
         </is>
       </c>
       <c r="F742" s="2" t="inlineStr">
@@ -47207,12 +47207,12 @@
       </c>
       <c r="G742" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected in the manufacturing environment</t>
+          <t>Suspicion of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H742" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I742" s="2" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="M742" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21993/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/22001/Interne</t>
         </is>
       </c>
     </row>
@@ -49387,42 +49387,42 @@
       </c>
       <c r="B777" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C777" s="2" t="inlineStr">
         <is>
-          <t>BLV (multi-producer public warning)</t>
+          <t>Luna Food</t>
         </is>
       </c>
       <c r="D777" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Luisa e basilio</t>
         </is>
       </c>
       <c r="E777" s="2" t="inlineStr">
         <is>
-          <t>Various soft cheeses</t>
+          <t>Luisa e basilio ready meal</t>
         </is>
       </c>
       <c r="F777" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G777" s="2" t="inlineStr">
         <is>
-          <t>Public warning — Salmonella detected in various soft cheeses</t>
+          <t>Listeria detected in the manufacturing environment</t>
         </is>
       </c>
       <c r="H777" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I777" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J777" s="2" t="inlineStr">
@@ -49438,7 +49438,7 @@
       </c>
       <c r="M777" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-salmonellen-weichkaese.pdf.download.pdf/oW_Salmonellen%20in%20verschiedenen%20Weichk%C3%A4sen.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21942/Interne</t>
         </is>
       </c>
     </row>
@@ -49450,42 +49450,42 @@
       </c>
       <c r="B778" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C778" s="2" t="inlineStr">
         <is>
-          <t>Origin: Ireland | Notifying: Ireland</t>
+          <t>Luna Food</t>
         </is>
       </c>
       <c r="D778" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Luisa e basilio</t>
         </is>
       </c>
       <c r="E778" s="2" t="inlineStr">
         <is>
-          <t>Detection of Cronobacter in a batch of Infant Formula</t>
+          <t>Luisa e basilio ready meal</t>
         </is>
       </c>
       <c r="F778" s="2" t="inlineStr">
         <is>
-          <t>Cronobacter sakazakii</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G778" s="2" t="inlineStr">
         <is>
-          <t>Detection of Cronobacter in a batch of Infant Formula; risk: serious; category: milk and milk products</t>
+          <t>Listeria detected in the manufacturing environment</t>
         </is>
       </c>
       <c r="H778" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I778" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J778" s="2" t="inlineStr">
@@ -49494,14 +49494,14 @@
         </is>
       </c>
       <c r="K778" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L778" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M778" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836052</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21943/Interne</t>
         </is>
       </c>
     </row>
@@ -49513,42 +49513,42 @@
       </c>
       <c r="B779" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C779" s="2" t="inlineStr">
         <is>
-          <t>Origin: Netherlands | Notifying: Italy</t>
+          <t>BLV (multi-producer public warning)</t>
         </is>
       </c>
       <c r="D779" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E779" s="2" t="inlineStr">
         <is>
-          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp</t>
+          <t>Various soft cheeses</t>
         </is>
       </c>
       <c r="F779" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G779" s="2" t="inlineStr">
         <is>
-          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp; risk: potentially serious; category: crustaceans and products thereof</t>
+          <t>Public warning — Salmonella detected in various soft cheeses</t>
         </is>
       </c>
       <c r="H779" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I779" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J779" s="2" t="inlineStr">
@@ -49564,7 +49564,7 @@
       </c>
       <c r="M779" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835939</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-salmonellen-weichkaese.pdf.download.pdf/oW_Salmonellen%20in%20verschiedenen%20Weichk%C3%A4sen.pdf</t>
         </is>
       </c>
     </row>
@@ -49581,7 +49581,7 @@
       </c>
       <c r="C780" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: Ireland | Notifying: Ireland</t>
         </is>
       </c>
       <c r="D780" s="2" t="inlineStr">
@@ -49591,27 +49591,27 @@
       </c>
       <c r="E780" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkey</t>
+          <t>Detection of Cronobacter in a batch of Infant Formula</t>
         </is>
       </c>
       <c r="F780" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Cronobacter sakazakii</t>
         </is>
       </c>
       <c r="G780" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkey; risk: serious; category: fruits and vegetables</t>
+          <t>Detection of Cronobacter in a batch of Infant Formula; risk: serious; category: milk and milk products</t>
         </is>
       </c>
       <c r="H780" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I780" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J780" s="2" t="inlineStr">
@@ -49627,7 +49627,7 @@
       </c>
       <c r="M780" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835929</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836052</t>
         </is>
       </c>
     </row>
@@ -49644,7 +49644,7 @@
       </c>
       <c r="C781" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Greece</t>
+          <t>Origin: Netherlands | Notifying: Italy</t>
         </is>
       </c>
       <c r="D781" s="2" t="inlineStr">
@@ -49654,27 +49654,27 @@
       </c>
       <c r="E781" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye</t>
+          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp</t>
         </is>
       </c>
       <c r="F781" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G781" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
+          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp; risk: potentially serious; category: crustaceans and products thereof</t>
         </is>
       </c>
       <c r="H781" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I781" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="J781" s="2" t="inlineStr">
@@ -49683,14 +49683,14 @@
         </is>
       </c>
       <c r="K781" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L781" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M781" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835805</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835939</t>
         </is>
       </c>
     </row>
@@ -49707,7 +49707,7 @@
       </c>
       <c r="C782" s="2" t="inlineStr">
         <is>
-          <t>Origin: United States | Notifying: Italy</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D782" s="2" t="inlineStr">
@@ -49717,7 +49717,7 @@
       </c>
       <c r="E782" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in shelled Pistachios from USA via Turkey</t>
+          <t>Aflatoxins in dried figs from Turkey</t>
         </is>
       </c>
       <c r="F782" s="2" t="inlineStr">
@@ -49727,7 +49727,7 @@
       </c>
       <c r="G782" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in shelled Pistachios from USA via Turkey; risk: serious; category: fruits and vegetables</t>
+          <t>Aflatoxins in dried figs from Turkey; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H782" s="2" t="inlineStr">
@@ -49737,12 +49737,12 @@
       </c>
       <c r="I782" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J782" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K782" s="2" t="n">
@@ -49753,7 +49753,7 @@
       </c>
       <c r="M782" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835699</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835929</t>
         </is>
       </c>
     </row>
@@ -49765,42 +49765,42 @@
       </c>
       <c r="B783" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C783" s="2" t="inlineStr">
         <is>
-          <t>Luna Food</t>
+          <t>Origin: Türkiye | Notifying: Greece</t>
         </is>
       </c>
       <c r="D783" s="2" t="inlineStr">
         <is>
-          <t>Shakishaki</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E783" s="2" t="inlineStr">
         <is>
-          <t>Onigiri with avocado and wasabi (GTIN 3760373401084)</t>
+          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye</t>
         </is>
       </c>
       <c r="F783" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G783" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected in the manufacturing environment</t>
+          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H783" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I783" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J783" s="2" t="inlineStr">
@@ -49809,14 +49809,14 @@
         </is>
       </c>
       <c r="K783" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L783" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M783" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21962/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835805</t>
         </is>
       </c>
     </row>
@@ -49828,58 +49828,58 @@
       </c>
       <c r="B784" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C784" s="2" t="inlineStr">
         <is>
-          <t>Luna Food</t>
+          <t>Origin: United States | Notifying: Italy</t>
         </is>
       </c>
       <c r="D784" s="2" t="inlineStr">
         <is>
-          <t>Shakishaki</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E784" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Beef Teriyaki</t>
+          <t>Aflatoxins in shelled Pistachios from USA via Turkey</t>
         </is>
       </c>
       <c r="F784" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G784" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected in the manufacturing environment</t>
+          <t>Aflatoxins in shelled Pistachios from USA via Turkey; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H784" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I784" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J784" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K784" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L784" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M784" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21961/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835699</t>
         </is>
       </c>
     </row>
@@ -49906,7 +49906,7 @@
       </c>
       <c r="E785" s="2" t="inlineStr">
         <is>
-          <t>Onigiri du Moment</t>
+          <t>Onigiri with avocado and wasabi (GTIN 3760373401084)</t>
         </is>
       </c>
       <c r="F785" s="2" t="inlineStr">
@@ -49942,7 +49942,7 @@
       </c>
       <c r="M785" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21960/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21962/Interne</t>
         </is>
       </c>
     </row>
@@ -49969,7 +49969,7 @@
       </c>
       <c r="E786" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Chicken Yakitori</t>
+          <t>Onigiri Beef Teriyaki</t>
         </is>
       </c>
       <c r="F786" s="2" t="inlineStr">
@@ -50005,7 +50005,7 @@
       </c>
       <c r="M786" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21959/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21961/Interne</t>
         </is>
       </c>
     </row>
@@ -50032,7 +50032,7 @@
       </c>
       <c r="E787" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Salmon Cream Cheese</t>
+          <t>Onigiri du Moment</t>
         </is>
       </c>
       <c r="F787" s="2" t="inlineStr">
@@ -50068,7 +50068,7 @@
       </c>
       <c r="M787" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21958/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21960/Interne</t>
         </is>
       </c>
     </row>
@@ -50095,7 +50095,7 @@
       </c>
       <c r="E788" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Spicy Tuna Mayo</t>
+          <t>Onigiri Chicken Yakitori</t>
         </is>
       </c>
       <c r="F788" s="2" t="inlineStr">
@@ -50131,7 +50131,7 @@
       </c>
       <c r="M788" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21957/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21959/Interne</t>
         </is>
       </c>
     </row>
@@ -50158,7 +50158,7 @@
       </c>
       <c r="E789" s="2" t="inlineStr">
         <is>
-          <t>Cooked Salmon Poke</t>
+          <t>Onigiri Salmon Cream Cheese</t>
         </is>
       </c>
       <c r="F789" s="2" t="inlineStr">
@@ -50194,7 +50194,7 @@
       </c>
       <c r="M789" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21954/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21958/Interne</t>
         </is>
       </c>
     </row>
@@ -50221,7 +50221,7 @@
       </c>
       <c r="E790" s="2" t="inlineStr">
         <is>
-          <t>Onigiri (assorted variety)</t>
+          <t>Onigiri Spicy Tuna Mayo</t>
         </is>
       </c>
       <c r="F790" s="2" t="inlineStr">
@@ -50257,7 +50257,7 @@
       </c>
       <c r="M790" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21953/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21957/Interne</t>
         </is>
       </c>
     </row>
@@ -50284,7 +50284,7 @@
       </c>
       <c r="E791" s="2" t="inlineStr">
         <is>
-          <t>Onigiri (assorted variety)</t>
+          <t>Cooked Salmon Poke</t>
         </is>
       </c>
       <c r="F791" s="2" t="inlineStr">
@@ -50320,7 +50320,7 @@
       </c>
       <c r="M791" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21952/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21954/Interne</t>
         </is>
       </c>
     </row>
@@ -50347,7 +50347,7 @@
       </c>
       <c r="E792" s="2" t="inlineStr">
         <is>
-          <t>Onigiri du Moment</t>
+          <t>Onigiri (assorted variety)</t>
         </is>
       </c>
       <c r="F792" s="2" t="inlineStr">
@@ -50383,7 +50383,7 @@
       </c>
       <c r="M792" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21951/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21953/Interne</t>
         </is>
       </c>
     </row>
@@ -50405,12 +50405,12 @@
       </c>
       <c r="D793" s="2" t="inlineStr">
         <is>
-          <t>Foodles</t>
+          <t>Shakishaki</t>
         </is>
       </c>
       <c r="E793" s="2" t="inlineStr">
         <is>
-          <t>Cooked salmon poke</t>
+          <t>Onigiri (assorted variety)</t>
         </is>
       </c>
       <c r="F793" s="2" t="inlineStr">
@@ -50446,7 +50446,7 @@
       </c>
       <c r="M793" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21950/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21952/Interne</t>
         </is>
       </c>
     </row>
@@ -50468,12 +50468,12 @@
       </c>
       <c r="D794" s="2" t="inlineStr">
         <is>
-          <t>Foodles</t>
+          <t>Shakishaki</t>
         </is>
       </c>
       <c r="E794" s="2" t="inlineStr">
         <is>
-          <t>Foodles ready meal</t>
+          <t>Onigiri du Moment</t>
         </is>
       </c>
       <c r="F794" s="2" t="inlineStr">
@@ -50509,7 +50509,7 @@
       </c>
       <c r="M794" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21949/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21951/Interne</t>
         </is>
       </c>
     </row>
@@ -50526,17 +50526,17 @@
       </c>
       <c r="C795" s="2" t="inlineStr">
         <is>
-          <t>Bretzels Moricettes MFP Poulaillon</t>
+          <t>Luna Food</t>
         </is>
       </c>
       <c r="D795" s="2" t="inlineStr">
         <is>
-          <t>POULAILLON</t>
+          <t>Foodles</t>
         </is>
       </c>
       <c r="E795" s="2" t="inlineStr">
         <is>
-          <t>Duck Parmentier ready meal</t>
+          <t>Cooked salmon poke</t>
         </is>
       </c>
       <c r="F795" s="2" t="inlineStr">
@@ -50546,12 +50546,12 @@
       </c>
       <c r="G795" s="2" t="inlineStr">
         <is>
-          <t>Detection of Listeria monocytogenes</t>
+          <t>Listeria detected in the manufacturing environment</t>
         </is>
       </c>
       <c r="H795" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I795" s="2" t="inlineStr">
@@ -50572,7 +50572,7 @@
       </c>
       <c r="M795" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21948/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21950/Interne</t>
         </is>
       </c>
     </row>
@@ -50594,12 +50594,12 @@
       </c>
       <c r="D796" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio</t>
+          <t>Foodles</t>
         </is>
       </c>
       <c r="E796" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Foodles ready meal</t>
         </is>
       </c>
       <c r="F796" s="2" t="inlineStr">
@@ -50635,7 +50635,7 @@
       </c>
       <c r="M796" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21947/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21949/Interne</t>
         </is>
       </c>
     </row>
@@ -50652,27 +50652,27 @@
       </c>
       <c r="C797" s="2" t="inlineStr">
         <is>
-          <t>Fromagerie Beaude</t>
+          <t>Bretzels Moricettes MFP Poulaillon</t>
         </is>
       </c>
       <c r="D797" s="2" t="inlineStr">
         <is>
-          <t>La grisée chèvre</t>
+          <t>POULAILLON</t>
         </is>
       </c>
       <c r="E797" s="2" t="inlineStr">
         <is>
-          <t>Goat Raclette cheese (Lot 2604201C, best-before 2026-05-02 to 2026-05-10)</t>
+          <t>Duck Parmentier ready meal</t>
         </is>
       </c>
       <c r="F797" s="2" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing E. coli (STEC)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G797" s="2" t="inlineStr">
         <is>
-          <t>Microbiological risks — STEC</t>
+          <t>Detection of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H797" s="2" t="inlineStr">
@@ -50698,7 +50698,7 @@
       </c>
       <c r="M797" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21946/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21948/Interne</t>
         </is>
       </c>
     </row>
@@ -50761,7 +50761,7 @@
       </c>
       <c r="M798" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21945/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21947/Interne</t>
         </is>
       </c>
     </row>
@@ -50778,32 +50778,32 @@
       </c>
       <c r="C799" s="2" t="inlineStr">
         <is>
-          <t>Luna Food</t>
+          <t>Fromagerie Beaude</t>
         </is>
       </c>
       <c r="D799" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio</t>
+          <t>La grisée chèvre</t>
         </is>
       </c>
       <c r="E799" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Goat Raclette cheese (Lot 2604201C, best-before 2026-05-02 to 2026-05-10)</t>
         </is>
       </c>
       <c r="F799" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
         </is>
       </c>
       <c r="G799" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected in the manufacturing environment</t>
+          <t>Microbiological risks — STEC</t>
         </is>
       </c>
       <c r="H799" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I799" s="2" t="inlineStr">
@@ -50824,7 +50824,7 @@
       </c>
       <c r="M799" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21944/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21946/Interne</t>
         </is>
       </c>
     </row>
@@ -50887,7 +50887,7 @@
       </c>
       <c r="M800" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21943/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21945/Interne</t>
         </is>
       </c>
     </row>
@@ -50950,7 +50950,7 @@
       </c>
       <c r="M801" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21942/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21944/Interne</t>
         </is>
       </c>
     </row>
@@ -52358,12 +52358,12 @@
       </c>
       <c r="D824" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio</t>
+          <t>Unknown (LUNA FOOD multi-brand recall)</t>
         </is>
       </c>
       <c r="E824" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Ready meal / sandwich (SKU not extractable)</t>
         </is>
       </c>
       <c r="F824" s="2" t="inlineStr">
@@ -52399,7 +52399,7 @@
       </c>
       <c r="M824" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21935/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21919/Interne</t>
         </is>
       </c>
     </row>
@@ -52421,12 +52421,12 @@
       </c>
       <c r="D825" s="2" t="inlineStr">
         <is>
-          <t>French Kitchen</t>
+          <t>Unknown (LUNA FOOD multi-brand recall)</t>
         </is>
       </c>
       <c r="E825" s="2" t="inlineStr">
         <is>
-          <t>Sautéed Chicken, Thyme Potatoes, Mustard Sauce (GTIN 3760373401534)</t>
+          <t>Ready meal / sandwich (SKU not extractable)</t>
         </is>
       </c>
       <c r="F825" s="2" t="inlineStr">
@@ -52462,7 +52462,7 @@
       </c>
       <c r="M825" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21933/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21918/Interne</t>
         </is>
       </c>
     </row>
@@ -52484,12 +52484,12 @@
       </c>
       <c r="D826" s="2" t="inlineStr">
         <is>
-          <t>French Kitchen</t>
+          <t>Unknown (LUNA FOOD multi-brand recall)</t>
         </is>
       </c>
       <c r="E826" s="2" t="inlineStr">
         <is>
-          <t>French Kitchen ready meal</t>
+          <t>Ready meal / sandwich (SKU not extractable)</t>
         </is>
       </c>
       <c r="F826" s="2" t="inlineStr">
@@ -52525,7 +52525,7 @@
       </c>
       <c r="M826" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21932/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21921/Interne</t>
         </is>
       </c>
     </row>
@@ -52547,12 +52547,12 @@
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen</t>
+          <t>Unknown (LUNA FOOD multi-brand recall)</t>
         </is>
       </c>
       <c r="E827" s="2" t="inlineStr">
         <is>
-          <t>Beef Fried Rice (GTIN 3760373402203)</t>
+          <t>Ready meal / sandwich (SKU not extractable)</t>
         </is>
       </c>
       <c r="F827" s="2" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="M827" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21931/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21920/Interne</t>
         </is>
       </c>
     </row>
@@ -52610,12 +52610,12 @@
       </c>
       <c r="D828" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen</t>
+          <t>Luisa e basilio</t>
         </is>
       </c>
       <c r="E828" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen ready meal</t>
+          <t>Luisa e basilio ready meal</t>
         </is>
       </c>
       <c r="F828" s="2" t="inlineStr">
@@ -52651,7 +52651,7 @@
       </c>
       <c r="M828" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21930/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21935/Interne</t>
         </is>
       </c>
     </row>
@@ -52673,12 +52673,12 @@
       </c>
       <c r="D829" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen</t>
+          <t>French Kitchen</t>
         </is>
       </c>
       <c r="E829" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen ready meal</t>
+          <t>Sautéed Chicken, Thyme Potatoes, Mustard Sauce (GTIN 3760373401534)</t>
         </is>
       </c>
       <c r="F829" s="2" t="inlineStr">
@@ -52714,7 +52714,7 @@
       </c>
       <c r="M829" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21929/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21933/Interne</t>
         </is>
       </c>
     </row>
@@ -52736,12 +52736,12 @@
       </c>
       <c r="D830" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen</t>
+          <t>French Kitchen</t>
         </is>
       </c>
       <c r="E830" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen ready meal</t>
+          <t>French Kitchen ready meal</t>
         </is>
       </c>
       <c r="F830" s="2" t="inlineStr">
@@ -52777,7 +52777,7 @@
       </c>
       <c r="M830" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21928/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21932/Interne</t>
         </is>
       </c>
     </row>
@@ -52799,12 +52799,12 @@
       </c>
       <c r="D831" s="2" t="inlineStr">
         <is>
-          <t>Bim bang</t>
+          <t>Chinese Kitchen</t>
         </is>
       </c>
       <c r="E831" s="2" t="inlineStr">
         <is>
-          <t>Caramel Pork with White Rice (GTIN 3760373400858)</t>
+          <t>Beef Fried Rice (GTIN 3760373402203)</t>
         </is>
       </c>
       <c r="F831" s="2" t="inlineStr">
@@ -52840,7 +52840,7 @@
       </c>
       <c r="M831" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21927/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21931/Interne</t>
         </is>
       </c>
     </row>
@@ -52862,12 +52862,12 @@
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>Bim bang</t>
+          <t>Chinese Kitchen</t>
         </is>
       </c>
       <c r="E832" s="2" t="inlineStr">
         <is>
-          <t>Bim bang Asian-style ready meal / kimbap</t>
+          <t>Chinese Kitchen ready meal</t>
         </is>
       </c>
       <c r="F832" s="2" t="inlineStr">
@@ -52903,7 +52903,7 @@
       </c>
       <c r="M832" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21926/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21930/Interne</t>
         </is>
       </c>
     </row>
@@ -52925,12 +52925,12 @@
       </c>
       <c r="D833" s="2" t="inlineStr">
         <is>
-          <t>Bim bang</t>
+          <t>Chinese Kitchen</t>
         </is>
       </c>
       <c r="E833" s="2" t="inlineStr">
         <is>
-          <t>Bim bang Asian-style ready meal / kimbap</t>
+          <t>Chinese Kitchen ready meal</t>
         </is>
       </c>
       <c r="F833" s="2" t="inlineStr">
@@ -52966,7 +52966,7 @@
       </c>
       <c r="M833" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21925/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21929/Interne</t>
         </is>
       </c>
     </row>
@@ -52988,12 +52988,12 @@
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>Bim bang</t>
+          <t>Chinese Kitchen</t>
         </is>
       </c>
       <c r="E834" s="2" t="inlineStr">
         <is>
-          <t>Bim bang Asian-style ready meal / kimbap</t>
+          <t>Chinese Kitchen ready meal</t>
         </is>
       </c>
       <c r="F834" s="2" t="inlineStr">
@@ -53029,7 +53029,7 @@
       </c>
       <c r="M834" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21924/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21928/Interne</t>
         </is>
       </c>
     </row>
@@ -53051,12 +53051,12 @@
       </c>
       <c r="D835" s="2" t="inlineStr">
         <is>
-          <t>The bread Bandits</t>
+          <t>Bim bang</t>
         </is>
       </c>
       <c r="E835" s="2" t="inlineStr">
         <is>
-          <t>Salmon Yuzu Duo Baguette (GTIN 3760373403781)</t>
+          <t>Caramel Pork with White Rice (GTIN 3760373400858)</t>
         </is>
       </c>
       <c r="F835" s="2" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="M835" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21923/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21927/Interne</t>
         </is>
       </c>
     </row>
@@ -53114,12 +53114,12 @@
       </c>
       <c r="D836" s="2" t="inlineStr">
         <is>
-          <t>The bread Bandits</t>
+          <t>Bim bang</t>
         </is>
       </c>
       <c r="E836" s="2" t="inlineStr">
         <is>
-          <t>The bread Bandits sandwich/snack</t>
+          <t>Bim bang Asian-style ready meal / kimbap</t>
         </is>
       </c>
       <c r="F836" s="2" t="inlineStr">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="M836" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21922/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21926/Interne</t>
         </is>
       </c>
     </row>
@@ -53177,12 +53177,12 @@
       </c>
       <c r="D837" s="2" t="inlineStr">
         <is>
-          <t>Unknown (LUNA FOOD multi-brand recall)</t>
+          <t>Bim bang</t>
         </is>
       </c>
       <c r="E837" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Bim bang Asian-style ready meal / kimbap</t>
         </is>
       </c>
       <c r="F837" s="2" t="inlineStr">
@@ -53218,7 +53218,7 @@
       </c>
       <c r="M837" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21921/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21925/Interne</t>
         </is>
       </c>
     </row>
@@ -53240,12 +53240,12 @@
       </c>
       <c r="D838" s="2" t="inlineStr">
         <is>
-          <t>Unknown (LUNA FOOD multi-brand recall)</t>
+          <t>Bim bang</t>
         </is>
       </c>
       <c r="E838" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Bim bang Asian-style ready meal / kimbap</t>
         </is>
       </c>
       <c r="F838" s="2" t="inlineStr">
@@ -53281,7 +53281,7 @@
       </c>
       <c r="M838" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21920/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21924/Interne</t>
         </is>
       </c>
     </row>
@@ -53303,12 +53303,12 @@
       </c>
       <c r="D839" s="2" t="inlineStr">
         <is>
-          <t>Unknown (LUNA FOOD multi-brand recall)</t>
+          <t>The bread Bandits</t>
         </is>
       </c>
       <c r="E839" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Salmon Yuzu Duo Baguette (GTIN 3760373403781)</t>
         </is>
       </c>
       <c r="F839" s="2" t="inlineStr">
@@ -53344,7 +53344,7 @@
       </c>
       <c r="M839" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21919/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21923/Interne</t>
         </is>
       </c>
     </row>
@@ -53366,12 +53366,12 @@
       </c>
       <c r="D840" s="2" t="inlineStr">
         <is>
-          <t>Unknown (LUNA FOOD multi-brand recall)</t>
+          <t>The bread Bandits</t>
         </is>
       </c>
       <c r="E840" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>The bread Bandits sandwich/snack</t>
         </is>
       </c>
       <c r="F840" s="2" t="inlineStr">
@@ -53407,7 +53407,7 @@
       </c>
       <c r="M840" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21918/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21922/Interne</t>
         </is>
       </c>
     </row>
@@ -65541,7 +65541,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-03 07:52 UTC</t>
+          <t>Generated: 2026-07-03 13:34 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -42142,12 +42142,12 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>Orienta Foods GmbH</t>
+          <t>Origin: Argentina | Notifying: Greece</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
@@ -42157,7 +42157,7 @@
       </c>
       <c r="E662" s="2" t="inlineStr">
         <is>
-          <t>Rotes Chilipulver der Marke Rino</t>
+          <t>Aflatoxins in  groundnut kernels  from Argentina</t>
         </is>
       </c>
       <c r="F662" s="2" t="inlineStr">
@@ -42167,33 +42167,33 @@
       </c>
       <c r="G662" s="2" t="inlineStr">
         <is>
-          <t>Die Orienta Foods GmbH ruft Rotes Chilipulver der Marke Rino (250g und 500g Packungen, MHD E2028/1/1, Charge P2026/1/2) zurück. Bei einer Lebensmittelkontrolle wurden Aflatoxin-Werte über dem Grenzwert nachgewiesen.</t>
+          <t>Aflatoxins in  groundnut kernels  from Argentina; risk: serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H662" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I662" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J662" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K662" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L662" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M662" s="2" t="inlineStr">
         <is>
-          <t>https://www.produktwarnung.eu/2026/04/24/rueckruf-aflatoxin-orienta-foods-ruft-rotes-chilipulver-der-marke-rino-zurueck/37845</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839676</t>
         </is>
       </c>
     </row>
@@ -42210,27 +42210,27 @@
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>REWE Dortmund eG</t>
+          <t>Orienta Foods GmbH</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>REWE Dortmund Hausmarke</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E663" s="2" t="inlineStr">
         <is>
-          <t>Schinken-Zwiebelmettwurst — 4 varieties (200 g x2, Kugeln 90 g, Ring 850 g), use-by 2026-04-28</t>
+          <t>Rotes Chilipulver der Marke Rino</t>
         </is>
       </c>
       <c r="F663" s="2" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing E. coli (STEC)</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G663" s="2" t="inlineStr">
         <is>
-          <t>STEC detected in a sample</t>
+          <t>Die Orienta Foods GmbH ruft Rotes Chilipulver der Marke Rino (250g und 500g Packungen, MHD E2028/1/1, Charge P2026/1/2) zurück. Bei einer Lebensmittelkontrolle wurden Aflatoxin-Werte über dem Grenzwert nachgewiesen.</t>
         </is>
       </c>
       <c r="H663" s="2" t="inlineStr">
@@ -42249,14 +42249,14 @@
         </is>
       </c>
       <c r="K663" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L663" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M663" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260424_27_NW_Mettwurst/260424_27_NW_Mettwurst_Meldung.html</t>
+          <t>https://www.produktwarnung.eu/2026/04/24/rueckruf-aflatoxin-orienta-foods-ruft-rotes-chilipulver-der-marke-rino-zurueck/37845</t>
         </is>
       </c>
     </row>
@@ -42268,32 +42268,32 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>Gourmet Çelebi</t>
+          <t>REWE Dortmund eG</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>Gourmet Çelebi</t>
+          <t>REWE Dortmund Hausmarke</t>
         </is>
       </c>
       <c r="E664" s="2" t="inlineStr">
         <is>
-          <t>Pistachio cream 200 g (Lot 2162, best-before 2026-12-23)</t>
+          <t>Schinken-Zwiebelmettwurst — 4 varieties (200 g x2, Kugeln 90 g, Ring 850 g), use-by 2026-04-28</t>
         </is>
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
         </is>
       </c>
       <c r="G664" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in pistachio cream — health risk cannot be excluded</t>
+          <t>STEC detected in a sample</t>
         </is>
       </c>
       <c r="H664" s="2" t="inlineStr">
@@ -42303,7 +42303,7 @@
       </c>
       <c r="I664" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J664" s="2" t="inlineStr">
@@ -42319,7 +42319,7 @@
       </c>
       <c r="M664" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-salmonellen-pistaziencreme-gourmet-celebi.pdf.download.pdf/DE_Oeffentliche%20Warnung%20Salmonellen%20in%20Pistaziencreme%20DE.pdf</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260424_27_NW_Mettwurst/260424_27_NW_Mettwurst_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -42331,58 +42331,58 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>Origin: Bolivia | Notifying: Netherlands</t>
+          <t>Gourmet Çelebi</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gourmet Çelebi</t>
         </is>
       </c>
       <c r="E665" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin B1 in Amazon nuts from Bolivia</t>
+          <t>Pistachio cream 200 g (Lot 2162, best-before 2026-12-23)</t>
         </is>
       </c>
       <c r="F665" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G665" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin B1 in Amazon nuts from Bolivia; risk: serious; category: nuts, nut products and seeds</t>
+          <t>Salmonella detected in pistachio cream — health risk cannot be excluded</t>
         </is>
       </c>
       <c r="H665" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I665" s="2" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J665" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K665" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L665" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M665" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/840023</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-salmonellen-pistaziencreme-gourmet-celebi.pdf.download.pdf/DE_Oeffentliche%20Warnung%20Salmonellen%20in%20Pistaziencreme%20DE.pdf</t>
         </is>
       </c>
     </row>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>Origin: Syria | Notifying: Germany</t>
+          <t>Origin: Bolivia | Notifying: Netherlands</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -42409,7 +42409,7 @@
       </c>
       <c r="E666" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in red chili powder from Syria</t>
+          <t>Aflatoxin B1 in Amazon nuts from Bolivia</t>
         </is>
       </c>
       <c r="F666" s="2" t="inlineStr">
@@ -42419,7 +42419,7 @@
       </c>
       <c r="G666" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in red chili powder from Syria; risk: serious; category: herbs and spices</t>
+          <t>Aflatoxin B1 in Amazon nuts from Bolivia; risk: serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H666" s="2" t="inlineStr">
@@ -42429,12 +42429,12 @@
       </c>
       <c r="I666" s="2" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="J666" s="2" t="inlineStr">
         <is>
-          <t>Middle East</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K666" s="2" t="n">
@@ -42445,7 +42445,7 @@
       </c>
       <c r="M666" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839804</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/840023</t>
         </is>
       </c>
     </row>
@@ -42462,7 +42462,7 @@
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>Origin: Argentina | Notifying: Greece</t>
+          <t>Origin: Syria | Notifying: Germany</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
@@ -42472,7 +42472,7 @@
       </c>
       <c r="E667" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in  groundnut kernels  from Argentina</t>
+          <t>Aflatoxins in red chili powder from Syria</t>
         </is>
       </c>
       <c r="F667" s="2" t="inlineStr">
@@ -42482,22 +42482,22 @@
       </c>
       <c r="G667" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in  groundnut kernels  from Argentina; risk: serious; category: nuts, nut products and seeds</t>
+          <t>Aflatoxins in red chili powder from Syria; risk: serious; category: herbs and spices</t>
         </is>
       </c>
       <c r="H667" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I667" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="J667" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="K667" s="2" t="n">
@@ -42508,7 +42508,7 @@
       </c>
       <c r="M667" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839676</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839804</t>
         </is>
       </c>
     </row>
@@ -43276,42 +43276,42 @@
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>Star Impex</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>Casabor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E680" s="2" t="inlineStr">
         <is>
-          <t>Blue Swimming Crab Cut U/10 12x1, China origin (Casabor brand crab meat)</t>
+          <t>Aflatoxins in roasted and salted pistachios from Turkey</t>
         </is>
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>PFOA / PFAS</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G680" s="2" t="inlineStr">
         <is>
-          <t>PFOA (perfluorooctanoic acid) levels above the regulatory limit detected in lab tests</t>
+          <t>Aflatoxins in roasted and salted pistachios from Turkey; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H680" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I680" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J680" s="2" t="inlineStr">
@@ -43320,14 +43320,14 @@
         </is>
       </c>
       <c r="K680" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L680" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M680" s="2" t="inlineStr">
         <is>
-          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-pfoa-star-impex-ruft-blaukrabben-zurueck/37833</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839296</t>
         </is>
       </c>
     </row>
@@ -43339,12 +43339,12 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>Asia Express Food (Green Box Limited)</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
@@ -43354,27 +43354,27 @@
       </c>
       <c r="E681" s="2" t="inlineStr">
         <is>
-          <t>Enoki-Pilzen</t>
+          <t>Bacillus cereus in tomatoes from Türkiye</t>
         </is>
       </c>
       <c r="F681" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Bacillus cereus</t>
         </is>
       </c>
       <c r="G681" s="2" t="inlineStr">
         <is>
-          <t>Der Großhändler Asia Express Food ruft Enoki-Pilze der Marke Green Box Limited zurück. Im Rahmen einer Kontrolle wurde das Bakterium Listeria monocytogenes nachgewiesen, und vom Verzehr wird dringend abgeraten.</t>
+          <t>Bacillus cereus in tomatoes from Türkiye; risk: potential risk; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H681" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I681" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J681" s="2" t="inlineStr">
@@ -43383,14 +43383,14 @@
         </is>
       </c>
       <c r="K681" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L681" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M681" s="2" t="inlineStr">
         <is>
-          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-listerien-in-enoki-pilzen-der-marke-green-box-limited/37823</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838854</t>
         </is>
       </c>
     </row>
@@ -43407,27 +43407,27 @@
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>REWE Dortmund</t>
+          <t>Star Impex</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Casabor</t>
         </is>
       </c>
       <c r="E682" s="2" t="inlineStr">
         <is>
-          <t>Schinken-Zwiebelmettwurst</t>
+          <t>Blue Swimming Crab Cut U/10 12x1, China origin (Casabor brand crab meat)</t>
         </is>
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing E. coli (STEC)</t>
+          <t>PFOA / PFAS</t>
         </is>
       </c>
       <c r="G682" s="2" t="inlineStr">
         <is>
-          <t>Die REWE Dortmund ruft vier verschiedene Schinken-Zwiebelmettwurst Artikel zurück. In einer einzelnen Probe wurden Shigatoxin-bildende Escherichia coli (STEC) nachgewiesen, weshalb vom Verzehr dringend abgeraten wird.</t>
+          <t>PFOA (perfluorooctanoic acid) levels above the regulatory limit detected in lab tests</t>
         </is>
       </c>
       <c r="H682" s="2" t="inlineStr">
@@ -43446,14 +43446,14 @@
         </is>
       </c>
       <c r="K682" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L682" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M682" s="2" t="inlineStr">
         <is>
-          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-ecoli-rewe-dortmund-ruft-schinken-zwiebelmettwurst-zurueck/37840</t>
+          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-pfoa-star-impex-ruft-blaukrabben-zurueck/37833</t>
         </is>
       </c>
     </row>
@@ -43470,27 +43470,27 @@
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>Orienta Foods GmbH</t>
+          <t>Asia Express Food (Green Box Limited)</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>Rino</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E683" s="2" t="inlineStr">
         <is>
-          <t>Red chili powder 250 g and 500 g (best-before E2028/1/1, lot P2026/1/2)</t>
+          <t>Enoki-Pilzen</t>
         </is>
       </c>
       <c r="F683" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G683" s="2" t="inlineStr">
         <is>
-          <t>Health-hazardous aflatoxins detected during food inspection</t>
+          <t>Der Großhändler Asia Express Food ruft Enoki-Pilze der Marke Green Box Limited zurück. Im Rahmen einer Kontrolle wurde das Bakterium Listeria monocytogenes nachgewiesen, und vom Verzehr wird dringend abgeraten.</t>
         </is>
       </c>
       <c r="H683" s="2" t="inlineStr">
@@ -43509,14 +43509,14 @@
         </is>
       </c>
       <c r="K683" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L683" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M683" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260423_24_ST_Rotes_Chilipulver/260423_ST_Rotes_Chilipulver_Meldung.html</t>
+          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-listerien-in-enoki-pilzen-der-marke-green-box-limited/37823</t>
         </is>
       </c>
     </row>
@@ -43528,12 +43528,12 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: France</t>
+          <t>REWE Dortmund</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
@@ -43543,27 +43543,27 @@
       </c>
       <c r="E684" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkiye</t>
+          <t>Schinken-Zwiebelmettwurst</t>
         </is>
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Shiga toxin-producing E. coli (STEC)</t>
         </is>
       </c>
       <c r="G684" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkiye; risk: serious; category: fruits and vegetables</t>
+          <t>Die REWE Dortmund ruft vier verschiedene Schinken-Zwiebelmettwurst Artikel zurück. In einer einzelnen Probe wurden Shigatoxin-bildende Escherichia coli (STEC) nachgewiesen, weshalb vom Verzehr dringend abgeraten wird.</t>
         </is>
       </c>
       <c r="H684" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I684" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J684" s="2" t="inlineStr">
@@ -43572,14 +43572,14 @@
         </is>
       </c>
       <c r="K684" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L684" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M684" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839681</t>
+          <t>https://www.produktwarnung.eu/2026/04/23/rueckruf-ecoli-rewe-dortmund-ruft-schinken-zwiebelmettwurst-zurueck/37840</t>
         </is>
       </c>
     </row>
@@ -43591,58 +43591,58 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>Origin: Brazil | Notifying: Lithuania</t>
+          <t>Orienta Foods GmbH</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rino</t>
         </is>
       </c>
       <c r="E685" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in frozen chicken breast fillets from Brazil</t>
+          <t>Red chili powder 250 g and 500 g (best-before E2028/1/1, lot P2026/1/2)</t>
         </is>
       </c>
       <c r="F685" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G685" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in frozen chicken breast fillets from Brazil; risk: not serious; category: poultry meat and poultry meat products</t>
+          <t>Health-hazardous aflatoxins detected during food inspection</t>
         </is>
       </c>
       <c r="H685" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I685" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J685" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K685" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L685" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M685" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839649</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260423_24_ST_Rotes_Chilipulver/260423_ST_Rotes_Chilipulver_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -43659,7 +43659,7 @@
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>Origin: Vietnam | Notifying: Germany</t>
+          <t>Origin: Türkiye | Notifying: France</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
@@ -43669,7 +43669,7 @@
       </c>
       <c r="E686" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands</t>
+          <t>Aflatoxins in dried figs from Turkiye</t>
         </is>
       </c>
       <c r="F686" s="2" t="inlineStr">
@@ -43679,22 +43679,22 @@
       </c>
       <c r="G686" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands; risk: serious; category: fruits and vegetables</t>
+          <t>Aflatoxins in dried figs from Turkiye; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H686" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I686" s="2" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J686" s="2" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K686" s="2" t="n">
@@ -43705,7 +43705,7 @@
       </c>
       <c r="M686" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839480</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839681</t>
         </is>
       </c>
     </row>
@@ -43722,7 +43722,7 @@
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>Origin: United States | Notifying: Italy</t>
+          <t>Origin: Brazil | Notifying: Lithuania</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -43732,32 +43732,32 @@
       </c>
       <c r="E687" s="2" t="inlineStr">
         <is>
-          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin</t>
+          <t>Salmonella detected in frozen chicken breast fillets from Brazil</t>
         </is>
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G687" s="2" t="inlineStr">
         <is>
-          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin; risk: serious; category: nuts, nut products and seeds</t>
+          <t>Salmonella detected in frozen chicken breast fillets from Brazil; risk: not serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H687" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I687" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J687" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K687" s="2" t="n">
@@ -43768,7 +43768,7 @@
       </c>
       <c r="M687" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839423</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839649</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: Vietnam | Notifying: Germany</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -43795,7 +43795,7 @@
       </c>
       <c r="E688" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in roasted and salted pistachios from Turkey</t>
+          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands</t>
         </is>
       </c>
       <c r="F688" s="2" t="inlineStr">
@@ -43805,22 +43805,22 @@
       </c>
       <c r="G688" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in roasted and salted pistachios from Turkey; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Aflatoxins in peanuts from Vietnam, via the Netherlands; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H688" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I688" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="J688" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="K688" s="2" t="n">
@@ -43831,7 +43831,7 @@
       </c>
       <c r="M688" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839296</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839480</t>
         </is>
       </c>
     </row>
@@ -43848,7 +43848,7 @@
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: United States | Notifying: Italy</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -43858,32 +43858,32 @@
       </c>
       <c r="E689" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus in tomatoes from Türkiye</t>
+          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin</t>
         </is>
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G689" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus in tomatoes from Türkiye; risk: potential risk; category: fruits and vegetables</t>
+          <t>AFLATOSSINE IN PISTACCHI SGUSCIATI/aflatoxins in shelled pistachios from Türkiye, US origin; risk: serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H689" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I689" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J689" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K689" s="2" t="n">
@@ -43894,7 +43894,7 @@
       </c>
       <c r="M689" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838854</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/839423</t>
         </is>
       </c>
     </row>
@@ -47938,12 +47938,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>Gomez Shellfish, LLC (WA-1724-SS)</t>
+          <t>Origin: Georgia | Notifying: Germany</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -47953,43 +47953,43 @@
       </c>
       <c r="E754" s="2" t="inlineStr">
         <is>
-          <t>Recalled shellfish — all species of shellstock (oysters, clams) harvested 2026-03-22 through 2026-04-09 from a portion of Hammersley Inlet, WA. Distributed to restaurants and retailers in CA, OR, TX, WA — possibly further distributed.</t>
+          <t>Aflatoxins in hazelnut flour from Georgia</t>
         </is>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G754" s="2" t="inlineStr">
         <is>
-          <t>Potential norovirus contamination — norovirus-like illnesses associated with raw oyster consumption; recall initiated by Washington State Department of Health 2026-04-10; FDA safety alert published 2026-04-17 advising no eat/serve/sell</t>
+          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
         </is>
       </c>
       <c r="H754" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I754" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="J754" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K754" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L754" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M754" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/food/alerts-advisories-safety-information/fda-advises-restaurants-and-retailers-not-serve-or-sell-and-consumers-not-eat-recalled-shellfish</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838360</t>
         </is>
       </c>
     </row>
@@ -48001,58 +48001,58 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>Rossmann</t>
+          <t>Origin: Chile | Notifying: Sweden</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
         <is>
-          <t>Foodloose</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E755" s="2" t="inlineStr">
         <is>
-          <t>White Delights-Pistazie</t>
+          <t>Lack of guarantee concerning salmonella in pork</t>
         </is>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
-          <t>Physical/foreign-body contamination</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G755" s="2" t="inlineStr">
         <is>
-          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
+          <t>Lack of guarantee concerning salmonella in pork; risk: potentially serious; category: meat and meat products (other than poultry)</t>
         </is>
       </c>
       <c r="H755" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I755" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J755" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K755" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L755" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M755" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-rossmann-foodloose.pdf.download.pdf/R%C3%BCckruf%20Aushang_Foodloose_16.04.2026_aktualisiert.pdf</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838294</t>
         </is>
       </c>
     </row>
@@ -48064,32 +48064,32 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>Phag GmbH</t>
+          <t>Gomez Shellfish, LLC (WA-1724-SS)</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
         <is>
-          <t>Foodloose</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E756" s="2" t="inlineStr">
         <is>
-          <t>White Delights-Pistazie</t>
+          <t>Recalled shellfish — all species of shellstock (oysters, clams) harvested 2026-03-22 through 2026-04-09 from a portion of Hammersley Inlet, WA. Distributed to restaurants and retailers in CA, OR, TX, WA — possibly further distributed.</t>
         </is>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
-          <t>Physical/foreign-body contamination</t>
+          <t>Norovirus</t>
         </is>
       </c>
       <c r="G756" s="2" t="inlineStr">
         <is>
-          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
+          <t>Potential norovirus contamination — norovirus-like illnesses associated with raw oyster consumption; recall initiated by Washington State Department of Health 2026-04-10; FDA safety alert published 2026-04-17 advising no eat/serve/sell</t>
         </is>
       </c>
       <c r="H756" s="2" t="inlineStr">
@@ -48099,23 +48099,23 @@
       </c>
       <c r="I756" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J756" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K756" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L756" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M756" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-phag-gmbh-foodloose.pdf.download.pdf/Marktaushang%20R%C3%BCckruf%20(erweitert).pdf</t>
+          <t>https://www.fda.gov/food/alerts-advisories-safety-information/fda-advises-restaurants-and-retailers-not-serve-or-sell-and-consumers-not-eat-recalled-shellfish</t>
         </is>
       </c>
     </row>
@@ -48127,42 +48127,42 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>Origin: Slovakia | Notifying: France</t>
+          <t>Rossmann</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Foodloose</t>
         </is>
       </c>
       <c r="E757" s="2" t="inlineStr">
         <is>
-          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken</t>
+          <t>White Delights-Pistazie</t>
         </is>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Physical/foreign-body contamination</t>
         </is>
       </c>
       <c r="G757" s="2" t="inlineStr">
         <is>
-          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken; risk: serious; category: poultry meat and poultry meat products</t>
+          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
         </is>
       </c>
       <c r="H757" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I757" s="2" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J757" s="2" t="inlineStr">
@@ -48171,14 +48171,14 @@
         </is>
       </c>
       <c r="K757" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L757" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M757" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838436</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-rossmann-foodloose.pdf.download.pdf/R%C3%BCckruf%20Aushang_Foodloose_16.04.2026_aktualisiert.pdf</t>
         </is>
       </c>
     </row>
@@ -48190,58 +48190,58 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>Origin: Georgia | Notifying: Germany</t>
+          <t>Phag GmbH</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Foodloose</t>
         </is>
       </c>
       <c r="E758" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia</t>
+          <t>White Delights-Pistazie</t>
         </is>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Physical/foreign-body contamination</t>
         </is>
       </c>
       <c r="G758" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in hazelnut flour from Georgia; risk: potentially serious; category: nuts, nut products and seeds</t>
+          <t>Recall over foreign bodies posing injury risk; an additional batch is also affected</t>
         </is>
       </c>
       <c r="H758" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I758" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J758" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K758" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L758" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M758" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838360</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/rueckrufe/rr-phag-gmbh-foodloose.pdf.download.pdf/Marktaushang%20R%C3%BCckruf%20(erweitert).pdf</t>
         </is>
       </c>
     </row>
@@ -48258,7 +48258,7 @@
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>Origin: Chile | Notifying: Sweden</t>
+          <t>Origin: Slovakia | Notifying: France</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -48268,7 +48268,7 @@
       </c>
       <c r="E759" s="2" t="inlineStr">
         <is>
-          <t>Lack of guarantee concerning salmonella in pork</t>
+          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken</t>
         </is>
       </c>
       <c r="F759" s="2" t="inlineStr">
@@ -48278,22 +48278,22 @@
       </c>
       <c r="G759" s="2" t="inlineStr">
         <is>
-          <t>Lack of guarantee concerning salmonella in pork; risk: potentially serious; category: meat and meat products (other than poultry)</t>
+          <t>Detection of Salmonella Enteritidis in frozen sautéed chicken; risk: serious; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H759" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I759" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="J759" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K759" s="2" t="n">
@@ -48304,7 +48304,7 @@
       </c>
       <c r="M759" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838294</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/838436</t>
         </is>
       </c>
     </row>
@@ -52285,22 +52285,22 @@
       </c>
       <c r="B823" s="2" t="inlineStr">
         <is>
-          <t>MAPAQ QC</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C823" s="2" t="inlineStr">
         <is>
-          <t>chocoStyle 440</t>
+          <t>Sultan Fine Foods</t>
         </is>
       </c>
       <c r="D823" s="2" t="inlineStr">
         <is>
-          <t>chocoStyle 440</t>
+          <t>Sultan Fine Foods</t>
         </is>
       </c>
       <c r="E823" s="2" t="inlineStr">
         <is>
-          <t>Pistachio chocolate bars and pistachio chocolate bites</t>
+          <t>Pistachio Kernel, 10 kg (Lot TME20250825PK, best-before AUG 2027)</t>
         </is>
       </c>
       <c r="F823" s="2" t="inlineStr">
@@ -52310,12 +52310,12 @@
       </c>
       <c r="G823" s="2" t="inlineStr">
         <is>
-          <t>Possible Salmonella contamination — linked to national pistachio outbreak investigation</t>
+          <t>Salmonella contamination — precautionary recall (linked to ongoing Iranian pistachio outbreak investigation; no illnesses tied to this specific Sultan product per CFIA page)</t>
         </is>
       </c>
       <c r="H823" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I823" s="2" t="inlineStr">
@@ -52336,7 +52336,7 @@
       </c>
       <c r="M823" s="2" t="inlineStr">
         <is>
-          <t>https://www.quebec.ca/nouvelles/actualites/details/mise-en-garde-a-la-population-presence-possible-de-salmonelle-dans-les-barres-de-chocolat-aux-pistaches-et-les-bouchees-de-chocolat-aux-pistaches-preparees-et-vendues-par-lentreprise-chocostyle-440-69727</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/pistachio-kernel-recalled-due-salmonella-0</t>
         </is>
       </c>
     </row>
@@ -52348,58 +52348,58 @@
       </c>
       <c r="B824" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C824" s="2" t="inlineStr">
         <is>
-          <t>foodloose</t>
+          <t>Fresh Start Foods</t>
         </is>
       </c>
       <c r="D824" s="2" t="inlineStr">
         <is>
-          <t>foodloose</t>
+          <t>Fresh Start Foods</t>
         </is>
       </c>
       <c r="E824" s="2" t="inlineStr">
         <is>
-          <t>Bio-Dattel-Kugeln White Delight Pistazie (best-before 2026-10-04, batch J49B0)</t>
+          <t>Salads (BC)</t>
         </is>
       </c>
       <c r="F824" s="2" t="inlineStr">
         <is>
-          <t>Physical/foreign-body contamination</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G824" s="2" t="inlineStr">
         <is>
-          <t>Foreign-body contamination posing injury risk cannot be excluded in individual packages</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H824" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I824" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J824" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K824" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L824" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M824" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_12_HH_Suessware_Pistazie/260410_12_HH_Suessware_Pistazie_Meldung.html</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/fresh-start-foods-brand-salads-recalled-due-listeria-monocytogenes</t>
         </is>
       </c>
     </row>
@@ -52411,22 +52411,22 @@
       </c>
       <c r="B825" s="2" t="inlineStr">
         <is>
-          <t>BVL (DE)</t>
+          <t>MAPAQ QC</t>
         </is>
       </c>
       <c r="C825" s="2" t="inlineStr">
         <is>
-          <t>Sächsische und Dresdner Back- und Süßwaren GmbH</t>
+          <t>chocoStyle 440</t>
         </is>
       </c>
       <c r="D825" s="2" t="inlineStr">
         <is>
-          <t>Nudossi</t>
+          <t>chocoStyle 440</t>
         </is>
       </c>
       <c r="E825" s="2" t="inlineStr">
         <is>
-          <t>Nudossi Hazelnut-Nougat-Crème, 300 g jar (specific batches affected)</t>
+          <t>Pistachio chocolate bars and pistachio chocolate bites</t>
         </is>
       </c>
       <c r="F825" s="2" t="inlineStr">
@@ -52436,22 +52436,22 @@
       </c>
       <c r="G825" s="2" t="inlineStr">
         <is>
-          <t>Positive Salmonella test result in specific batches</t>
+          <t>Possible Salmonella contamination — linked to national pistachio outbreak investigation</t>
         </is>
       </c>
       <c r="H825" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I825" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J825" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K825" s="2" t="n">
@@ -52462,7 +52462,7 @@
       </c>
       <c r="M825" s="2" t="inlineStr">
         <is>
-          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_10_SN_Nuss-Nougat-Creme/260410_10_SN_Nuss-Nougat-Creme_Meldung.html</t>
+          <t>https://www.quebec.ca/nouvelles/actualites/details/mise-en-garde-a-la-population-presence-possible-de-salmonelle-dans-les-barres-de-chocolat-aux-pistaches-et-les-bouchees-de-chocolat-aux-pistaches-preparees-et-vendues-par-lentreprise-chocostyle-440-69727</t>
         </is>
       </c>
     </row>
@@ -52474,47 +52474,47 @@
       </c>
       <c r="B826" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C826" s="2" t="inlineStr">
         <is>
-          <t>Origin: Uzbekistan | Notifying: Denmark</t>
+          <t>foodloose</t>
         </is>
       </c>
       <c r="D826" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>foodloose</t>
         </is>
       </c>
       <c r="E826" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany</t>
+          <t>Bio-Dattel-Kugeln White Delight Pistazie (best-before 2026-10-04, batch J49B0)</t>
         </is>
       </c>
       <c r="F826" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin</t>
+          <t>Physical/foreign-body contamination</t>
         </is>
       </c>
       <c r="G826" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany; risk: serious; category: fruits and vegetables</t>
+          <t>Foreign-body contamination posing injury risk cannot be excluded in individual packages</t>
         </is>
       </c>
       <c r="H826" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I826" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J826" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K826" s="2" t="n">
@@ -52525,7 +52525,7 @@
       </c>
       <c r="M826" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836889</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_12_HH_Suessware_Pistazie/260410_12_HH_Suessware_Pistazie_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -52537,42 +52537,42 @@
       </c>
       <c r="B827" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BVL (DE)</t>
         </is>
       </c>
       <c r="C827" s="2" t="inlineStr">
         <is>
-          <t>Origin: Netherlands | Notifying: Belgium</t>
+          <t>Sächsische und Dresdner Back- und Süßwaren GmbH</t>
         </is>
       </c>
       <c r="D827" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nudossi</t>
         </is>
       </c>
       <c r="E827" s="2" t="inlineStr">
         <is>
-          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands</t>
+          <t>Nudossi Hazelnut-Nougat-Crème, 300 g jar (specific batches affected)</t>
         </is>
       </c>
       <c r="F827" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G827" s="2" t="inlineStr">
         <is>
-          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands; risk: potentially serious; category: bivalve molluscs and products thereof</t>
+          <t>Positive Salmonella test result in specific batches</t>
         </is>
       </c>
       <c r="H827" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I827" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="J827" s="2" t="inlineStr">
@@ -52581,14 +52581,14 @@
         </is>
       </c>
       <c r="K827" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L827" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M827" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836765</t>
+          <t>https://www.lebensmittelwarnung.de/___lebensmittelwarnung.de/Meldungen/2026/04_April/260410_10_SN_Nuss-Nougat-Creme/260410_10_SN_Nuss-Nougat-Creme_Meldung.html</t>
         </is>
       </c>
     </row>
@@ -52605,7 +52605,7 @@
       </c>
       <c r="C828" s="2" t="inlineStr">
         <is>
-          <t>Origin: Brazil | Notifying: Croatia</t>
+          <t>Origin: Uzbekistan | Notifying: Denmark</t>
         </is>
       </c>
       <c r="D828" s="2" t="inlineStr">
@@ -52615,32 +52615,32 @@
       </c>
       <c r="E828" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp. in frozen poultry meat from Brazil</t>
+          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany</t>
         </is>
       </c>
       <c r="F828" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Ochratoxin</t>
         </is>
       </c>
       <c r="G828" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp. in frozen poultry meat from Brazil; risk: potential risk; category: poultry meat and poultry meat products</t>
+          <t>Ochratoxin in organic sultanas from Uzbekistan via Germany; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H828" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I828" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="J828" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K828" s="2" t="n">
@@ -52651,7 +52651,7 @@
       </c>
       <c r="M828" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836741</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836889</t>
         </is>
       </c>
     </row>
@@ -52668,7 +52668,7 @@
       </c>
       <c r="C829" s="2" t="inlineStr">
         <is>
-          <t>Origin: Turkey | Notifying: Germany | Distributed: Germany</t>
+          <t>Origin: Netherlands | Notifying: Belgium</t>
         </is>
       </c>
       <c r="D829" s="2" t="inlineStr">
@@ -52678,17 +52678,17 @@
       </c>
       <c r="E829" s="2" t="inlineStr">
         <is>
-          <t>Dry figs from Turkey</t>
+          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands</t>
         </is>
       </c>
       <c r="F829" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A</t>
+          <t>Norovirus</t>
         </is>
       </c>
       <c r="G829" s="2" t="inlineStr">
         <is>
-          <t>High level of Ochratoxin A detected in dry figs from Turkey distributed in Germany</t>
+          <t>Norovirus (GI /2g) in oysters (Crassostrea gigas) from the Netherlands; risk: potentially serious; category: bivalve molluscs and products thereof</t>
         </is>
       </c>
       <c r="H829" s="2" t="inlineStr">
@@ -52698,7 +52698,7 @@
       </c>
       <c r="I829" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="J829" s="2" t="inlineStr">
@@ -52714,7 +52714,7 @@
       </c>
       <c r="M829" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836362</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836765</t>
         </is>
       </c>
     </row>
@@ -52731,7 +52731,7 @@
       </c>
       <c r="C830" s="2" t="inlineStr">
         <is>
-          <t>Origin: Turkey | Notifying: unknown | Distributed: EU (multi)</t>
+          <t>Origin: Brazil | Notifying: Croatia</t>
         </is>
       </c>
       <c r="D830" s="2" t="inlineStr">
@@ -52741,32 +52741,32 @@
       </c>
       <c r="E830" s="2" t="inlineStr">
         <is>
-          <t>Dry figs from Turkey</t>
+          <t>Salmonella spp. in frozen poultry meat from Brazil</t>
         </is>
       </c>
       <c r="F830" s="2" t="inlineStr">
         <is>
-          <t>Ochratoxin A</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G830" s="2" t="inlineStr">
         <is>
-          <t>High level of Ochratoxin A detected in dry figs from Turkey</t>
+          <t>Salmonella spp. in frozen poultry meat from Brazil; risk: potential risk; category: poultry meat and poultry meat products</t>
         </is>
       </c>
       <c r="H830" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I830" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J830" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K830" s="2" t="n">
@@ -52777,7 +52777,7 @@
       </c>
       <c r="M830" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836354</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836741</t>
         </is>
       </c>
     </row>
@@ -52789,58 +52789,58 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C831" s="2" t="inlineStr">
         <is>
-          <t>Sultan Fine Foods</t>
+          <t>Origin: Turkey | Notifying: Germany | Distributed: Germany</t>
         </is>
       </c>
       <c r="D831" s="2" t="inlineStr">
         <is>
-          <t>Sultan Fine Foods</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E831" s="2" t="inlineStr">
         <is>
-          <t>Pistachio Kernel, 10 kg (Lot TME20250825PK, best-before AUG 2027)</t>
+          <t>Dry figs from Turkey</t>
         </is>
       </c>
       <c r="F831" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Ochratoxin A</t>
         </is>
       </c>
       <c r="G831" s="2" t="inlineStr">
         <is>
-          <t>Salmonella contamination — precautionary recall (linked to ongoing Iranian pistachio outbreak investigation; no illnesses tied to this specific Sultan product per CFIA page)</t>
+          <t>High level of Ochratoxin A detected in dry figs from Turkey distributed in Germany</t>
         </is>
       </c>
       <c r="H831" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I831" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J831" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K831" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L831" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M831" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/pistachio-kernel-recalled-due-salmonella-0</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836362</t>
         </is>
       </c>
     </row>
@@ -52852,58 +52852,58 @@
       </c>
       <c r="B832" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C832" s="2" t="inlineStr">
         <is>
-          <t>Fresh Start Foods</t>
+          <t>Origin: Turkey | Notifying: unknown | Distributed: EU (multi)</t>
         </is>
       </c>
       <c r="D832" s="2" t="inlineStr">
         <is>
-          <t>Fresh Start Foods</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E832" s="2" t="inlineStr">
         <is>
-          <t>Salads (BC)</t>
+          <t>Dry figs from Turkey</t>
         </is>
       </c>
       <c r="F832" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Ochratoxin A</t>
         </is>
       </c>
       <c r="G832" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>High level of Ochratoxin A detected in dry figs from Turkey</t>
         </is>
       </c>
       <c r="H832" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I832" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J832" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K832" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L832" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M832" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/fresh-start-foods-brand-salads-recalled-due-listeria-monocytogenes</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836354</t>
         </is>
       </c>
     </row>
@@ -53046,7 +53046,7 @@
       </c>
       <c r="C835" s="2" t="inlineStr">
         <is>
-          <t>LA FERME DU SOUHEIL GAEC LA FERME DU SOUHEIL</t>
+          <t>GAEC La Ferme du Souheil</t>
         </is>
       </c>
       <c r="D835" s="2" t="inlineStr">
@@ -53056,7 +53056,7 @@
       </c>
       <c r="E835" s="2" t="inlineStr">
         <is>
-          <t>Sainte Maure de Touraine AOP (lot 78 e... — full lot string per fiche)</t>
+          <t>Sainte Maure de Touraine AOP</t>
         </is>
       </c>
       <c r="F835" s="2" t="inlineStr">
@@ -53109,7 +53109,7 @@
       </c>
       <c r="C836" s="2" t="inlineStr">
         <is>
-          <t>LA FERME DU SOUHEIL GAEC LA FERME DU SOUHEIL</t>
+          <t>GAEC La Ferme du Souheil</t>
         </is>
       </c>
       <c r="D836" s="2" t="inlineStr">
@@ -55561,42 +55561,42 @@
       </c>
       <c r="B875" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C875" s="2" t="inlineStr">
         <is>
-          <t>BLV (multi-producer public warning)</t>
+          <t>Luna Food</t>
         </is>
       </c>
       <c r="D875" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Shakishaki</t>
         </is>
       </c>
       <c r="E875" s="2" t="inlineStr">
         <is>
-          <t>Various soft cheeses</t>
+          <t>Onigiri du Moment</t>
         </is>
       </c>
       <c r="F875" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G875" s="2" t="inlineStr">
         <is>
-          <t>Public warning — Salmonella detected in various soft cheeses</t>
+          <t>Listeria detected in the manufacturing environment</t>
         </is>
       </c>
       <c r="H875" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I875" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J875" s="2" t="inlineStr">
@@ -55612,7 +55612,7 @@
       </c>
       <c r="M875" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-salmonellen-weichkaese.pdf.download.pdf/oW_Salmonellen%20in%20verschiedenen%20Weichk%C3%A4sen.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21951/Interne</t>
         </is>
       </c>
     </row>
@@ -55624,42 +55624,42 @@
       </c>
       <c r="B876" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C876" s="2" t="inlineStr">
         <is>
-          <t>Origin: Ireland | Notifying: Ireland</t>
+          <t>Luna Food</t>
         </is>
       </c>
       <c r="D876" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Foodles</t>
         </is>
       </c>
       <c r="E876" s="2" t="inlineStr">
         <is>
-          <t>Detection of Cronobacter in a batch of Infant Formula</t>
+          <t>Cooked salmon poke</t>
         </is>
       </c>
       <c r="F876" s="2" t="inlineStr">
         <is>
-          <t>Cronobacter sakazakii</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G876" s="2" t="inlineStr">
         <is>
-          <t>Detection of Cronobacter in a batch of Infant Formula; risk: serious; category: milk and milk products</t>
+          <t>Listeria detected in the manufacturing environment</t>
         </is>
       </c>
       <c r="H876" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I876" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J876" s="2" t="inlineStr">
@@ -55668,14 +55668,14 @@
         </is>
       </c>
       <c r="K876" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L876" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M876" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836052</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21950/Interne</t>
         </is>
       </c>
     </row>
@@ -55687,42 +55687,42 @@
       </c>
       <c r="B877" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C877" s="2" t="inlineStr">
         <is>
-          <t>Origin: Netherlands | Notifying: Italy</t>
+          <t>BLV (multi-producer public warning)</t>
         </is>
       </c>
       <c r="D877" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E877" s="2" t="inlineStr">
         <is>
-          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp</t>
+          <t>Various soft cheeses</t>
         </is>
       </c>
       <c r="F877" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G877" s="2" t="inlineStr">
         <is>
-          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp; risk: potentially serious; category: crustaceans and products thereof</t>
+          <t>Public warning — Salmonella detected in various soft cheeses</t>
         </is>
       </c>
       <c r="H877" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I877" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J877" s="2" t="inlineStr">
@@ -55738,7 +55738,7 @@
       </c>
       <c r="M877" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835939</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-salmonellen-weichkaese.pdf.download.pdf/oW_Salmonellen%20in%20verschiedenen%20Weichk%C3%A4sen.pdf</t>
         </is>
       </c>
     </row>
@@ -55755,7 +55755,7 @@
       </c>
       <c r="C878" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Germany</t>
+          <t>Origin: Ireland | Notifying: Ireland</t>
         </is>
       </c>
       <c r="D878" s="2" t="inlineStr">
@@ -55765,27 +55765,27 @@
       </c>
       <c r="E878" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkey</t>
+          <t>Detection of Cronobacter in a batch of Infant Formula</t>
         </is>
       </c>
       <c r="F878" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Cronobacter sakazakii</t>
         </is>
       </c>
       <c r="G878" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in dried figs from Turkey; risk: serious; category: fruits and vegetables</t>
+          <t>Detection of Cronobacter in a batch of Infant Formula; risk: serious; category: milk and milk products</t>
         </is>
       </c>
       <c r="H878" s="2" t="inlineStr">
         <is>
-          <t>Border Rejection</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I878" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J878" s="2" t="inlineStr">
@@ -55801,7 +55801,7 @@
       </c>
       <c r="M878" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835929</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/836052</t>
         </is>
       </c>
     </row>
@@ -55818,7 +55818,7 @@
       </c>
       <c r="C879" s="2" t="inlineStr">
         <is>
-          <t>Origin: Türkiye | Notifying: Greece</t>
+          <t>Origin: Netherlands | Notifying: Italy</t>
         </is>
       </c>
       <c r="D879" s="2" t="inlineStr">
@@ -55828,27 +55828,27 @@
       </c>
       <c r="E879" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye</t>
+          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp</t>
         </is>
       </c>
       <c r="F879" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G879" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
+          <t>listeria m. in gamberi congelati precotti red it to eat/Listeria monocytogenes in frozen, precooked shrimp; risk: potentially serious; category: crustaceans and products thereof</t>
         </is>
       </c>
       <c r="H879" s="2" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I879" s="2" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="J879" s="2" t="inlineStr">
@@ -55857,14 +55857,14 @@
         </is>
       </c>
       <c r="K879" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L879" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M879" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835805</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835939</t>
         </is>
       </c>
     </row>
@@ -55881,7 +55881,7 @@
       </c>
       <c r="C880" s="2" t="inlineStr">
         <is>
-          <t>Origin: United States | Notifying: Italy</t>
+          <t>Origin: Türkiye | Notifying: Germany</t>
         </is>
       </c>
       <c r="D880" s="2" t="inlineStr">
@@ -55891,7 +55891,7 @@
       </c>
       <c r="E880" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in shelled Pistachios from USA via Turkey</t>
+          <t>Aflatoxins in dried figs from Turkey</t>
         </is>
       </c>
       <c r="F880" s="2" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="G880" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins in shelled Pistachios from USA via Turkey; risk: serious; category: fruits and vegetables</t>
+          <t>Aflatoxins in dried figs from Turkey; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H880" s="2" t="inlineStr">
@@ -55911,12 +55911,12 @@
       </c>
       <c r="I880" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J880" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K880" s="2" t="n">
@@ -55927,7 +55927,7 @@
       </c>
       <c r="M880" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835699</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835929</t>
         </is>
       </c>
     </row>
@@ -55939,42 +55939,42 @@
       </c>
       <c r="B881" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C881" s="2" t="inlineStr">
         <is>
-          <t>Luna Food</t>
+          <t>Origin: Türkiye | Notifying: Greece</t>
         </is>
       </c>
       <c r="D881" s="2" t="inlineStr">
         <is>
-          <t>Shakishaki</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E881" s="2" t="inlineStr">
         <is>
-          <t>Onigiri with avocado and wasabi (GTIN 3760373401084)</t>
+          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye</t>
         </is>
       </c>
       <c r="F881" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G881" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected in the manufacturing environment</t>
+          <t>Aflatoxins (B1=15.2; Tot.=38.0 μg/kg - ppb) in dried figs from Türkiye; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H881" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="I881" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="J881" s="2" t="inlineStr">
@@ -55983,14 +55983,14 @@
         </is>
       </c>
       <c r="K881" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L881" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M881" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21962/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835805</t>
         </is>
       </c>
     </row>
@@ -56002,58 +56002,58 @@
       </c>
       <c r="B882" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C882" s="2" t="inlineStr">
         <is>
-          <t>Luna Food</t>
+          <t>Origin: United States | Notifying: Italy</t>
         </is>
       </c>
       <c r="D882" s="2" t="inlineStr">
         <is>
-          <t>Shakishaki</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E882" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Beef Teriyaki</t>
+          <t>Aflatoxins in shelled Pistachios from USA via Turkey</t>
         </is>
       </c>
       <c r="F882" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Aflatoxin</t>
         </is>
       </c>
       <c r="G882" s="2" t="inlineStr">
         <is>
-          <t>Listeria detected in the manufacturing environment</t>
+          <t>Aflatoxins in shelled Pistachios from USA via Turkey; risk: serious; category: fruits and vegetables</t>
         </is>
       </c>
       <c r="H882" s="2" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Border Rejection</t>
         </is>
       </c>
       <c r="I882" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J882" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K882" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L882" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M882" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21961/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/835699</t>
         </is>
       </c>
     </row>
@@ -56080,7 +56080,7 @@
       </c>
       <c r="E883" s="2" t="inlineStr">
         <is>
-          <t>Onigiri du Moment</t>
+          <t>Onigiri with avocado and wasabi (GTIN 3760373401084)</t>
         </is>
       </c>
       <c r="F883" s="2" t="inlineStr">
@@ -56116,7 +56116,7 @@
       </c>
       <c r="M883" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21960/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21962/Interne</t>
         </is>
       </c>
     </row>
@@ -56143,7 +56143,7 @@
       </c>
       <c r="E884" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Chicken Yakitori</t>
+          <t>Onigiri Beef Teriyaki</t>
         </is>
       </c>
       <c r="F884" s="2" t="inlineStr">
@@ -56179,7 +56179,7 @@
       </c>
       <c r="M884" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21959/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21961/Interne</t>
         </is>
       </c>
     </row>
@@ -56206,7 +56206,7 @@
       </c>
       <c r="E885" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Salmon Cream Cheese</t>
+          <t>Onigiri du Moment</t>
         </is>
       </c>
       <c r="F885" s="2" t="inlineStr">
@@ -56242,7 +56242,7 @@
       </c>
       <c r="M885" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21958/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21960/Interne</t>
         </is>
       </c>
     </row>
@@ -56269,7 +56269,7 @@
       </c>
       <c r="E886" s="2" t="inlineStr">
         <is>
-          <t>Onigiri Spicy Tuna Mayo</t>
+          <t>Onigiri Chicken Yakitori</t>
         </is>
       </c>
       <c r="F886" s="2" t="inlineStr">
@@ -56305,7 +56305,7 @@
       </c>
       <c r="M886" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21957/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21959/Interne</t>
         </is>
       </c>
     </row>
@@ -56332,7 +56332,7 @@
       </c>
       <c r="E887" s="2" t="inlineStr">
         <is>
-          <t>Cooked Salmon Poke</t>
+          <t>Onigiri Salmon Cream Cheese</t>
         </is>
       </c>
       <c r="F887" s="2" t="inlineStr">
@@ -56368,7 +56368,7 @@
       </c>
       <c r="M887" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21954/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21958/Interne</t>
         </is>
       </c>
     </row>
@@ -56395,7 +56395,7 @@
       </c>
       <c r="E888" s="2" t="inlineStr">
         <is>
-          <t>Onigiri (assorted variety)</t>
+          <t>Onigiri Spicy Tuna Mayo</t>
         </is>
       </c>
       <c r="F888" s="2" t="inlineStr">
@@ -56431,7 +56431,7 @@
       </c>
       <c r="M888" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21953/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21957/Interne</t>
         </is>
       </c>
     </row>
@@ -56458,7 +56458,7 @@
       </c>
       <c r="E889" s="2" t="inlineStr">
         <is>
-          <t>Onigiri (assorted variety)</t>
+          <t>Cooked Salmon Poke</t>
         </is>
       </c>
       <c r="F889" s="2" t="inlineStr">
@@ -56494,7 +56494,7 @@
       </c>
       <c r="M889" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21952/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21954/Interne</t>
         </is>
       </c>
     </row>
@@ -56521,7 +56521,7 @@
       </c>
       <c r="E890" s="2" t="inlineStr">
         <is>
-          <t>Onigiri du Moment</t>
+          <t>Onigiri (assorted variety)</t>
         </is>
       </c>
       <c r="F890" s="2" t="inlineStr">
@@ -56557,7 +56557,7 @@
       </c>
       <c r="M890" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21951/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21953/Interne</t>
         </is>
       </c>
     </row>
@@ -56579,12 +56579,12 @@
       </c>
       <c r="D891" s="2" t="inlineStr">
         <is>
-          <t>Foodles</t>
+          <t>Shakishaki</t>
         </is>
       </c>
       <c r="E891" s="2" t="inlineStr">
         <is>
-          <t>Cooked salmon poke</t>
+          <t>Onigiri (assorted variety)</t>
         </is>
       </c>
       <c r="F891" s="2" t="inlineStr">
@@ -56620,7 +56620,7 @@
       </c>
       <c r="M891" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21950/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21952/Interne</t>
         </is>
       </c>
     </row>
@@ -58847,12 +58847,12 @@
       </c>
       <c r="D927" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio</t>
+          <t>French Kitchen</t>
         </is>
       </c>
       <c r="E927" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Sautéed Chicken, Thyme Potatoes, Mustard Sauce (GTIN 3760373401534)</t>
         </is>
       </c>
       <c r="F927" s="2" t="inlineStr">
@@ -58888,7 +58888,7 @@
       </c>
       <c r="M927" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21935/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21933/Interne</t>
         </is>
       </c>
     </row>
@@ -58915,7 +58915,7 @@
       </c>
       <c r="E928" s="2" t="inlineStr">
         <is>
-          <t>Sautéed Chicken, Thyme Potatoes, Mustard Sauce (GTIN 3760373401534)</t>
+          <t>French Kitchen ready meal</t>
         </is>
       </c>
       <c r="F928" s="2" t="inlineStr">
@@ -58951,7 +58951,7 @@
       </c>
       <c r="M928" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21933/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21932/Interne</t>
         </is>
       </c>
     </row>
@@ -58973,12 +58973,12 @@
       </c>
       <c r="D929" s="2" t="inlineStr">
         <is>
-          <t>French Kitchen</t>
+          <t>Chinese Kitchen</t>
         </is>
       </c>
       <c r="E929" s="2" t="inlineStr">
         <is>
-          <t>French Kitchen ready meal</t>
+          <t>Beef Fried Rice (GTIN 3760373402203)</t>
         </is>
       </c>
       <c r="F929" s="2" t="inlineStr">
@@ -59014,7 +59014,7 @@
       </c>
       <c r="M929" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21932/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21931/Interne</t>
         </is>
       </c>
     </row>
@@ -59036,12 +59036,12 @@
       </c>
       <c r="D930" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen</t>
+          <t>Luisa e basilio</t>
         </is>
       </c>
       <c r="E930" s="2" t="inlineStr">
         <is>
-          <t>Beef Fried Rice (GTIN 3760373402203)</t>
+          <t>Luisa e basilio ready meal</t>
         </is>
       </c>
       <c r="F930" s="2" t="inlineStr">
@@ -59077,7 +59077,7 @@
       </c>
       <c r="M930" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21931/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21935/Interne</t>
         </is>
       </c>
     </row>
@@ -71211,7 +71211,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12 06:59 UTC</t>
+          <t>Generated: 2026-07-12 14:32 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -2845,7 +2845,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Salade de taboulé poulet; Salade de taboulé poulet mariné</t>
+          <t>Salade de taboulé poulet; Salade de taboulé poulet mariné (RappelConso fiche 22762)</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>salade de taboulé poulet; salade de taboulé poulet mariné</t>
+          <t>salade de taboulé poulet; salade de taboulé poulet mariné (RappelConso fiche 22757)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>salade strasbourgeoise</t>
+          <t>salade strasbourgeoise (RappelConso fiche 22699)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>brisures de saumon fumé 150g</t>
+          <t>brisures de saumon fumé 150g (RappelConso fiche 22623)</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>format 180g</t>
+          <t>format 180g (RappelConso fiche 22598)</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Steak haché vendu au rayon traditionnel à la demande du client</t>
+          <t>Steak haché vendu au rayon traditionnel à la demande du client (RappelConso fiche 22607)</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>format 180g</t>
+          <t>format 180g (RappelConso fiche 22600)</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>steak haché vendu au rayon traditionnel à la demande du client</t>
+          <t>steak haché vendu au rayon traditionnel à la demande du client (RappelConso fiche 22608)</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>salade strasbourgeoise</t>
+          <t>salade strasbourgeoise (RappelConso fiche 22596)</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>crevettes grises cuites</t>
+          <t>crevettes grises cuites (RappelConso fiche 22517)</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>crevettes grises cuites</t>
+          <t>crevettes grises cuites (RappelConso fiche 22491)</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
@@ -18721,7 +18721,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>SURPRISE DE PORC MARINE A L'ANDALOUSE</t>
+          <t>SURPRISE DE PORC MARINE A L'ANDALOUSE (RappelConso fiche 22529)</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
@@ -19351,7 +19351,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>surprise de porc marine a l'andalouse</t>
+          <t>surprise de porc marine a l'andalouse (RappelConso fiche 22472)</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>ti guémené</t>
+          <t>ti guémené (RappelConso fiche 22444)</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>brisures de saumon fumé 150g</t>
+          <t>brisures de saumon fumé 150g (RappelConso fiche 22435)</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>ti guémené</t>
+          <t>ti guémené (RappelConso fiche 22443)</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -26281,7 +26281,7 @@
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22353)</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22352)</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22351)</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22350)</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
@@ -26533,7 +26533,7 @@
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22349)</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22348)</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
@@ -26659,7 +26659,7 @@
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22347)</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22346)</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
@@ -32455,7 +32455,7 @@
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>Reblochon de Savoie fermier AOP 450g</t>
+          <t>Reblochon de Savoie fermier AOP 450g (RappelConso fiche 22275)</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
@@ -32644,7 +32644,7 @@
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>reblochon de savoie fermier aop 450g</t>
+          <t>reblochon de savoie fermier aop 450g (RappelConso fiche 22274)</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>Brisures de saumon fumé 150g</t>
+          <t>Brisures de saumon fumé 150g (RappelConso fiche 22234)</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -35416,7 +35416,7 @@
       </c>
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>Viandes (charcuterie)</t>
+          <t>Viandes (charcuterie) (RappelConso fiche 22196)</t>
         </is>
       </c>
       <c r="F555" s="2" t="inlineStr">
@@ -35479,7 +35479,7 @@
       </c>
       <c r="E556" s="2" t="inlineStr">
         <is>
-          <t>Viandes (charcuterie)</t>
+          <t>Viandes (charcuterie) (RappelConso fiche 22197)</t>
         </is>
       </c>
       <c r="F556" s="2" t="inlineStr">
@@ -35542,7 +35542,7 @@
       </c>
       <c r="E557" s="2" t="inlineStr">
         <is>
-          <t>Viandes (charcuterie)</t>
+          <t>Viandes (charcuterie) (RappelConso fiche 22198)</t>
         </is>
       </c>
       <c r="F557" s="2" t="inlineStr">
@@ -35605,7 +35605,7 @@
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>Viandes (charcuterie)</t>
+          <t>Viandes (charcuterie) (RappelConso fiche 22199)</t>
         </is>
       </c>
       <c r="F558" s="2" t="inlineStr">
@@ -35668,7 +35668,7 @@
       </c>
       <c r="E559" s="2" t="inlineStr">
         <is>
-          <t>Viandes</t>
+          <t>Viandes (RappelConso fiche 22211)</t>
         </is>
       </c>
       <c r="F559" s="2" t="inlineStr">
@@ -35794,7 +35794,7 @@
       </c>
       <c r="E561" s="2" t="inlineStr">
         <is>
-          <t>tomme</t>
+          <t>tomme (RappelConso fiche 22219)</t>
         </is>
       </c>
       <c r="F561" s="2" t="inlineStr">
@@ -37747,7 +37747,7 @@
       </c>
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>viandes</t>
+          <t>viandes (RappelConso fiche 22190)</t>
         </is>
       </c>
       <c r="F592" s="2" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="E598" s="2" t="inlineStr">
         <is>
-          <t>fruits et légumes</t>
+          <t>fruits et légumes (RappelConso fiche 22178)</t>
         </is>
       </c>
       <c r="F598" s="2" t="inlineStr">
@@ -38188,7 +38188,7 @@
       </c>
       <c r="E599" s="2" t="inlineStr">
         <is>
-          <t>viandes</t>
+          <t>viandes (RappelConso fiche 22177)</t>
         </is>
       </c>
       <c r="F599" s="2" t="inlineStr">
@@ -38251,7 +38251,7 @@
       </c>
       <c r="E600" s="2" t="inlineStr">
         <is>
-          <t>viandes</t>
+          <t>viandes (RappelConso fiche 22173)</t>
         </is>
       </c>
       <c r="F600" s="2" t="inlineStr">
@@ -40519,7 +40519,7 @@
       </c>
       <c r="E636" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 22157)</t>
         </is>
       </c>
       <c r="F636" s="2" t="inlineStr">
@@ -42976,7 +42976,7 @@
       </c>
       <c r="E675" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 22113)</t>
         </is>
       </c>
       <c r="F675" s="2" t="inlineStr">
@@ -44740,7 +44740,7 @@
       </c>
       <c r="E703" s="2" t="inlineStr">
         <is>
-          <t>fruits et légumes</t>
+          <t>fruits et légumes (RappelConso fiche 22055)</t>
         </is>
       </c>
       <c r="F703" s="2" t="inlineStr">
@@ -44803,7 +44803,7 @@
       </c>
       <c r="E704" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 22067)</t>
         </is>
       </c>
       <c r="F704" s="2" t="inlineStr">
@@ -45181,7 +45181,7 @@
       </c>
       <c r="E710" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 22082)</t>
         </is>
       </c>
       <c r="F710" s="2" t="inlineStr">
@@ -47071,7 +47071,7 @@
       </c>
       <c r="E740" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 22056)</t>
         </is>
       </c>
       <c r="F740" s="2" t="inlineStr">
@@ -49465,7 +49465,7 @@
       </c>
       <c r="E778" s="2" t="inlineStr">
         <is>
-          <t>fruits et légumes</t>
+          <t>fruits et légumes (RappelConso fiche 22039)</t>
         </is>
       </c>
       <c r="F778" s="2" t="inlineStr">
@@ -52048,7 +52048,7 @@
       </c>
       <c r="E819" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 22005)</t>
         </is>
       </c>
       <c r="F819" s="2" t="inlineStr">
@@ -53308,7 +53308,7 @@
       </c>
       <c r="E839" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 21987)</t>
         </is>
       </c>
       <c r="F839" s="2" t="inlineStr">
@@ -54190,7 +54190,7 @@
       </c>
       <c r="E853" s="2" t="inlineStr">
         <is>
-          <t>produits de la pêche et d'aquaculture</t>
+          <t>produits de la pêche et d'aquaculture (RappelConso fiche 21975)</t>
         </is>
       </c>
       <c r="F853" s="2" t="inlineStr">
@@ -55072,7 +55072,7 @@
       </c>
       <c r="E867" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Luisa e basilio ready meal (RappelConso fiche 21942)</t>
         </is>
       </c>
       <c r="F867" s="2" t="inlineStr">
@@ -55135,7 +55135,7 @@
       </c>
       <c r="E868" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Luisa e basilio ready meal (RappelConso fiche 21943)</t>
         </is>
       </c>
       <c r="F868" s="2" t="inlineStr">
@@ -55198,7 +55198,7 @@
       </c>
       <c r="E869" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Luisa e basilio ready meal (RappelConso fiche 21945)</t>
         </is>
       </c>
       <c r="F869" s="2" t="inlineStr">
@@ -55261,7 +55261,7 @@
       </c>
       <c r="E870" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Luisa e basilio ready meal (RappelConso fiche 21944)</t>
         </is>
       </c>
       <c r="F870" s="2" t="inlineStr">
@@ -55324,7 +55324,7 @@
       </c>
       <c r="E871" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Luisa e basilio ready meal (RappelConso fiche 21947)</t>
         </is>
       </c>
       <c r="F871" s="2" t="inlineStr">
@@ -55639,7 +55639,7 @@
       </c>
       <c r="E876" s="2" t="inlineStr">
         <is>
-          <t>Cooked salmon poke</t>
+          <t>Cooked salmon poke (RappelConso fiche 21950)</t>
         </is>
       </c>
       <c r="F876" s="2" t="inlineStr">
@@ -56584,7 +56584,7 @@
       </c>
       <c r="E891" s="2" t="inlineStr">
         <is>
-          <t>Cooked Salmon Poke</t>
+          <t>Cooked Salmon Poke (RappelConso fiche 21954)</t>
         </is>
       </c>
       <c r="F891" s="2" t="inlineStr">
@@ -56773,7 +56773,7 @@
       </c>
       <c r="E894" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21899)</t>
         </is>
       </c>
       <c r="F894" s="2" t="inlineStr">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="E895" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21898)</t>
         </is>
       </c>
       <c r="F895" s="2" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="E896" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21897)</t>
         </is>
       </c>
       <c r="F896" s="2" t="inlineStr">
@@ -56962,7 +56962,7 @@
       </c>
       <c r="E897" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21901)</t>
         </is>
       </c>
       <c r="F897" s="2" t="inlineStr">
@@ -57025,7 +57025,7 @@
       </c>
       <c r="E898" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21902)</t>
         </is>
       </c>
       <c r="F898" s="2" t="inlineStr">
@@ -57088,7 +57088,7 @@
       </c>
       <c r="E899" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21903)</t>
         </is>
       </c>
       <c r="F899" s="2" t="inlineStr">
@@ -57151,7 +57151,7 @@
       </c>
       <c r="E900" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21904)</t>
         </is>
       </c>
       <c r="F900" s="2" t="inlineStr">
@@ -57214,7 +57214,7 @@
       </c>
       <c r="E901" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21905)</t>
         </is>
       </c>
       <c r="F901" s="2" t="inlineStr">
@@ -57277,7 +57277,7 @@
       </c>
       <c r="E902" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21906)</t>
         </is>
       </c>
       <c r="F902" s="2" t="inlineStr">
@@ -57340,7 +57340,7 @@
       </c>
       <c r="E903" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21907)</t>
         </is>
       </c>
       <c r="F903" s="2" t="inlineStr">
@@ -57403,7 +57403,7 @@
       </c>
       <c r="E904" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21908)</t>
         </is>
       </c>
       <c r="F904" s="2" t="inlineStr">
@@ -57466,7 +57466,7 @@
       </c>
       <c r="E905" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21909)</t>
         </is>
       </c>
       <c r="F905" s="2" t="inlineStr">
@@ -57529,7 +57529,7 @@
       </c>
       <c r="E906" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21911)</t>
         </is>
       </c>
       <c r="F906" s="2" t="inlineStr">
@@ -57592,7 +57592,7 @@
       </c>
       <c r="E907" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21910)</t>
         </is>
       </c>
       <c r="F907" s="2" t="inlineStr">
@@ -57655,7 +57655,7 @@
       </c>
       <c r="E908" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21913)</t>
         </is>
       </c>
       <c r="F908" s="2" t="inlineStr">
@@ -57718,7 +57718,7 @@
       </c>
       <c r="E909" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21912)</t>
         </is>
       </c>
       <c r="F909" s="2" t="inlineStr">
@@ -57781,7 +57781,7 @@
       </c>
       <c r="E910" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21915)</t>
         </is>
       </c>
       <c r="F910" s="2" t="inlineStr">
@@ -57844,7 +57844,7 @@
       </c>
       <c r="E911" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21914)</t>
         </is>
       </c>
       <c r="F911" s="2" t="inlineStr">
@@ -57970,7 +57970,7 @@
       </c>
       <c r="E913" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21916)</t>
         </is>
       </c>
       <c r="F913" s="2" t="inlineStr">
@@ -58033,7 +58033,7 @@
       </c>
       <c r="E914" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21919)</t>
         </is>
       </c>
       <c r="F914" s="2" t="inlineStr">
@@ -58096,7 +58096,7 @@
       </c>
       <c r="E915" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21918)</t>
         </is>
       </c>
       <c r="F915" s="2" t="inlineStr">
@@ -58159,7 +58159,7 @@
       </c>
       <c r="E916" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21921)</t>
         </is>
       </c>
       <c r="F916" s="2" t="inlineStr">
@@ -58222,7 +58222,7 @@
       </c>
       <c r="E917" s="2" t="inlineStr">
         <is>
-          <t>Ready meal / sandwich (SKU not extractable)</t>
+          <t>Ready meal / sandwich (RappelConso fiche 21920)</t>
         </is>
       </c>
       <c r="F917" s="2" t="inlineStr">
@@ -58285,7 +58285,7 @@
       </c>
       <c r="E918" s="2" t="inlineStr">
         <is>
-          <t>Bim bang Asian-style ready meal / kimbap</t>
+          <t>Bim bang Asian-style ready meal / kimbap (RappelConso fiche 21924)</t>
         </is>
       </c>
       <c r="F918" s="2" t="inlineStr">
@@ -58537,7 +58537,7 @@
       </c>
       <c r="E922" s="2" t="inlineStr">
         <is>
-          <t>Bim bang Asian-style ready meal / kimbap</t>
+          <t>Bim bang Asian-style ready meal / kimbap (RappelConso fiche 21926)</t>
         </is>
       </c>
       <c r="F922" s="2" t="inlineStr">
@@ -58600,7 +58600,7 @@
       </c>
       <c r="E923" s="2" t="inlineStr">
         <is>
-          <t>Bim bang Asian-style ready meal / kimbap</t>
+          <t>Bim bang Asian-style ready meal / kimbap (RappelConso fiche 21925)</t>
         </is>
       </c>
       <c r="F923" s="2" t="inlineStr">
@@ -58663,7 +58663,7 @@
       </c>
       <c r="E924" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen ready meal</t>
+          <t>Chinese Kitchen ready meal (RappelConso fiche 21930)</t>
         </is>
       </c>
       <c r="F924" s="2" t="inlineStr">
@@ -58726,7 +58726,7 @@
       </c>
       <c r="E925" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen ready meal</t>
+          <t>Chinese Kitchen ready meal (RappelConso fiche 21929)</t>
         </is>
       </c>
       <c r="F925" s="2" t="inlineStr">
@@ -58789,7 +58789,7 @@
       </c>
       <c r="E926" s="2" t="inlineStr">
         <is>
-          <t>Chinese Kitchen ready meal</t>
+          <t>Chinese Kitchen ready meal (RappelConso fiche 21928)</t>
         </is>
       </c>
       <c r="F926" s="2" t="inlineStr">
@@ -59041,7 +59041,7 @@
       </c>
       <c r="E930" s="2" t="inlineStr">
         <is>
-          <t>Luisa e basilio ready meal</t>
+          <t>Luisa e basilio ready meal (RappelConso fiche 21935)</t>
         </is>
       </c>
       <c r="F930" s="2" t="inlineStr">
@@ -59167,7 +59167,7 @@
       </c>
       <c r="E932" s="2" t="inlineStr">
         <is>
-          <t>Monoprix-branded onigiri / ready meal (SKU not extractable)</t>
+          <t>Monoprix-branded onigiri / ready meal (RappelConso fiche 21883)</t>
         </is>
       </c>
       <c r="F932" s="2" t="inlineStr">
@@ -59293,7 +59293,7 @@
       </c>
       <c r="E934" s="2" t="inlineStr">
         <is>
-          <t>Monoprix-branded onigiri / ready meal (SKU not extractable)</t>
+          <t>Monoprix-branded onigiri / ready meal (RappelConso fiche 21889)</t>
         </is>
       </c>
       <c r="F934" s="2" t="inlineStr">
@@ -59482,7 +59482,7 @@
       </c>
       <c r="E937" s="2" t="inlineStr">
         <is>
-          <t>Monoprix-branded onigiri / ready meal (SKU not extractable)</t>
+          <t>Monoprix-branded onigiri / ready meal (RappelConso fiche 21887)</t>
         </is>
       </c>
       <c r="F937" s="2" t="inlineStr">
@@ -59923,7 +59923,7 @@
       </c>
       <c r="E944" s="2" t="inlineStr">
         <is>
-          <t>Carrefour Le Marché ready meal (SKU not extractable)</t>
+          <t>Carrefour Le Marché ready meal (RappelConso fiche 21877)</t>
         </is>
       </c>
       <c r="F944" s="2" t="inlineStr">
@@ -60175,7 +60175,7 @@
       </c>
       <c r="E948" s="2" t="inlineStr">
         <is>
-          <t>Onigiri / wrap / sandwich (SKU not extractable)</t>
+          <t>Onigiri / wrap / sandwich (RappelConso fiche 21873)</t>
         </is>
       </c>
       <c r="F948" s="2" t="inlineStr">
@@ -60238,7 +60238,7 @@
       </c>
       <c r="E949" s="2" t="inlineStr">
         <is>
-          <t>Carrefour Le Marché ready meal (SKU not extractable)</t>
+          <t>Carrefour Le Marché ready meal (RappelConso fiche 21872)</t>
         </is>
       </c>
       <c r="F949" s="2" t="inlineStr">
@@ -60364,7 +60364,7 @@
       </c>
       <c r="E951" s="2" t="inlineStr">
         <is>
-          <t>Carrefour Le Marché ready meal (SKU not extractable)</t>
+          <t>Carrefour Le Marché ready meal (RappelConso fiche 21870)</t>
         </is>
       </c>
       <c r="F951" s="2" t="inlineStr">
@@ -60490,7 +60490,7 @@
       </c>
       <c r="E953" s="2" t="inlineStr">
         <is>
-          <t>Carrefour Le Marché ready meal (SKU not extractable)</t>
+          <t>Carrefour Le Marché ready meal (RappelConso fiche 21868)</t>
         </is>
       </c>
       <c r="F953" s="2" t="inlineStr">
@@ -60553,7 +60553,7 @@
       </c>
       <c r="E954" s="2" t="inlineStr">
         <is>
-          <t>Carrefour Le Marché ready meal (SKU not extractable)</t>
+          <t>Carrefour Le Marché ready meal (RappelConso fiche 21867)</t>
         </is>
       </c>
       <c r="F954" s="2" t="inlineStr">
@@ -60616,7 +60616,7 @@
       </c>
       <c r="E955" s="2" t="inlineStr">
         <is>
-          <t>Onigiri / wrap / sandwich (SKU not extractable)</t>
+          <t>Onigiri / wrap / sandwich (RappelConso fiche 21866)</t>
         </is>
       </c>
       <c r="F955" s="2" t="inlineStr">
@@ -63451,7 +63451,7 @@
       </c>
       <c r="E1000" s="2" t="inlineStr">
         <is>
-          <t>14 halal chicken sausages tray 140 g</t>
+          <t>14 halal chicken sausages tray 140 g (RappelConso fiche 21736)</t>
         </is>
       </c>
       <c r="F1000" s="2" t="inlineStr">
@@ -63514,7 +63514,7 @@
       </c>
       <c r="E1001" s="2" t="inlineStr">
         <is>
-          <t>14 halal chicken sausages tray 140 g</t>
+          <t>14 halal chicken sausages tray 140 g (RappelConso fiche 21735)</t>
         </is>
       </c>
       <c r="F1001" s="2" t="inlineStr">
@@ -63577,7 +63577,7 @@
       </c>
       <c r="E1002" s="2" t="inlineStr">
         <is>
-          <t>14 chicken-emmental sausage tray 140 g HAL SFC (sous atmosphère)</t>
+          <t>14 chicken-emmental sausage tray 140 g HAL SFC (sous atmosphère) (RappelConso fiche 21734)</t>
         </is>
       </c>
       <c r="F1002" s="2" t="inlineStr">
@@ -64774,7 +64774,7 @@
       </c>
       <c r="E1021" s="2" t="inlineStr">
         <is>
-          <t>14 chicken-emmental sausage tray 140 g HAL SFC (sous atmosphère)</t>
+          <t>14 chicken-emmental sausage tray 140 g HAL SFC (sous atmosphère) (RappelConso fiche 21639)</t>
         </is>
       </c>
       <c r="F1021" s="2" t="inlineStr">
@@ -64837,7 +64837,7 @@
       </c>
       <c r="E1022" s="2" t="inlineStr">
         <is>
-          <t>6 chicken-emmental sausages tray 300 g</t>
+          <t>6 chicken-emmental sausages tray 300 g (RappelConso fiche 21635)</t>
         </is>
       </c>
       <c r="F1022" s="2" t="inlineStr">
@@ -64900,7 +64900,7 @@
       </c>
       <c r="E1023" s="2" t="inlineStr">
         <is>
-          <t>6 chicken-emmental sausages tray 300 g</t>
+          <t>6 chicken-emmental sausages tray 300 g (RappelConso fiche 21632)</t>
         </is>
       </c>
       <c r="F1023" s="2" t="inlineStr">
@@ -65593,7 +65593,7 @@
       </c>
       <c r="E1034" s="2" t="inlineStr">
         <is>
-          <t>TOMME</t>
+          <t>TOMME (RappelConso fiche 21578)</t>
         </is>
       </c>
       <c r="F1034" s="2" t="inlineStr">
@@ -71211,7 +71211,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-13 07:49 UTC</t>
+          <t>Generated: 2026-07-13 14:49 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -71211,7 +71211,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-13 14:49 UTC</t>
+          <t>Generated: 2026-07-13 15:28 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1124"/>
+  <dimension ref="A1:M1119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -65137,22 +65137,22 @@
       </c>
       <c r="B1027" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (MPI NZ)</t>
+          <t>CFS (HK) - aggregator (RappelConso FR)</t>
         </is>
       </c>
       <c r="C1027" s="2" t="inlineStr">
         <is>
-          <t>Emborg</t>
+          <t>AOSTE</t>
         </is>
       </c>
       <c r="D1027" s="2" t="inlineStr">
         <is>
-          <t>Emborg</t>
+          <t>AOSTE</t>
         </is>
       </c>
       <c r="E1027" s="2" t="inlineStr">
         <is>
-          <t>Emmentaler cheese 200g</t>
+          <t>Cooked ham products</t>
         </is>
       </c>
       <c r="F1027" s="2" t="inlineStr">
@@ -65162,7 +65162,7 @@
       </c>
       <c r="G1027" s="2" t="inlineStr">
         <is>
-          <t>Possible presence of Listeria</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H1027" s="2" t="inlineStr">
@@ -65172,12 +65172,12 @@
       </c>
       <c r="I1027" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1027" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1027" s="2" t="n">
@@ -65188,7 +65188,7 @@
       </c>
       <c r="M1027" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260316_3.pdf</t>
+          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260316_1.pdf</t>
         </is>
       </c>
     </row>
@@ -65200,58 +65200,58 @@
       </c>
       <c r="B1028" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (RappelConso FR)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1028" s="2" t="inlineStr">
         <is>
-          <t>AOSTE</t>
+          <t>Multiple firms (Tootsi Impex et al.)</t>
         </is>
       </c>
       <c r="D1028" s="2" t="inlineStr">
         <is>
-          <t>AOSTE</t>
+          <t>Various pistachios</t>
         </is>
       </c>
       <c r="E1028" s="2" t="inlineStr">
         <is>
-          <t>Cooked ham products</t>
+          <t>Pistachios + 300+ pistachio-containing products</t>
         </is>
       </c>
       <c r="F1028" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella spp.</t>
         </is>
       </c>
       <c r="G1028" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1028" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I1028" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1028" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1028" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1028" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1028" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260316_1.pdf</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/various-pistachios-and-pistachio-containing-products-recalled-due-salmonella-5</t>
         </is>
       </c>
     </row>
@@ -65268,32 +65268,32 @@
       </c>
       <c r="C1029" s="2" t="inlineStr">
         <is>
-          <t>Multiple firms (Tootsi Impex et al.)</t>
+          <t>Various pistachio-containing products</t>
         </is>
       </c>
       <c r="D1029" s="2" t="inlineStr">
         <is>
-          <t>Various pistachios</t>
+          <t>Various pistachio-containing products</t>
         </is>
       </c>
       <c r="E1029" s="2" t="inlineStr">
         <is>
-          <t>Pistachios + 300+ pistachio-containing products</t>
+          <t>Various pistachio-containing products</t>
         </is>
       </c>
       <c r="F1029" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp.</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1029" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="H1029" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1029" s="2" t="inlineStr">
@@ -65310,11 +65310,11 @@
         <v>1</v>
       </c>
       <c r="L1029" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1029" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/various-pistachios-and-pistachio-containing-products-recalled-due-salmonella-5</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/various-pistachio-containing-products-recalled-due-salmonella-3</t>
         </is>
       </c>
     </row>
@@ -65326,32 +65326,32 @@
       </c>
       <c r="B1030" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>NCC (ZA)</t>
         </is>
       </c>
       <c r="C1030" s="2" t="inlineStr">
         <is>
-          <t>Various pistachio-containing products</t>
+          <t>Clicks Group / Made for Tots</t>
         </is>
       </c>
       <c r="D1030" s="2" t="inlineStr">
         <is>
-          <t>Various pistachio-containing products</t>
+          <t>Made for Tots</t>
         </is>
       </c>
       <c r="E1030" s="2" t="inlineStr">
         <is>
-          <t>Various pistachio-containing products</t>
+          <t>Corn Puffs Chicken 12g (1,152 units; 348 sold; Lot 396194 MGF 03.03.26 Lot 6:003 BB 02.03.2027)</t>
         </is>
       </c>
       <c r="F1030" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1030" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria contamination detected by supplier testing</t>
         </is>
       </c>
       <c r="H1030" s="2" t="inlineStr">
@@ -65361,12 +65361,12 @@
       </c>
       <c r="I1030" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="J1030" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="K1030" s="2" t="n">
@@ -65377,59 +65377,59 @@
       </c>
       <c r="M1030" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/various-pistachio-containing-products-recalled-due-salmonella-3</t>
+          <t>https://thencc.org.za/product-recalls/</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B1031" s="2" t="inlineStr">
         <is>
-          <t>NCC (ZA)</t>
+          <t>CFS (HK) - aggregator (MPI NZ)</t>
         </is>
       </c>
       <c r="C1031" s="2" t="inlineStr">
         <is>
-          <t>Clicks Group / Made for Tots</t>
+          <t>Banks Peninsula shellfish harvesters</t>
         </is>
       </c>
       <c r="D1031" s="2" t="inlineStr">
         <is>
-          <t>Made for Tots</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1031" s="2" t="inlineStr">
         <is>
-          <t>Corn Puffs Chicken 12g (1,152 units; 348 sold; Lot 396194 MGF 03.03.26 Lot 6:003 BB 02.03.2027)</t>
+          <t>Banks Peninsula shellfish (mussels, oysters, scallops, paua, cockles)</t>
         </is>
       </c>
       <c r="F1031" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Paralytic shellfish toxins (PSP)</t>
         </is>
       </c>
       <c r="G1031" s="2" t="inlineStr">
         <is>
-          <t>Listeria contamination detected by supplier testing</t>
+          <t>MPI NZ public health warning - PSP biotoxin levels above regulatory limit at Banks Peninsula.</t>
         </is>
       </c>
       <c r="H1031" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Public health warning</t>
         </is>
       </c>
       <c r="I1031" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="J1031" s="2" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K1031" s="2" t="n">
@@ -65440,7 +65440,7 @@
       </c>
       <c r="M1031" s="2" t="inlineStr">
         <is>
-          <t>https://thencc.org.za/product-recalls/</t>
+          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260313_2.pdf</t>
         </is>
       </c>
     </row>
@@ -65457,7 +65457,7 @@
       </c>
       <c r="C1032" s="2" t="inlineStr">
         <is>
-          <t>Banks Peninsula shellfish harvesters</t>
+          <t>— (Banks Peninsula shellfish)</t>
         </is>
       </c>
       <c r="D1032" s="2" t="inlineStr">
@@ -65467,7 +65467,7 @@
       </c>
       <c r="E1032" s="2" t="inlineStr">
         <is>
-          <t>Banks Peninsula shellfish (mussels, oysters, scallops, paua, cockles)</t>
+          <t>Shellfish gathered from northern side of Banks Peninsula</t>
         </is>
       </c>
       <c r="F1032" s="2" t="inlineStr">
@@ -65477,12 +65477,12 @@
       </c>
       <c r="G1032" s="2" t="inlineStr">
         <is>
-          <t>MPI NZ public health warning - PSP biotoxin levels above regulatory limit at Banks Peninsula.</t>
+          <t>Risk of paralytic shellfish poisoning</t>
         </is>
       </c>
       <c r="H1032" s="2" t="inlineStr">
         <is>
-          <t>Public health warning</t>
+          <t>Public advisory</t>
         </is>
       </c>
       <c r="I1032" s="2" t="inlineStr">
@@ -65503,7 +65503,7 @@
       </c>
       <c r="M1032" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260313_2.pdf</t>
+          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260313_1.pdf</t>
         </is>
       </c>
     </row>
@@ -65515,47 +65515,47 @@
       </c>
       <c r="B1033" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (MPI NZ)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1033" s="2" t="inlineStr">
         <is>
-          <t>— (Banks Peninsula shellfish)</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="D1033" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E1033" s="2" t="inlineStr">
         <is>
-          <t>Shellfish gathered from northern side of Banks Peninsula</t>
+          <t>MUSEAU DE PORC</t>
         </is>
       </c>
       <c r="F1033" s="2" t="inlineStr">
         <is>
-          <t>Paralytic shellfish toxins (PSP)</t>
+          <t>Salmonella spp.</t>
         </is>
       </c>
       <c r="G1033" s="2" t="inlineStr">
         <is>
-          <t>Risk of paralytic shellfish poisoning</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H1033" s="2" t="inlineStr">
         <is>
-          <t>Public advisory</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1033" s="2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1033" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1033" s="2" t="n">
@@ -65566,14 +65566,14 @@
       </c>
       <c r="M1033" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260313_1.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21622/Interne</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B1034" s="2" t="inlineStr">
@@ -65593,7 +65593,7 @@
       </c>
       <c r="E1034" s="2" t="inlineStr">
         <is>
-          <t>MUSEAU DE PORC</t>
+          <t>TOMME (RappelConso fiche 21578)</t>
         </is>
       </c>
       <c r="F1034" s="2" t="inlineStr">
@@ -65603,7 +65603,7 @@
       </c>
       <c r="G1034" s="2" t="inlineStr">
         <is>
-          <t>Presence of Salmonella</t>
+          <t>Salmonella contamination (serotype identification in progress)</t>
         </is>
       </c>
       <c r="H1034" s="2" t="inlineStr">
@@ -65629,59 +65629,59 @@
       </c>
       <c r="M1034" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21622/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21578/Interne</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B1035" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (FSANZ AU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1035" s="2" t="inlineStr">
         <is>
-          <t>Datah International (Aust) Pty Ltd</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="D1035" s="2" t="inlineStr">
         <is>
-          <t>Vadilal</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E1035" s="2" t="inlineStr">
         <is>
-          <t>Grated Coconut 312g</t>
+          <t>CREVETTES CUITES 30/50</t>
         </is>
       </c>
       <c r="F1035" s="2" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Salmonella spp.</t>
         </is>
       </c>
       <c r="G1035" s="2" t="inlineStr">
         <is>
-          <t>Viral (Hepatitis A) contamination</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H1035" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1035" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1035" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1035" s="2" t="n">
@@ -65692,7 +65692,7 @@
       </c>
       <c r="M1035" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260312_1.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21591/Interne</t>
         </is>
       </c>
     </row>
@@ -65704,47 +65704,47 @@
       </c>
       <c r="B1036" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C1036" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Origin: Brazil | Notifying: Netherlands</t>
         </is>
       </c>
       <c r="D1036" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1036" s="2" t="inlineStr">
         <is>
-          <t>TOMME (RappelConso fiche 21578)</t>
+          <t>Salmonella spp. in poultry meat preparation</t>
         </is>
       </c>
       <c r="F1036" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp.</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1036" s="2" t="inlineStr">
         <is>
-          <t>Salmonella contamination (serotype identification in progress)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="H1036" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1036" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J1036" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1036" s="2" t="n">
@@ -65755,54 +65755,54 @@
       </c>
       <c r="M1036" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21578/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/829727</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B1037" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>CFS (HK)</t>
         </is>
       </c>
       <c r="C1037" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Nutricia (Danone)</t>
         </is>
       </c>
       <c r="D1037" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>BEBIKO nutriFLOR</t>
         </is>
       </c>
       <c r="E1037" s="2" t="inlineStr">
         <is>
-          <t>CREVETTES CUITES 30/50</t>
+          <t>BEBIKO 1 nutriFLOR EXPERT infant formula</t>
         </is>
       </c>
       <c r="F1037" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp.</t>
+          <t>Bacillus cereus / cereulide</t>
         </is>
       </c>
       <c r="G1037" s="2" t="inlineStr">
         <is>
-          <t>Presence of Salmonella</t>
+          <t>CFS Hong Kong import alert mirroring an AFSCA (Belgium) notification: possible cereulide (Bacillus cereus toxin) in BEBIKO 1 nutriFLOR EXPERT infant formula. Distinct product/market from the Aptamil recalls. Cereulide always Tier 1.</t>
         </is>
       </c>
       <c r="H1037" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1037" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="J1037" s="2" t="inlineStr">
@@ -65818,14 +65818,14 @@
       </c>
       <c r="M1037" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21591/Interne</t>
+          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260310_2.pdf</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B1038" s="2" t="inlineStr">
@@ -65835,7 +65835,7 @@
       </c>
       <c r="C1038" s="2" t="inlineStr">
         <is>
-          <t>Origin: Brazil | Notifying: Netherlands</t>
+          <t>Origin: Belgium | Distributed: Luxembourg</t>
         </is>
       </c>
       <c r="D1038" s="2" t="inlineStr">
@@ -65845,32 +65845,32 @@
       </c>
       <c r="E1038" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp. in poultry meat preparation</t>
+          <t>Cooked sausage</t>
         </is>
       </c>
       <c r="F1038" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1038" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H1038" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1038" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="J1038" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1038" s="2" t="n">
@@ -65881,54 +65881,54 @@
       </c>
       <c r="M1038" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/829727</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/829360</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B1039" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1039" s="2" t="inlineStr">
         <is>
-          <t>Nutricia (Danone)</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="D1039" s="2" t="inlineStr">
         <is>
-          <t>BEBIKO nutriFLOR</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E1039" s="2" t="inlineStr">
         <is>
-          <t>BEBIKO 1 nutriFLOR EXPERT infant formula</t>
+          <t>Steak haché</t>
         </is>
       </c>
       <c r="F1039" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus / cereulide</t>
+          <t>Salmonella spp.</t>
         </is>
       </c>
       <c r="G1039" s="2" t="inlineStr">
         <is>
-          <t>CFS Hong Kong import alert mirroring an AFSCA (Belgium) notification: possible cereulide (Bacillus cereus toxin) in BEBIKO 1 nutriFLOR EXPERT infant formula. Distinct product/market from the Aptamil recalls. Cereulide always Tier 1.</t>
+          <t>Presence of Salmonella</t>
         </is>
       </c>
       <c r="H1039" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1039" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1039" s="2" t="inlineStr">
@@ -65944,44 +65944,44 @@
       </c>
       <c r="M1039" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260310_2.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21539/Interne</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B1040" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (FDA US)</t>
+          <t>CFS (HK) - aggregator (RappelConso FR)</t>
         </is>
       </c>
       <c r="C1040" s="2" t="inlineStr">
         <is>
-          <t>Drayton Harbor Oyster Co.</t>
+          <t>AOSTE</t>
         </is>
       </c>
       <c r="D1040" s="2" t="inlineStr">
         <is>
-          <t>Drayton Harbor Oysters</t>
+          <t>AOSTE</t>
         </is>
       </c>
       <c r="E1040" s="2" t="inlineStr">
         <is>
-          <t>Drayton Harbor oysters</t>
+          <t>Cooked ham products</t>
         </is>
       </c>
       <c r="F1040" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1040" s="2" t="inlineStr">
         <is>
-          <t>FDA recall - norovirus contamination in raw oysters.</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H1040" s="2" t="inlineStr">
@@ -65991,75 +65991,75 @@
       </c>
       <c r="I1040" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1040" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1040" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1040" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M1040" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260310_5.pdf</t>
+          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260309_1.pdf</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B1041" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (FDA US)</t>
+          <t>CFS (HK) - aggregator (MHLW Japan)</t>
         </is>
       </c>
       <c r="C1041" s="2" t="inlineStr">
         <is>
-          <t>— (Drayton Harbor)</t>
+          <t>UCC Ueshima Coffee</t>
         </is>
       </c>
       <c r="D1041" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UCC BEANS&amp;ROASTERS</t>
         </is>
       </c>
       <c r="E1041" s="2" t="inlineStr">
         <is>
-          <t>Certain oysters and Manila clams from Drayton Harbor, Washington</t>
+          <t>UCC BEANS&amp;ROASTERS Cafe Latte リキャップ缶 375g</t>
         </is>
       </c>
       <c r="F1041" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Inadequate sterilization (microbiological hazard)</t>
         </is>
       </c>
       <c r="G1041" s="2" t="inlineStr">
         <is>
-          <t>Possible norovirus contamination</t>
+          <t>Inadequate sterilization process</t>
         </is>
       </c>
       <c r="H1041" s="2" t="inlineStr">
         <is>
-          <t>Public advisory</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1041" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="J1041" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia-Pacific</t>
         </is>
       </c>
       <c r="K1041" s="2" t="n">
@@ -66070,117 +66070,117 @@
       </c>
       <c r="M1041" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260310_3.pdf</t>
+          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260309_2.pdf</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B1042" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1042" s="2" t="inlineStr">
         <is>
-          <t>Origin: Belgium | Distributed: Luxembourg</t>
+          <t>Drayton Harbor Oyster Co. / Lummi Indian Business Council</t>
         </is>
       </c>
       <c r="D1042" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Drayton Harbor</t>
         </is>
       </c>
       <c r="E1042" s="2" t="inlineStr">
         <is>
-          <t>Cooked sausage</t>
+          <t>Raw oysters (WA-1723-SS) + Manila clams (WA-0098-SS); harvest 2/13-3/3/2026</t>
         </is>
       </c>
       <c r="F1042" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Norovirus</t>
         </is>
       </c>
       <c r="G1042" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1042" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="I1042" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1042" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1042" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1042" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1042" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/829360</t>
+          <t>https://www.fda.gov/food/alerts-advisories-safety-information/fda-advises-restaurants-and-retailers-not-serve-or-sell-and-consumers-not-eat-certain-oysters-and</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B1043" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C1043" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Origin: Unknown | Distributed: Unknown</t>
         </is>
       </c>
       <c r="D1043" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1043" s="2" t="inlineStr">
         <is>
-          <t>Steak haché</t>
+          <t>Meat products</t>
         </is>
       </c>
       <c r="F1043" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp.</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1043" s="2" t="inlineStr">
         <is>
-          <t>Presence of Salmonella</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1043" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1043" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J1043" s="2" t="inlineStr">
@@ -66196,44 +66196,44 @@
       </c>
       <c r="M1043" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21539/Interne</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/828968</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B1044" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (RappelConso FR)</t>
+          <t>NCC (ZA)</t>
         </is>
       </c>
       <c r="C1044" s="2" t="inlineStr">
         <is>
-          <t>AOSTE</t>
+          <t>Nutricia Southern Africa (Danone)</t>
         </is>
       </c>
       <c r="D1044" s="2" t="inlineStr">
         <is>
-          <t>AOSTE</t>
+          <t>Aptamil Nutribiotik / Aptajunior Nutribiotik</t>
         </is>
       </c>
       <c r="E1044" s="2" t="inlineStr">
         <is>
-          <t>Cooked ham products</t>
+          <t>Aptamil Nutribiotik 2 (800g) batches 20260911 &amp; 20261209; Aptajunior Nutribiotik 3 (800g) batch 20261209. 2,989 units; sold at Dis-Chem &amp; Clicks; distributed by United Pharmaceutical; exported to Botswana &amp; Namibia.</t>
         </is>
       </c>
       <c r="F1044" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Bacillus cereus / cereulide</t>
         </is>
       </c>
       <c r="G1044" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes</t>
+          <t>NCC (South Africa) national recall: raw material used in production may carry traces of cereulide (heat-stable Bacillus cereus toxin). Gazette notice NCC-IF-2026-03-07. Cereulide always Tier 1.</t>
         </is>
       </c>
       <c r="H1044" s="2" t="inlineStr">
@@ -66243,12 +66243,12 @@
       </c>
       <c r="I1044" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="J1044" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="K1044" s="2" t="n">
@@ -66259,122 +66259,122 @@
       </c>
       <c r="M1044" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260309_1.pdf</t>
+          <t>https://thencc.org.za/product-safety-recall-nutricia-aptamil-nutribiotik-2-and-nutricia-aptajunior-nutribiotik-3/</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B1045" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (MHLW Japan)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1045" s="2" t="inlineStr">
         <is>
-          <t>UCC Ueshima Coffee</t>
+          <t>AOSTE SNC</t>
         </is>
       </c>
       <c r="D1045" s="2" t="inlineStr">
         <is>
-          <t>UCC BEANS&amp;ROASTERS</t>
+          <t>AOSTE</t>
         </is>
       </c>
       <c r="E1045" s="2" t="inlineStr">
         <is>
-          <t>UCC BEANS&amp;ROASTERS Cafe Latte リキャップ缶 375g</t>
+          <t>Jambon cuit supérieur cuisiné à l'os 4 tranches 260g AOSTE</t>
         </is>
       </c>
       <c r="F1045" s="2" t="inlineStr">
         <is>
-          <t>Inadequate sterilization (microbiological hazard)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1045" s="2" t="inlineStr">
         <is>
-          <t>Inadequate sterilization process</t>
+          <t>Presence of Listeria monocytogenes</t>
         </is>
       </c>
       <c r="H1045" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1045" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1045" s="2" t="inlineStr">
         <is>
-          <t>Asia-Pacific</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1045" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1045" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M1045" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260309_2.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21548/Interne</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B1046" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>FSANZ (AU)</t>
         </is>
       </c>
       <c r="C1046" s="2" t="inlineStr">
         <is>
-          <t>Drayton Harbor Oyster Co. / Lummi Indian Business Council</t>
+          <t>Bajaria Global Pty Ltd T/a The Spice Merchants</t>
         </is>
       </c>
       <c r="D1046" s="2" t="inlineStr">
         <is>
-          <t>Drayton Harbor</t>
+          <t>Bajaria Global Pty Ltd T/a The Spice Merchants</t>
         </is>
       </c>
       <c r="E1046" s="2" t="inlineStr">
         <is>
-          <t>Raw oysters (WA-1723-SS) + Manila clams (WA-0098-SS); harvest 2/13-3/3/2026</t>
+          <t>Fresh 'N' Frozen Favour-ita Grated Coconut 400g | Food Standards Australia New Zealand</t>
         </is>
       </c>
       <c r="F1046" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Hepatitis A virus</t>
         </is>
       </c>
       <c r="G1046" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Hepatitis A — outbreak</t>
         </is>
       </c>
       <c r="H1046" s="2" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1046" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="J1046" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K1046" s="2" t="n">
@@ -66385,54 +66385,54 @@
       </c>
       <c r="M1046" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/food/alerts-advisories-safety-information/fda-advises-restaurants-and-retailers-not-serve-or-sell-and-consumers-not-eat-certain-oysters-and</t>
+          <t>https://www.foodstandards.gov.au/food-recalls/recall-alert/bajaria-global-pty-ltd-ta-spice-merchants-fresh-n-frozen-favour-ita</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" s="2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B1047" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1047" s="2" t="inlineStr">
         <is>
-          <t>Origin: Unknown | Distributed: Unknown</t>
+          <t>Pedavia</t>
         </is>
       </c>
       <c r="D1047" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pedavia</t>
         </is>
       </c>
       <c r="E1047" s="2" t="inlineStr">
         <is>
-          <t>Meat products</t>
+          <t>Minced veal preparation sv OF</t>
         </is>
       </c>
       <c r="F1047" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1047" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Salmonella detected in 10 g sample</t>
         </is>
       </c>
       <c r="H1047" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1047" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1047" s="2" t="inlineStr">
@@ -66448,117 +66448,117 @@
       </c>
       <c r="M1047" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/828968</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21467/Interne</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B1048" s="2" t="inlineStr">
         <is>
-          <t>NCC (ZA)</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C1048" s="2" t="inlineStr">
         <is>
-          <t>Nutricia Southern Africa (Danone)</t>
+          <t>Sacor (Compleat Food Group)</t>
         </is>
       </c>
       <c r="D1048" s="2" t="inlineStr">
         <is>
-          <t>Aptamil Nutribiotik / Aptajunior Nutribiotik</t>
+          <t>Bastides</t>
         </is>
       </c>
       <c r="E1048" s="2" t="inlineStr">
         <is>
-          <t>Aptamil Nutribiotik 2 (800g) batches 20260911 &amp; 20261209; Aptajunior Nutribiotik 3 (800g) batch 20261209. 2,989 units; sold at Dis-Chem &amp; Clicks; distributed by United Pharmaceutical; exported to Botswana &amp; Namibia.</t>
+          <t>Saucisson Sec 200 g — Tesco-exclusive</t>
         </is>
       </c>
       <c r="F1048" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus / cereulide</t>
+          <t>Salmonella Typhimurium</t>
         </is>
       </c>
       <c r="G1048" s="2" t="inlineStr">
         <is>
-          <t>NCC (South Africa) national recall: raw material used in production may carry traces of cereulide (heat-stable Bacillus cereus toxin). Gazette notice NCC-IF-2026-03-07. Cereulide always Tier 1.</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H1048" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1048" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J1048" s="2" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1048" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1048" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1048" s="2" t="inlineStr">
         <is>
-          <t>https://thencc.org.za/product-safety-recall-nutricia-aptamil-nutribiotik-2-and-nutricia-aptajunior-nutribiotik-3/</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-11-2026</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B1049" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>CFS (HK) - aggregator (Czech)</t>
         </is>
       </c>
       <c r="C1049" s="2" t="inlineStr">
         <is>
-          <t>AOSTE SNC</t>
+          <t>Czech Agriculture &amp; Food Inspection</t>
         </is>
       </c>
       <c r="D1049" s="2" t="inlineStr">
         <is>
-          <t>AOSTE</t>
+          <t>Happy Mimi 1</t>
         </is>
       </c>
       <c r="E1049" s="2" t="inlineStr">
         <is>
-          <t>Jambon cuit supérieur cuisiné à l'os 4 tranches 260g AOSTE</t>
+          <t>Happy Mimi 1 infant formula (single batch)</t>
         </is>
       </c>
       <c r="F1049" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Bacillus cereus / cereulide</t>
         </is>
       </c>
       <c r="G1049" s="2" t="inlineStr">
         <is>
-          <t>Presence of Listeria monocytogenes</t>
+          <t>Possible cereulide presence</t>
         </is>
       </c>
       <c r="H1049" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1049" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="J1049" s="2" t="inlineStr">
@@ -66574,44 +66574,44 @@
       </c>
       <c r="M1049" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21548/Interne</t>
+          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260302_1.pdf</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B1050" s="2" t="inlineStr">
         <is>
-          <t>FSANZ (AU)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1050" s="2" t="inlineStr">
         <is>
-          <t>Bajaria Global Pty Ltd T/a The Spice Merchants</t>
+          <t>Various macadamia nuts and macadamia nut-containing products</t>
         </is>
       </c>
       <c r="D1050" s="2" t="inlineStr">
         <is>
-          <t>Bajaria Global Pty Ltd T/a The Spice Merchants</t>
+          <t>Various macadamia nuts and macadamia nut-containing products</t>
         </is>
       </c>
       <c r="E1050" s="2" t="inlineStr">
         <is>
-          <t>Fresh 'N' Frozen Favour-ita Grated Coconut 400g | Food Standards Australia New Zealand</t>
+          <t>due to Salmonella - Canada.ca</t>
         </is>
       </c>
       <c r="F1050" s="2" t="inlineStr">
         <is>
-          <t>Hepatitis A virus</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1050" s="2" t="inlineStr">
         <is>
-          <t>Hepatitis A — outbreak</t>
+          <t>Salmonella — outbreak</t>
         </is>
       </c>
       <c r="H1050" s="2" t="inlineStr">
@@ -66621,12 +66621,12 @@
       </c>
       <c r="I1050" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1050" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1050" s="2" t="n">
@@ -66637,14 +66637,14 @@
       </c>
       <c r="M1050" s="2" t="inlineStr">
         <is>
-          <t>https://www.foodstandards.gov.au/food-recalls/recall-alert/bajaria-global-pty-ltd-ta-spice-merchants-fresh-n-frozen-favour-ita</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/various-macadamia-nuts-and-macadamia-nut-containing-products-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B1051" s="2" t="inlineStr">
@@ -66654,17 +66654,17 @@
       </c>
       <c r="C1051" s="2" t="inlineStr">
         <is>
-          <t>Pedavia</t>
+          <t>PALMI D'OR BOURGOGNE PALMID'OR BOURGOGNE</t>
         </is>
       </c>
       <c r="D1051" s="2" t="inlineStr">
         <is>
-          <t>Pedavia</t>
+          <t>NEUTRE</t>
         </is>
       </c>
       <c r="E1051" s="2" t="inlineStr">
         <is>
-          <t>Minced veal preparation sv OF</t>
+          <t>Duck fillets in 5% brine — extra tender vacuum-packed (Lot 2)</t>
         </is>
       </c>
       <c r="F1051" s="2" t="inlineStr">
@@ -66674,7 +66674,7 @@
       </c>
       <c r="G1051" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in 10 g sample</t>
+          <t>Salmonella detected</t>
         </is>
       </c>
       <c r="H1051" s="2" t="inlineStr">
@@ -66700,54 +66700,54 @@
       </c>
       <c r="M1051" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21467/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21437/Interne</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B1052" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1052" s="2" t="inlineStr">
         <is>
-          <t>Sacor (Compleat Food Group)</t>
+          <t>Teba 44</t>
         </is>
       </c>
       <c r="D1052" s="2" t="inlineStr">
         <is>
-          <t>Bastides</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E1052" s="2" t="inlineStr">
         <is>
-          <t>Saucisson Sec 200 g — Tesco-exclusive</t>
+          <t>Garlic saucisson BIO Ferme du Doiterneau (lot 040326041002, use-by 2026-03-11)</t>
         </is>
       </c>
       <c r="F1052" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Typhimurium</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1052" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Salmonella detected</t>
         </is>
       </c>
       <c r="H1052" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1052" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1052" s="2" t="inlineStr">
@@ -66759,38 +66759,38 @@
         <v>1</v>
       </c>
       <c r="L1052" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1052" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-11-2026</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21410/Interne</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B1053" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (UK FSA)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1053" s="2" t="inlineStr">
         <is>
-          <t>Sacor</t>
+          <t>Etablissements Monfort</t>
         </is>
       </c>
       <c r="D1053" s="2" t="inlineStr">
         <is>
-          <t>Bastides</t>
+          <t>Monfort Viandes</t>
         </is>
       </c>
       <c r="E1053" s="2" t="inlineStr">
         <is>
-          <t>Saucisson Sec</t>
+          <t>6 ground beef steaks 15% fat 100 g (GTIN 3361114015067, lot 980/605103201, use-by 2026-02-27)</t>
         </is>
       </c>
       <c r="F1053" s="2" t="inlineStr">
@@ -66800,17 +66800,17 @@
       </c>
       <c r="G1053" s="2" t="inlineStr">
         <is>
-          <t>Salmonella contamination</t>
+          <t>Salmonella detected</t>
         </is>
       </c>
       <c r="H1053" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1053" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1053" s="2" t="inlineStr">
@@ -66826,54 +66826,54 @@
       </c>
       <c r="M1053" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260303_1.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21419/Interne</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B1054" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK) - aggregator (Czech)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>Czech Agriculture &amp; Food Inspection</t>
+          <t>Eleveurs de Bretagne</t>
         </is>
       </c>
       <c r="D1054" s="2" t="inlineStr">
         <is>
-          <t>Happy Mimi 1</t>
+          <t>Eleveurs de Bretagne</t>
         </is>
       </c>
       <c r="E1054" s="2" t="inlineStr">
         <is>
-          <t>Happy Mimi 1 infant formula (single batch)</t>
+          <t>Ground beef steak 15% NEBH</t>
         </is>
       </c>
       <c r="F1054" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus / cereulide</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1054" s="2" t="inlineStr">
         <is>
-          <t>Possible cereulide presence</t>
+          <t>Salmonella detected</t>
         </is>
       </c>
       <c r="H1054" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1054" s="2" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1054" s="2" t="inlineStr">
@@ -66889,34 +66889,34 @@
       </c>
       <c r="M1054" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/rc/subject/files/20260302_1.pdf</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21418/Interne</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B1055" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1055" s="2" t="inlineStr">
         <is>
-          <t>Various macadamia nuts and macadamia nut-containing products</t>
+          <t>SCHILDIS E.LECLERC</t>
         </is>
       </c>
       <c r="D1055" s="2" t="inlineStr">
         <is>
-          <t>Various macadamia nuts and macadamia nut-containing products</t>
+          <t>E.Leclerc Schiltigheim</t>
         </is>
       </c>
       <c r="E1055" s="2" t="inlineStr">
         <is>
-          <t>due to Salmonella - Canada.ca</t>
+          <t>Chicken fillet (lots Nollens 16.02 LCFEGKND10, use-by from 2026-02-20)</t>
         </is>
       </c>
       <c r="F1055" s="2" t="inlineStr">
@@ -66926,40 +66926,40 @@
       </c>
       <c r="G1055" s="2" t="inlineStr">
         <is>
-          <t>Salmonella — outbreak</t>
+          <t>Salmonella detected</t>
         </is>
       </c>
       <c r="H1055" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1055" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1055" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1055" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1055" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1055" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/various-macadamia-nuts-and-macadamia-nut-containing-products-recalled-due-salmonella</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21416/Interne</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B1056" s="2" t="inlineStr">
@@ -66969,17 +66969,17 @@
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>PALMI D'OR BOURGOGNE PALMID'OR BOURGOGNE</t>
+          <t>SARL COMMENGES</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr">
         <is>
-          <t>NEUTRE</t>
+          <t>CHARCUTERIE COMMENGES</t>
         </is>
       </c>
       <c r="E1056" s="2" t="inlineStr">
         <is>
-          <t>Duck fillets in 5% brine — extra tender vacuum-packed (Lot 2)</t>
+          <t>Dry liver sausage</t>
         </is>
       </c>
       <c r="F1056" s="2" t="inlineStr">
@@ -67015,122 +67015,122 @@
       </c>
       <c r="M1056" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21437/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21344/Interne</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B1057" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1057" s="2" t="inlineStr">
         <is>
-          <t>Teba 44</t>
+          <t>Saputo USA</t>
         </is>
       </c>
       <c r="D1057" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>Great Value (Walmart)</t>
         </is>
       </c>
       <c r="E1057" s="2" t="inlineStr">
         <is>
-          <t>Garlic saucisson BIO Ferme du Doiterneau (lot 040326041002, use-by 2026-03-11)</t>
+          <t>Cottage Cheese (24 states)</t>
         </is>
       </c>
       <c r="F1057" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Possible incomplete pasteurization (process deviation)</t>
         </is>
       </c>
       <c r="G1057" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected</t>
+          <t>Possible health risk — product may not have been fully pasteurized</t>
         </is>
       </c>
       <c r="H1057" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I1057" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1057" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1057" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L1057" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M1057" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21410/Interne</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/saputo-usa-recalls-great-value-cottage-cheese-because-possible-health-risk</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B1058" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>Etablissements Monfort</t>
+          <t>Elite Treats, LLC</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr">
         <is>
-          <t>Monfort Viandes</t>
+          <t>Elite Treats</t>
         </is>
       </c>
       <c r="E1058" s="2" t="inlineStr">
         <is>
-          <t>6 ground beef steaks 15% fat 100 g (GTIN 3361114015067, lot 980/605103201, use-by 2026-02-27)</t>
+          <t>Chicken Chips for Dogs (6 oz, lot 24045) - PET FOOD</t>
         </is>
       </c>
       <c r="F1058" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Salmonella spp.</t>
         </is>
       </c>
       <c r="G1058" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1058" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I1058" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1058" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1058" s="2" t="n">
@@ -67141,14 +67141,14 @@
       </c>
       <c r="M1058" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21419/Interne</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/elite-treats-llc-recalls-single-lot-chicken-chips-due-salmonella-contamination</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B1059" s="2" t="inlineStr">
@@ -67158,17 +67158,17 @@
       </c>
       <c r="C1059" s="2" t="inlineStr">
         <is>
-          <t>Eleveurs de Bretagne</t>
+          <t>Etablissements Monfort</t>
         </is>
       </c>
       <c r="D1059" s="2" t="inlineStr">
         <is>
-          <t>Eleveurs de Bretagne</t>
+          <t>Monfort Viandes</t>
         </is>
       </c>
       <c r="E1059" s="2" t="inlineStr">
         <is>
-          <t>Ground beef steak 15% NEBH</t>
+          <t>Ground beef steak 15% fat 8x125 g</t>
         </is>
       </c>
       <c r="F1059" s="2" t="inlineStr">
@@ -67204,14 +67204,14 @@
       </c>
       <c r="M1059" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21418/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21395/Interne</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B1060" s="2" t="inlineStr">
@@ -67221,17 +67221,17 @@
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>SCHILDIS E.LECLERC</t>
+          <t>Etablissements Monfort</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr">
         <is>
-          <t>E.Leclerc Schiltigheim</t>
+          <t>Monfort Viandes</t>
         </is>
       </c>
       <c r="E1060" s="2" t="inlineStr">
         <is>
-          <t>Chicken fillet (lots Nollens 16.02 LCFEGKND10, use-by from 2026-02-20)</t>
+          <t>Round ground beef steak 15% fat 8x125 g</t>
         </is>
       </c>
       <c r="F1060" s="2" t="inlineStr">
@@ -67267,14 +67267,14 @@
       </c>
       <c r="M1060" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21416/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21393/Interne</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B1061" s="2" t="inlineStr">
@@ -67284,17 +67284,17 @@
       </c>
       <c r="C1061" s="2" t="inlineStr">
         <is>
-          <t>SARL COMMENGES</t>
+          <t>Etablissements Monfort</t>
         </is>
       </c>
       <c r="D1061" s="2" t="inlineStr">
         <is>
-          <t>CHARCUTERIE COMMENGES</t>
+          <t>Monfort Viandes</t>
         </is>
       </c>
       <c r="E1061" s="2" t="inlineStr">
         <is>
-          <t>Dry liver sausage</t>
+          <t>Round ground beef steak 15% fat — Valtero Bretagne</t>
         </is>
       </c>
       <c r="F1061" s="2" t="inlineStr">
@@ -67330,122 +67330,122 @@
       </c>
       <c r="M1061" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21344/Interne</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21391/Interne</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B1062" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>Saputo USA</t>
+          <t>Rosabella</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr">
         <is>
-          <t>Great Value (Walmart)</t>
+          <t>Rosabella</t>
         </is>
       </c>
       <c r="E1062" s="2" t="inlineStr">
         <is>
-          <t>Cottage Cheese (24 states)</t>
+          <t>Moringa capsules</t>
         </is>
       </c>
       <c r="F1062" s="2" t="inlineStr">
         <is>
-          <t>Possible incomplete pasteurization (process deviation)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1062" s="2" t="inlineStr">
         <is>
-          <t>Possible health risk — product may not have been fully pasteurized</t>
+          <t>Possible presence of Salmonella</t>
         </is>
       </c>
       <c r="H1062" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1062" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J1062" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1062" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1062" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M1062" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/saputo-usa-recalls-great-value-cottage-cheese-because-possible-health-risk</t>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-specific-batches-of-rosabella-moringa-capsules</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B1063" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C1063" s="2" t="inlineStr">
         <is>
-          <t>Elite Treats, LLC</t>
+          <t>Ambrosia Brands, LLC</t>
         </is>
       </c>
       <c r="D1063" s="2" t="inlineStr">
         <is>
-          <t>Elite Treats</t>
+          <t>Rosabella Moringa</t>
         </is>
       </c>
       <c r="E1063" s="2" t="inlineStr">
         <is>
-          <t>Chicken Chips for Dogs (6 oz, lot 24045) - PET FOOD</t>
+          <t>Rosabella Moringa 100% Pure capsules</t>
         </is>
       </c>
       <c r="F1063" s="2" t="inlineStr">
         <is>
-          <t>Salmonella spp.</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1063" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Container of Rosabella Moringa capsules</t>
         </is>
       </c>
       <c r="H1063" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1063" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J1063" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1063" s="2" t="n">
@@ -67456,59 +67456,59 @@
       </c>
       <c r="M1063" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/elite-treats-llc-recalls-single-lot-chicken-chips-due-salmonella-contamination</t>
+          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-specific-batches-of-rosabella-moringa-ca</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B1064" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>Etablissements Monfort</t>
+          <t>Made Fresh Salads, Inc.</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr">
         <is>
-          <t>Monfort Viandes</t>
+          <t>Made Fresh Salads</t>
         </is>
       </c>
       <c r="E1064" s="2" t="inlineStr">
         <is>
-          <t>Ground beef steak 15% fat 8x125 g</t>
+          <t>Cream cheese assorted flavors + tofu spread (5 lb tubs)</t>
         </is>
       </c>
       <c r="F1064" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1064" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1064" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1064" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1064" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1064" s="2" t="n">
@@ -67519,59 +67519,59 @@
       </c>
       <c r="M1064" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21395/Interne</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/made-fresh-salads-inc-recalls-assorted-flavors-cream-cheese-because-possible-health-risk</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B1065" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>COFEPRIS (MX)</t>
         </is>
       </c>
       <c r="C1065" s="2" t="inlineStr">
         <is>
-          <t>Etablissements Monfort</t>
+          <t>SANULAC NUTRICIÓN MÉXICO S. de R.L. de C.V.</t>
         </is>
       </c>
       <c r="D1065" s="2" t="inlineStr">
         <is>
-          <t>Monfort Viandes</t>
+          <t>ALULA Gold</t>
         </is>
       </c>
       <c r="E1065" s="2" t="inlineStr">
         <is>
-          <t>Round ground beef steak 15% fat 8x125 g</t>
+          <t>ALULA Gold infant formula — sanitary alert update</t>
         </is>
       </c>
       <c r="F1065" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Bacillus cereus / cereulide</t>
         </is>
       </c>
       <c r="G1065" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected</t>
+          <t>Reinforced action of 2026-01-23 due to possible cereulide contamination</t>
         </is>
       </c>
       <c r="H1065" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Sanitary alert (update)</t>
         </is>
       </c>
       <c r="I1065" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="J1065" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1065" s="2" t="n">
@@ -67582,34 +67582,34 @@
       </c>
       <c r="M1065" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21393/Interne</t>
+          <t>https://www.unotv.com/salud/cofepris-actualiza-alerta-por-formulas-para-bebes-advirte-que-representan-un-riesgo-para-la-salud/</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B1066" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>Etablissements Monfort</t>
+          <t>Jabbour Export/Import Ltd.</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr">
         <is>
-          <t>Monfort Viandes</t>
+          <t>Mahrousa</t>
         </is>
       </c>
       <c r="E1066" s="2" t="inlineStr">
         <is>
-          <t>Round ground beef steak 15% fat — Valtero Bretagne</t>
+          <t>Tahini 800 g</t>
         </is>
       </c>
       <c r="F1066" s="2" t="inlineStr">
@@ -67619,22 +67619,22 @@
       </c>
       <c r="G1066" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1066" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I1066" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1066" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1066" s="2" t="n">
@@ -67645,34 +67645,34 @@
       </c>
       <c r="M1066" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21391/Interne</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/mahrousa-brand-tahini-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B1067" s="2" t="inlineStr">
         <is>
-          <t>FSAI (IE)</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C1067" s="2" t="inlineStr">
         <is>
-          <t>Rosabella</t>
+          <t>Tesco</t>
         </is>
       </c>
       <c r="D1067" s="2" t="inlineStr">
         <is>
-          <t>Rosabella</t>
+          <t>Tesco</t>
         </is>
       </c>
       <c r="E1067" s="2" t="inlineStr">
         <is>
-          <t>Moringa capsules</t>
+          <t>Grape &amp; Berry Medley 230 g</t>
         </is>
       </c>
       <c r="F1067" s="2" t="inlineStr">
@@ -67682,17 +67682,17 @@
       </c>
       <c r="G1067" s="2" t="inlineStr">
         <is>
-          <t>Possible presence of Salmonella</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1067" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1067" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J1067" s="2" t="inlineStr">
@@ -67708,19 +67708,19 @@
       </c>
       <c r="M1067" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-specific-batches-of-rosabella-moringa-capsules</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-10-2026</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B1068" s="2" t="inlineStr">
         <is>
-          <t>FSAI (IE)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1068" s="2" t="inlineStr">
@@ -67730,163 +67730,163 @@
       </c>
       <c r="D1068" s="2" t="inlineStr">
         <is>
-          <t>Rosabella Moringa</t>
+          <t>Rosabella</t>
         </is>
       </c>
       <c r="E1068" s="2" t="inlineStr">
         <is>
-          <t>Rosabella Moringa 100% Pure capsules</t>
+          <t>Pure Organic Moringa Powder Capsules 800 mg</t>
         </is>
       </c>
       <c r="F1068" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Salmonella Newport</t>
         </is>
       </c>
       <c r="G1068" s="2" t="inlineStr">
         <is>
-          <t>Container of Rosabella Moringa capsules</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H1068" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1068" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1068" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1068" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1068" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1068" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/food-alerts/recall-of-specific-batches-of-rosabella-moringa-ca</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/ambrosia-brands-llc-recalls-rosabella-moringa-capsules-because-possible-health-risk</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B1069" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C1069" s="2" t="inlineStr">
         <is>
-          <t>Made Fresh Salads, Inc.</t>
+          <t>Origin: France | Notifying: unknown | Distributed: unknown</t>
         </is>
       </c>
       <c r="D1069" s="2" t="inlineStr">
         <is>
-          <t>Made Fresh Salads</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1069" s="2" t="inlineStr">
         <is>
-          <t>Cream cheese assorted flavors + tofu spread (5 lb tubs)</t>
+          <t>Oysters from France</t>
         </is>
       </c>
       <c r="F1069" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Norovirus</t>
         </is>
       </c>
       <c r="G1069" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Norovirus detected in oysters of French origin</t>
         </is>
       </c>
       <c r="H1069" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1069" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1069" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1069" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L1069" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M1069" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/made-fresh-salads-inc-recalls-assorted-flavors-cream-cheese-because-possible-health-risk</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/822538</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B1070" s="2" t="inlineStr">
         <is>
-          <t>COFEPRIS (MX)</t>
+          <t>FSANZ (AU)</t>
         </is>
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>SANULAC NUTRICIÓN MÉXICO S. de R.L. de C.V.</t>
+          <t>La Vera Group Pty Ltd</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr">
         <is>
-          <t>ALULA Gold</t>
+          <t>La Vera</t>
         </is>
       </c>
       <c r="E1070" s="2" t="inlineStr">
         <is>
-          <t>ALULA Gold infant formula — sanitary alert update</t>
+          <t>La Vera Fresh Ricotta 500 g</t>
         </is>
       </c>
       <c r="F1070" s="2" t="inlineStr">
         <is>
-          <t>Bacillus cereus / cereulide</t>
+          <t>E. coli</t>
         </is>
       </c>
       <c r="G1070" s="2" t="inlineStr">
         <is>
-          <t>Reinforced action of 2026-01-23 due to possible cereulide contamination</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1070" s="2" t="inlineStr">
         <is>
-          <t>Sanitary alert (update)</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1070" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="J1070" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K1070" s="2" t="n">
@@ -67897,14 +67897,14 @@
       </c>
       <c r="M1070" s="2" t="inlineStr">
         <is>
-          <t>https://www.unotv.com/salud/cofepris-actualiza-alerta-por-formulas-para-bebes-advirte-que-representan-un-riesgo-para-la-salud/</t>
+          <t>https://www.foodstandards.gov.au/food-recalls/recall-alert/la-vera-group-pty-ltd-trading-la-vera-cheese-la-vera-fresh-ricotta-500g</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B1071" s="2" t="inlineStr">
@@ -67914,32 +67914,32 @@
       </c>
       <c r="C1071" s="2" t="inlineStr">
         <is>
-          <t>Jabbour Export/Import Ltd.</t>
+          <t>Stellar Bay Shellfish Ltd.</t>
         </is>
       </c>
       <c r="D1071" s="2" t="inlineStr">
         <is>
-          <t>Mahrousa</t>
+          <t>Kusshi / Chrome Point / Stellar Bay</t>
         </is>
       </c>
       <c r="E1071" s="2" t="inlineStr">
         <is>
-          <t>Tahini 800 g</t>
+          <t>Oysters from BC harvest area BC 17-20</t>
         </is>
       </c>
       <c r="F1071" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Norovirus</t>
         </is>
       </c>
       <c r="G1071" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H1071" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I1071" s="2" t="inlineStr">
@@ -67956,63 +67956,63 @@
         <v>1</v>
       </c>
       <c r="L1071" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1071" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/mahrousa-brand-tahini-recalled-due-salmonella</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/certain-stellar-bay-shellfish-brand-oysters-recalled-due-norovirus-0</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B1072" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>USDA FSIS</t>
         </is>
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>Tesco</t>
+          <t>CS Beef Packers, LLC (Kuna, ID)</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr">
         <is>
-          <t>Tesco</t>
+          <t>Fire River Farms / Beef 73L</t>
         </is>
       </c>
       <c r="E1072" s="2" t="inlineStr">
         <is>
-          <t>Grape &amp; Berry Medley 230 g</t>
+          <t>Raw ground beef ~22,912 lbs (EST 630)</t>
         </is>
       </c>
       <c r="F1072" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>E. coli O145 (STEC)</t>
         </is>
       </c>
       <c r="G1072" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>STEC contamination</t>
         </is>
       </c>
       <c r="H1072" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1072" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1072" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1072" s="2" t="n">
@@ -68023,14 +68023,14 @@
       </c>
       <c r="M1072" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-10-2026</t>
+          <t>https://www.fsis.usda.gov/recalls-alerts/cs-beef-packers-llc-recalls-ground-beef-products-may-be-contaminated-e--coli-o145</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B1073" s="2" t="inlineStr">
@@ -68040,32 +68040,32 @@
       </c>
       <c r="C1073" s="2" t="inlineStr">
         <is>
-          <t>Ambrosia Brands, LLC</t>
+          <t>Slade Gorton &amp; Co., Inc.</t>
         </is>
       </c>
       <c r="D1073" s="2" t="inlineStr">
         <is>
-          <t>Rosabella</t>
+          <t>Wellsley Farms</t>
         </is>
       </c>
       <c r="E1073" s="2" t="inlineStr">
         <is>
-          <t>Pure Organic Moringa Powder Capsules 800 mg</t>
+          <t>Farm-Raised Atlantic Salmon, 2-lb bags (sold at BJ's Wholesale Club)</t>
         </is>
       </c>
       <c r="F1073" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Newport</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1073" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1073" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I1073" s="2" t="inlineStr">
@@ -68082,126 +68082,126 @@
         <v>1</v>
       </c>
       <c r="L1073" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1073" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/ambrosia-brands-llc-recalls-rosabella-moringa-capsules-because-possible-health-risk</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/slade-gorton-co-inc-recalls-one-lot-wellsley-farms-farm-raised-atlantic-salmon-sold-bjs-wholesale</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B1074" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>Origin: France | Notifying: unknown | Distributed: unknown</t>
+          <t>Phoenicia Group Inc.</t>
         </is>
       </c>
       <c r="D1074" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Al Kanater</t>
         </is>
       </c>
       <c r="E1074" s="2" t="inlineStr">
         <is>
-          <t>Oysters from France</t>
+          <t>Halawa with Pistachio (450 g)</t>
         </is>
       </c>
       <c r="F1074" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1074" s="2" t="inlineStr">
         <is>
-          <t>Norovirus detected in oysters of French origin</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1074" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I1074" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1074" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1074" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1074" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M1074" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/822538</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/al-kanater-brand-halawa-pistachio-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B1075" s="2" t="inlineStr">
         <is>
-          <t>FSANZ (AU)</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1075" s="2" t="inlineStr">
         <is>
-          <t>La Vera Group Pty Ltd</t>
+          <t>PLUKON MAASMECHELEN Plukon Maasmechelen NV</t>
         </is>
       </c>
       <c r="D1075" s="2" t="inlineStr">
         <is>
-          <t>La Vera</t>
+          <t>Unbranded</t>
         </is>
       </c>
       <c r="E1075" s="2" t="inlineStr">
         <is>
-          <t>La Vera Fresh Ricotta 500 g</t>
+          <t>Chicken filet 1 kg, chicken aiguillettes 500 g, chicken filet 2.5 kg, à la minute filet 600 g, halal chicken filet 4×2.5 kg, halal chicken filet 1 kg, chicken aiguillettes 1000 g (multi-SKU plastic trays)</t>
         </is>
       </c>
       <c r="F1075" s="2" t="inlineStr">
         <is>
-          <t>E. coli</t>
+          <t>Salmonella Enteritidis</t>
         </is>
       </c>
       <c r="G1075" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Salmonella Enteritidis (causative agent of salmonellosis)</t>
         </is>
       </c>
       <c r="H1075" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1075" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1075" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1075" s="2" t="n">
@@ -68212,117 +68212,117 @@
       </c>
       <c r="M1075" s="2" t="inlineStr">
         <is>
-          <t>https://www.foodstandards.gov.au/food-recalls/recall-alert/la-vera-group-pty-ltd-trading-la-vera-cheese-la-vera-fresh-ricotta-500g</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/21234/Interne</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B1076" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>Stellar Bay Shellfish Ltd.</t>
+          <t>Danone</t>
         </is>
       </c>
       <c r="D1076" s="2" t="inlineStr">
         <is>
-          <t>Kusshi / Chrome Point / Stellar Bay</t>
+          <t>Danone</t>
         </is>
       </c>
       <c r="E1076" s="2" t="inlineStr">
         <is>
-          <t>Oysters from BC harvest area BC 17-20</t>
+          <t>several Aptamil and Cow &amp; Gate First Infant Milk and Follow on Milk formula products</t>
         </is>
       </c>
       <c r="F1076" s="2" t="inlineStr">
         <is>
-          <t>Norovirus</t>
+          <t>Cereulide (B. cereus toxin)</t>
         </is>
       </c>
       <c r="G1076" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="H1076" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1076" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J1076" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1076" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1076" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1076" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/certain-stellar-bay-shellfish-brand-oysters-recalled-due-norovirus-0</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-05-2026</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B1077" s="2" t="inlineStr">
         <is>
-          <t>USDA FSIS</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1077" s="2" t="inlineStr">
         <is>
-          <t>CS Beef Packers, LLC (Kuna, ID)</t>
+          <t>Les Aliments Johnvince Foods</t>
         </is>
       </c>
       <c r="D1077" s="2" t="inlineStr">
         <is>
-          <t>Fire River Farms / Beef 73L</t>
+          <t>Les Aliments Johnvince</t>
         </is>
       </c>
       <c r="E1077" s="2" t="inlineStr">
         <is>
-          <t>Raw ground beef ~22,912 lbs (EST 630)</t>
+          <t>Raw Pecan Halves (230 g)</t>
         </is>
       </c>
       <c r="F1077" s="2" t="inlineStr">
         <is>
-          <t>E. coli O145 (STEC)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1077" s="2" t="inlineStr">
         <is>
-          <t>STEC contamination</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1077" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I1077" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1077" s="2" t="inlineStr">
@@ -68338,14 +68338,14 @@
       </c>
       <c r="M1077" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsis.usda.gov/recalls-alerts/cs-beef-packers-llc-recalls-ground-beef-products-may-be-contaminated-e--coli-o145</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/aliments-johnvince-brand-pecans-halves-raw-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B1078" s="2" t="inlineStr">
@@ -68355,32 +68355,32 @@
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>Slade Gorton &amp; Co., Inc.</t>
+          <t>Prime Food Processing LLC</t>
         </is>
       </c>
       <c r="D1078" s="2" t="inlineStr">
         <is>
-          <t>Wellsley Farms</t>
+          <t>(Dried Croaker Fish)</t>
         </is>
       </c>
       <c r="E1078" s="2" t="inlineStr">
         <is>
-          <t>Farm-Raised Atlantic Salmon, 2-lb bags (sold at BJ's Wholesale Club)</t>
+          <t>Uneviscerated Dried Croaker Fish</t>
         </is>
       </c>
       <c r="F1078" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Clostridium botulinum</t>
         </is>
       </c>
       <c r="G1078" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Risk of botulism — fish not adequately eviscerated</t>
         </is>
       </c>
       <c r="H1078" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="I1078" s="2" t="inlineStr">
@@ -68401,59 +68401,59 @@
       </c>
       <c r="M1078" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/slade-gorton-co-inc-recalls-one-lot-wellsley-farms-farm-raised-atlantic-salmon-sold-bjs-wholesale</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/prime-food-processing-llc-issues-safety-warning-regarding-uneviscerated-dried-croaker-fish</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" s="2" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B1079" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C1079" s="2" t="inlineStr">
         <is>
-          <t>Phoenicia Group Inc.</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="D1079" s="2" t="inlineStr">
         <is>
-          <t>Al Kanater</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="E1079" s="2" t="inlineStr">
         <is>
-          <t>Halawa with Pistachio (450 g)</t>
+          <t>SMA Infant Formula and Follow-On Formula</t>
         </is>
       </c>
       <c r="F1079" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Cereulide (B. cereus toxin)</t>
         </is>
       </c>
       <c r="G1079" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Cereulide (B. cereus toxin) contamination</t>
         </is>
       </c>
       <c r="H1079" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1079" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J1079" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1079" s="2" t="n">
@@ -68464,54 +68464,54 @@
       </c>
       <c r="M1079" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/al-kanater-brand-halawa-pistachio-recalled-due-salmonella</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026-update-2</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B1080" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>PLUKON MAASMECHELEN Plukon Maasmechelen NV</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="D1080" s="2" t="inlineStr">
         <is>
-          <t>Unbranded</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="E1080" s="2" t="inlineStr">
         <is>
-          <t>Chicken filet 1 kg, chicken aiguillettes 500 g, chicken filet 2.5 kg, à la minute filet 600 g, halal chicken filet 4×2.5 kg, halal chicken filet 1 kg, chicken aiguillettes 1000 g (multi-SKU plastic trays)</t>
+          <t>SMA Infant Formula and Follow-On Formula</t>
         </is>
       </c>
       <c r="F1080" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Enteritidis</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="G1080" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Enteritidis (causative agent of salmonellosis)</t>
+          <t>Cereulide (B. cereus toxin) contamination</t>
         </is>
       </c>
       <c r="H1080" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1080" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J1080" s="2" t="inlineStr">
@@ -68523,23 +68523,23 @@
         <v>1</v>
       </c>
       <c r="L1080" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1080" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/21234/Interne</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026-update-1</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B1081" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>CFS (HK)</t>
         </is>
       </c>
       <c r="C1081" s="2" t="inlineStr">
@@ -68549,12 +68549,12 @@
       </c>
       <c r="D1081" s="2" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>Aptamil</t>
         </is>
       </c>
       <c r="E1081" s="2" t="inlineStr">
         <is>
-          <t>several Aptamil and Cow &amp; Gate First Infant Milk and Follow on Milk formula products</t>
+          <t>Aptamil powdered infant formula</t>
         </is>
       </c>
       <c r="F1081" s="2" t="inlineStr">
@@ -68564,7 +68564,7 @@
       </c>
       <c r="G1081" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Cereulide (B. cereus toxin) contamination</t>
         </is>
       </c>
       <c r="H1081" s="2" t="inlineStr">
@@ -68574,12 +68574,12 @@
       </c>
       <c r="I1081" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J1081" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="K1081" s="2" t="n">
@@ -68590,59 +68590,59 @@
       </c>
       <c r="M1081" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-05-2026</t>
+          <t>https://www.cfs.gov.hk/english/press/20260203_12167.html</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B1082" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>CFS (HK)</t>
         </is>
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>Les Aliments Johnvince Foods</t>
+          <t>— (infant formula manufacturer)</t>
         </is>
       </c>
       <c r="D1082" s="2" t="inlineStr">
         <is>
-          <t>Les Aliments Johnvince</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1082" s="2" t="inlineStr">
         <is>
-          <t>Raw Pecan Halves (230 g)</t>
+          <t>Powdered infant formula (single batch)</t>
         </is>
       </c>
       <c r="F1082" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1082" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Powdered infant formula recall</t>
         </is>
       </c>
       <c r="H1082" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Food Alert</t>
         </is>
       </c>
       <c r="I1082" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J1082" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia-Pacific</t>
         </is>
       </c>
       <c r="K1082" s="2" t="n">
@@ -68653,54 +68653,54 @@
       </c>
       <c r="M1082" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/aliments-johnvince-brand-pecans-halves-raw-recalled-due-salmonella</t>
+          <t>https://www.cfs.gov.hk/english/whatsnew/whatsnew_fa/2026_611.html</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B1083" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1083" s="2" t="inlineStr">
         <is>
-          <t>Prime Food Processing LLC</t>
+          <t>Longsheng (Canada) Agricultural Products Ltd.</t>
         </is>
       </c>
       <c r="D1083" s="2" t="inlineStr">
         <is>
-          <t>(Dried Croaker Fish)</t>
+          <t>Mushmoshi</t>
         </is>
       </c>
       <c r="E1083" s="2" t="inlineStr">
         <is>
-          <t>Uneviscerated Dried Croaker Fish</t>
+          <t>Enoki Mushroom (200 g)</t>
         </is>
       </c>
       <c r="F1083" s="2" t="inlineStr">
         <is>
-          <t>Clostridium botulinum</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1083" s="2" t="inlineStr">
         <is>
-          <t>Risk of botulism — fish not adequately eviscerated</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1083" s="2" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I1083" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1083" s="2" t="inlineStr">
@@ -68716,59 +68716,59 @@
       </c>
       <c r="M1083" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/prime-food-processing-llc-issues-safety-warning-regarding-uneviscerated-dried-croaker-fish</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/mushmoshi-brand-enoki-mushroom-recalled-due-listeria-monocytogenes</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B1084" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>COFEPRIS (MX)</t>
         </is>
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Nestlé México</t>
         </is>
       </c>
       <c r="D1084" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>NAN Alfamino</t>
         </is>
       </c>
       <c r="E1084" s="2" t="inlineStr">
         <is>
-          <t>SMA Infant Formula and Follow-On Formula</t>
+          <t>NAN Alfamino + Alfamino 400 g (imported from Europe; lots with expiration 2027)</t>
         </is>
       </c>
       <c r="F1084" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin)</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1084" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin) contamination</t>
+          <t>Possible cereulide contamination</t>
         </is>
       </c>
       <c r="H1084" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Preventive withdrawal</t>
         </is>
       </c>
       <c r="I1084" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="J1084" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1084" s="2" t="n">
@@ -68779,59 +68779,59 @@
       </c>
       <c r="M1084" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026-update-2</t>
+          <t>https://www.gob.mx/cms/uploads/attachment/file/1047052/Alerta_Sanitaria__Nestl__07012026.pdf</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B1085" s="2" t="inlineStr">
         <is>
-          <t>FSA (UK)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1085" s="2" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Art Monkey LLC (dba Why Not Natural)</t>
         </is>
       </c>
       <c r="D1085" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>Why Not Natural</t>
         </is>
       </c>
       <c r="E1085" s="2" t="inlineStr">
         <is>
-          <t>SMA Infant Formula and Follow-On Formula</t>
+          <t>Pure Organic Moringa Green Superfood capsules</t>
         </is>
       </c>
       <c r="F1085" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Salmonella Newport</t>
         </is>
       </c>
       <c r="G1085" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin) contamination</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H1085" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1085" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1085" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1085" s="2" t="n">
@@ -68842,44 +68842,44 @@
       </c>
       <c r="M1085" s="2" t="inlineStr">
         <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026-update-1</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/why-not-natural-houston-texas-recalling-its-why-not-natural-organic-moringa-green-superfood-because</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B1086" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK)</t>
+          <t>NVWA (NL)</t>
         </is>
       </c>
       <c r="C1086" s="2" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>Nutrilon (Danone)</t>
         </is>
       </c>
       <c r="D1086" s="2" t="inlineStr">
         <is>
-          <t>Aptamil</t>
+          <t>Nutrilon</t>
         </is>
       </c>
       <c r="E1086" s="2" t="inlineStr">
         <is>
-          <t>Aptamil powdered infant formula</t>
+          <t>Infant formula / zuigelingenvoeding</t>
         </is>
       </c>
       <c r="F1086" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin)</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="G1086" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin) contamination</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="H1086" s="2" t="inlineStr">
@@ -68889,75 +68889,75 @@
       </c>
       <c r="I1086" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="J1086" s="2" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1086" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1086" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1086" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/press/20260203_12167.html</t>
+          <t>https://www.nvwa.nl/actueel/nieuws/2026/01/23/nvwa-monitort-situatie-zuigelingenvoeding-nauwgezet</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B1087" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK)</t>
+          <t>FSANZ (AU)</t>
         </is>
       </c>
       <c r="C1087" s="2" t="inlineStr">
         <is>
-          <t>— (infant formula manufacturer)</t>
+          <t>Nestlé Australia</t>
         </is>
       </c>
       <c r="D1087" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alfamino</t>
         </is>
       </c>
       <c r="E1087" s="2" t="inlineStr">
         <is>
-          <t>Powdered infant formula (single batch)</t>
+          <t>Alfamino Infant Formula (0-12 months) 400g (5 batches)</t>
         </is>
       </c>
       <c r="F1087" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="G1087" s="2" t="inlineStr">
         <is>
-          <t>Powdered infant formula recall</t>
+          <t>Potential presence of cereulide toxin (produced by Bacillus cereus). Linked to a contaminated ingredient identified through international recalls. No cases of illness reported in Australia.</t>
         </is>
       </c>
       <c r="H1087" s="2" t="inlineStr">
         <is>
-          <t>Food Alert</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1087" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="J1087" s="2" t="inlineStr">
         <is>
-          <t>Asia-Pacific</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K1087" s="2" t="n">
@@ -68968,59 +68968,59 @@
       </c>
       <c r="M1087" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfs.gov.hk/english/whatsnew/whatsnew_fa/2026_611.html</t>
+          <t>https://www.foodstandards.gov.au/food-recalls/recall-alert/nestle-alfamino-infant-formula-0-12-months-400g</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B1088" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>FAVV (BE)</t>
         </is>
       </c>
       <c r="C1088" s="2" t="inlineStr">
         <is>
-          <t>Longsheng (Canada) Agricultural Products Ltd.</t>
+          <t>Danone</t>
         </is>
       </c>
       <c r="D1088" s="2" t="inlineStr">
         <is>
-          <t>Mushmoshi</t>
+          <t>Nutrilon</t>
         </is>
       </c>
       <c r="E1088" s="2" t="inlineStr">
         <is>
-          <t>Enoki Mushroom (200 g)</t>
+          <t>Various Nutrilon infant formula</t>
         </is>
       </c>
       <c r="F1088" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Cereulide (B. cereus toxin)</t>
         </is>
       </c>
       <c r="G1088" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Cereulide (B. cereus toxin) contamination</t>
         </is>
       </c>
       <c r="H1088" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1088" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="J1088" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1088" s="2" t="n">
@@ -69031,59 +69031,59 @@
       </c>
       <c r="M1088" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/mushmoshi-brand-enoki-mushroom-recalled-due-listeria-monocytogenes</t>
+          <t>https://favv-afsca.be/nl/producten/terugroeping-van-danone-0</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B1089" s="2" t="inlineStr">
         <is>
-          <t>COFEPRIS (MX)</t>
+          <t>BLV (CH)</t>
         </is>
       </c>
       <c r="C1089" s="2" t="inlineStr">
         <is>
-          <t>Nestlé México</t>
+          <t>(BLV public warning — multiple producers)</t>
         </is>
       </c>
       <c r="D1089" s="2" t="inlineStr">
         <is>
-          <t>NAN Alfamino</t>
+          <t>Migros</t>
         </is>
       </c>
       <c r="E1089" s="2" t="inlineStr">
         <is>
-          <t>NAN Alfamino + Alfamino 400 g (imported from Europe; lots with expiration 2027)</t>
+          <t>Bio-Power Mix</t>
         </is>
       </c>
       <c r="F1089" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1089" s="2" t="inlineStr">
         <is>
-          <t>Possible cereulide contamination</t>
+          <t>Salmonella detected in Bio-Power Mix</t>
         </is>
       </c>
       <c r="H1089" s="2" t="inlineStr">
         <is>
-          <t>Preventive withdrawal</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1089" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="J1089" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1089" s="2" t="n">
@@ -69094,14 +69094,14 @@
       </c>
       <c r="M1089" s="2" t="inlineStr">
         <is>
-          <t>https://www.gob.mx/cms/uploads/attachment/file/1047052/Alerta_Sanitaria__Nestl__07012026.pdf</t>
+          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-bio-power-mix.pdf.download.pdf/Oeffentliche%20Warnung_Salmonellen%20in%20Bio%20Power%20Mix_verkauft%20bei%20Migros%20DE.pdf</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B1090" s="2" t="inlineStr">
@@ -69111,32 +69111,32 @@
       </c>
       <c r="C1090" s="2" t="inlineStr">
         <is>
-          <t>Art Monkey LLC (dba Why Not Natural)</t>
+          <t>Navitas Organics</t>
         </is>
       </c>
       <c r="D1090" s="2" t="inlineStr">
         <is>
-          <t>Why Not Natural</t>
+          <t>Navitas Organics</t>
         </is>
       </c>
       <c r="E1090" s="2" t="inlineStr">
         <is>
-          <t>Pure Organic Moringa Green Superfood capsules</t>
+          <t>Organic Chia Seeds, 8 oz</t>
         </is>
       </c>
       <c r="F1090" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Newport</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1090" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1090" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I1090" s="2" t="inlineStr">
@@ -69153,11 +69153,11 @@
         <v>1</v>
       </c>
       <c r="L1090" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1090" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/why-not-natural-houston-texas-recalling-its-why-not-natural-organic-moringa-green-superfood-because</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/navitas-organics-voluntarily-recalls-select-lots-8oz-organic-chia-seeds-because-possible-health-risk</t>
         </is>
       </c>
     </row>
@@ -69169,22 +69169,22 @@
       </c>
       <c r="B1091" s="2" t="inlineStr">
         <is>
-          <t>NVWA (NL)</t>
+          <t>FSANZ (AU)</t>
         </is>
       </c>
       <c r="C1091" s="2" t="inlineStr">
         <is>
-          <t>Nutrilon (Danone)</t>
+          <t>Sanulac Nutritionals Australia Pty Ltd</t>
         </is>
       </c>
       <c r="D1091" s="2" t="inlineStr">
         <is>
-          <t>Nutrilon</t>
+          <t>Alula Gold</t>
         </is>
       </c>
       <c r="E1091" s="2" t="inlineStr">
         <is>
-          <t>Infant formula / zuigelingenvoeding</t>
+          <t>Alula Gold Reflux infant formula 900g (0-12 months) and Alula Gold Premium infant formula 900g</t>
         </is>
       </c>
       <c r="F1091" s="2" t="inlineStr">
@@ -69194,7 +69194,7 @@
       </c>
       <c r="G1091" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Cereulide — outbreak</t>
         </is>
       </c>
       <c r="H1091" s="2" t="inlineStr">
@@ -69204,12 +69204,12 @@
       </c>
       <c r="I1091" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="J1091" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="K1091" s="2" t="n">
@@ -69220,7 +69220,7 @@
       </c>
       <c r="M1091" s="2" t="inlineStr">
         <is>
-          <t>https://www.nvwa.nl/actueel/nieuws/2026/01/23/nvwa-monitort-situatie-zuigelingenvoeding-nauwgezet</t>
+          <t>https://www.foodstandards.gov.au/news/cereulide-toxin-infant-formula-products</t>
         </is>
       </c>
     </row>
@@ -69232,34 +69232,34 @@
       </c>
       <c r="B1092" s="2" t="inlineStr">
         <is>
-          <t>FSANZ (AU)</t>
+          <t>FSAI (IE)</t>
         </is>
       </c>
       <c r="C1092" s="2" t="inlineStr">
         <is>
-          <t>Nestlé Australia</t>
+          <t>Danone infant formula and follow-on formula</t>
         </is>
       </c>
       <c r="D1092" s="2" t="inlineStr">
         <is>
-          <t>Alfamino</t>
+          <t>Danone infant formula and follow-on formula</t>
         </is>
       </c>
       <c r="E1092" s="2" t="inlineStr">
         <is>
-          <t>Alfamino Infant Formula (0-12 months) 400g (5 batches)</t>
+          <t>| Food Safety Authority of Ireland</t>
         </is>
       </c>
       <c r="F1092" s="2" t="inlineStr">
         <is>
+          <t>Cereulide (B. cereus toxin)</t>
+        </is>
+      </c>
+      <c r="G1092" s="2" t="inlineStr">
+        <is>
           <t>Cereulide</t>
         </is>
       </c>
-      <c r="G1092" s="2" t="inlineStr">
-        <is>
-          <t>Potential presence of cereulide toxin (produced by Bacillus cereus). Linked to a contaminated ingredient identified through international recalls. No cases of illness reported in Australia.</t>
-        </is>
-      </c>
       <c r="H1092" s="2" t="inlineStr">
         <is>
           <t>Recall</t>
@@ -69267,12 +69267,12 @@
       </c>
       <c r="I1092" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="J1092" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1092" s="2" t="n">
@@ -69283,7 +69283,7 @@
       </c>
       <c r="M1092" s="2" t="inlineStr">
         <is>
-          <t>https://www.foodstandards.gov.au/food-recalls/recall-alert/nestle-alfamino-infant-formula-0-12-months-400g</t>
+          <t>https://www.fsai.ie/news-and-alerts/latest-news/danone-infant-formula-and-follow-on-formula-recall</t>
         </is>
       </c>
     </row>
@@ -69295,47 +69295,47 @@
       </c>
       <c r="B1093" s="2" t="inlineStr">
         <is>
-          <t>FAVV (BE)</t>
+          <t>COFEPRIS (MX)</t>
         </is>
       </c>
       <c r="C1093" s="2" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>SANULAC NUTRICIÓN MÉXICO S. de R.L. de C.V.</t>
         </is>
       </c>
       <c r="D1093" s="2" t="inlineStr">
         <is>
-          <t>Nutrilon</t>
+          <t>ALULA Gold Premium / ALULA Gold Comfort</t>
         </is>
       </c>
       <c r="E1093" s="2" t="inlineStr">
         <is>
-          <t>Various Nutrilon infant formula</t>
+          <t>ALULA Gold Premium 1, 2, 3 + ALULA Gold Comfort Kid Premium + ALULA Gold Comfort Premium (38 lots, imported from France, expirations Nov 2026 – Mar 2027)</t>
         </is>
       </c>
       <c r="F1093" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin)</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1093" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin) contamination</t>
+          <t>Preventive market withdrawal — possible cereulide contamination in one ingredient</t>
         </is>
       </c>
       <c r="H1093" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Sanitary alert</t>
         </is>
       </c>
       <c r="I1093" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="J1093" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1093" s="2" t="n">
@@ -69346,54 +69346,54 @@
       </c>
       <c r="M1093" s="2" t="inlineStr">
         <is>
-          <t>https://favv-afsca.be/nl/producten/terugroeping-van-danone-0</t>
+          <t>https://www.gob.mx/cms/uploads/attachment/file/1051500/Alerta_Sanitaria__Alula_23012026.pdf</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B1094" s="2" t="inlineStr">
         <is>
-          <t>BLV (CH)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C1094" s="2" t="inlineStr">
         <is>
-          <t>(BLV public warning — multiple producers)</t>
+          <t>Origin: Italy | Notifying: Austria | Distributed: Austria, Belgium, France, Germany, Ireland, Liechtenstein, Slovenia, Spain, Switzerland, UK (Northern Ireland)</t>
         </is>
       </c>
       <c r="D1094" s="2" t="inlineStr">
         <is>
-          <t>Migros</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1094" s="2" t="inlineStr">
         <is>
-          <t>Bio-Power Mix</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="F1094" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1094" s="2" t="inlineStr">
         <is>
-          <t>Salmonella detected in Bio-Power Mix</t>
+          <t>Listeria monocytogenes detected in cheese of Italian origin distributed across 10+ EU/EEA countries plus UK (Northern Ireland) — alert notification</t>
         </is>
       </c>
       <c r="H1094" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alert notification</t>
         </is>
       </c>
       <c r="I1094" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="J1094" s="2" t="inlineStr">
@@ -69409,14 +69409,14 @@
       </c>
       <c r="M1094" s="2" t="inlineStr">
         <is>
-          <t>https://www.blv.admin.ch/dam/blv/de/dokumente/oeffentliche-warnungen/ow-bio-power-mix.pdf.download.pdf/Oeffentliche%20Warnung_Salmonellen%20in%20Bio%20Power%20Mix_verkauft%20bei%20Migros%20DE.pdf</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/818280</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B1095" s="2" t="inlineStr">
@@ -69426,32 +69426,32 @@
       </c>
       <c r="C1095" s="2" t="inlineStr">
         <is>
-          <t>Navitas Organics</t>
+          <t>Superfoods, Inc. (dba Live it Up)</t>
         </is>
       </c>
       <c r="D1095" s="2" t="inlineStr">
         <is>
-          <t>Navitas Organics</t>
+          <t>Live it Up</t>
         </is>
       </c>
       <c r="E1095" s="2" t="inlineStr">
         <is>
-          <t>Organic Chia Seeds, 8 oz</t>
+          <t>Super Greens dietary supplement powder (Original + Wild Berry)</t>
         </is>
       </c>
       <c r="F1095" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Salmonella Typhimurium</t>
         </is>
       </c>
       <c r="G1095" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H1095" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1095" s="2" t="inlineStr">
@@ -69468,126 +69468,126 @@
         <v>1</v>
       </c>
       <c r="L1095" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1095" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/navitas-organics-voluntarily-recalls-select-lots-8oz-organic-chia-seeds-because-possible-health-risk</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/superfoods-inc-dba-live-it-recalls-live-it-super-greens-because-possible-health-risk</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B1096" s="2" t="inlineStr">
         <is>
-          <t>FSANZ (AU)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C1096" s="2" t="inlineStr">
         <is>
-          <t>Sanulac Nutritionals Australia Pty Ltd</t>
+          <t>Origin: Argentina | Notifying: Netherlands | Distributed: Netherlands, Uruguay</t>
         </is>
       </c>
       <c r="D1096" s="2" t="inlineStr">
         <is>
-          <t>Alula Gold</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1096" s="2" t="inlineStr">
         <is>
-          <t>Alula Gold Reflux infant formula 900g (0-12 months) and Alula Gold Premium infant formula 900g</t>
+          <t>Groundnuts kernels runner</t>
         </is>
       </c>
       <c r="F1096" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Aflatoxins</t>
         </is>
       </c>
       <c r="G1096" s="2" t="inlineStr">
         <is>
-          <t>Cereulide — outbreak</t>
+          <t>Aflatoxin contamination detected in groundnut runner kernels from Argentina, distributed in Netherlands and Uruguay — found by company's own check</t>
         </is>
       </c>
       <c r="H1096" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Information notification for attention</t>
         </is>
       </c>
       <c r="I1096" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J1096" s="2" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1096" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L1096" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1096" s="2" t="inlineStr">
         <is>
-          <t>https://www.foodstandards.gov.au/news/cereulide-toxin-infant-formula-products</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/817723</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B1097" s="2" t="inlineStr">
         <is>
-          <t>FSAI (IE)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1097" s="2" t="inlineStr">
         <is>
-          <t>Danone infant formula and follow-on formula</t>
+          <t>Left Coast Organics</t>
         </is>
       </c>
       <c r="D1097" s="2" t="inlineStr">
         <is>
-          <t>Danone infant formula and follow-on formula</t>
+          <t>Left Coast Organics</t>
         </is>
       </c>
       <c r="E1097" s="2" t="inlineStr">
         <is>
-          <t>| Food Safety Authority of Ireland</t>
+          <t>Organic Chia Seeds (900 g)</t>
         </is>
       </c>
       <c r="F1097" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (B. cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1097" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1097" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I1097" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1097" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1097" s="2" t="n">
@@ -69598,122 +69598,122 @@
       </c>
       <c r="M1097" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsai.ie/news-and-alerts/latest-news/danone-infant-formula-and-follow-on-formula-recall</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/left-coast-organics-brand-organic-chia-seeds-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B1098" s="2" t="inlineStr">
         <is>
-          <t>COFEPRIS (MX)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1098" s="2" t="inlineStr">
         <is>
-          <t>SANULAC NUTRICIÓN MÉXICO S. de R.L. de C.V.</t>
+          <t>General Mills Canada / Pillsbury</t>
         </is>
       </c>
       <c r="D1098" s="2" t="inlineStr">
         <is>
-          <t>ALULA Gold Premium / ALULA Gold Comfort</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E1098" s="2" t="inlineStr">
         <is>
-          <t>ALULA Gold Premium 1, 2, 3 + ALULA Gold Comfort Kid Premium + ALULA Gold Comfort Premium (38 lots, imported from France, expirations Nov 2026 – Mar 2027)</t>
+          <t>Pizza Pops (full product line)</t>
         </is>
       </c>
       <c r="F1098" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>E. coli O26 (STEC)</t>
         </is>
       </c>
       <c r="G1098" s="2" t="inlineStr">
         <is>
-          <t>Preventive market withdrawal — possible cereulide contamination in one ingredient</t>
+          <t>Pathogen contamination — outbreak-linked</t>
         </is>
       </c>
       <c r="H1098" s="2" t="inlineStr">
         <is>
-          <t>Sanitary alert</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I1098" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1098" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1098" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L1098" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1098" s="2" t="inlineStr">
         <is>
-          <t>https://www.gob.mx/cms/uploads/attachment/file/1051500/Alerta_Sanitaria__Alula_23012026.pdf</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/certain-pillsbury-brand-pizza-pops-recalled-due-e-coli-o26</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B1099" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>INVIMA (CO)</t>
         </is>
       </c>
       <c r="C1099" s="2" t="inlineStr">
         <is>
-          <t>Origin: Italy | Notifying: Austria | Distributed: Austria, Belgium, France, Germany, Ireland, Liechtenstein, Slovenia, Spain, Switzerland, UK (Northern Ireland)</t>
+          <t>Nestlé de Colombia S.A.</t>
         </is>
       </c>
       <c r="D1099" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NAN Alfamino</t>
         </is>
       </c>
       <c r="E1099" s="2" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Food for special medical purposes, powder, 400 g, lot 52660017Y2</t>
         </is>
       </c>
       <c r="F1099" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1099" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes detected in cheese of Italian origin distributed across 10+ EU/EEA countries plus UK (Northern Ireland) — alert notification</t>
+          <t>Contamination with cereulide toxin</t>
         </is>
       </c>
       <c r="H1099" s="2" t="inlineStr">
         <is>
-          <t>Alert notification</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1099" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="J1099" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1099" s="2" t="n">
@@ -69724,14 +69724,14 @@
       </c>
       <c r="M1099" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/818280</t>
+          <t>https://www.invima.gov.co/blog/sala-de-prensa-13/alimento-para-propositos-medicos-especiales-contaminado-con-toxina-cereulida-no-ha-sido-comercializado-en-colombia-279</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B1100" s="2" t="inlineStr">
@@ -69741,27 +69741,27 @@
       </c>
       <c r="C1100" s="2" t="inlineStr">
         <is>
-          <t>Superfoods, Inc. (dba Live it Up)</t>
+          <t>Tri-Union Seafoods</t>
         </is>
       </c>
       <c r="D1100" s="2" t="inlineStr">
         <is>
-          <t>Live it Up</t>
+          <t>Genova</t>
         </is>
       </c>
       <c r="E1100" s="2" t="inlineStr">
         <is>
-          <t>Super Greens dietary supplement powder (Original + Wild Berry)</t>
+          <t>Yellowfin Tuna in Olive Oil 5 oz 4-pack + 5 oz can EVOO</t>
         </is>
       </c>
       <c r="F1100" s="2" t="inlineStr">
         <is>
-          <t>Salmonella Typhimurium</t>
+          <t>Clostridium botulinum</t>
         </is>
       </c>
       <c r="G1100" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Botulism risk — defective easy-open pull tabs</t>
         </is>
       </c>
       <c r="H1100" s="2" t="inlineStr">
@@ -69783,126 +69783,126 @@
         <v>1</v>
       </c>
       <c r="L1100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1100" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/superfoods-inc-dba-live-it-recalls-live-it-super-greens-because-possible-health-risk</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/tri-union-seafoods-identifies-additional-quantities-recalled-genovar-tuna-limited-retailers-due</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B1101" s="2" t="inlineStr">
         <is>
-          <t>RASFF (EU)</t>
+          <t>SFA (SG)</t>
         </is>
       </c>
       <c r="C1101" s="2" t="inlineStr">
         <is>
-          <t>Origin: Argentina | Notifying: Netherlands | Distributed: Netherlands, Uruguay</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="D1101" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nestle NAN HA1 SupremePro</t>
         </is>
       </c>
       <c r="E1101" s="2" t="inlineStr">
         <is>
-          <t>Groundnuts kernels runner</t>
+          <t>800 g infant formula, batch 52340017C3, expiry 2027-08-31, country of origin Switzerland</t>
         </is>
       </c>
       <c r="F1101" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1101" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxin contamination detected in groundnut runner kernels from Argentina, distributed in Netherlands and Uruguay — found by company's own check</t>
+          <t>Presence of cereulide toxin</t>
         </is>
       </c>
       <c r="H1101" s="2" t="inlineStr">
         <is>
-          <t>Information notification for attention</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1101" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="J1101" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia-Pacific</t>
         </is>
       </c>
       <c r="K1101" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M1101" s="2" t="inlineStr">
         <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/817723</t>
+          <t>https://www.sfa.gov.sg/news-publications/newsroom/direction-to-recall-additional-infant-formula-products-due-to-presence-of-cereulide-toxin</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B1102" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>RappelConso (FR)</t>
         </is>
       </c>
       <c r="C1102" s="2" t="inlineStr">
         <is>
-          <t>Left Coast Organics</t>
+          <t>O.P.A.DISTRIBUTION OPA DISTRIBUTION</t>
         </is>
       </c>
       <c r="D1102" s="2" t="inlineStr">
         <is>
-          <t>Left Coast Organics</t>
+          <t>AREV</t>
         </is>
       </c>
       <c r="E1102" s="2" t="inlineStr">
         <is>
-          <t>Organic Chia Seeds (900 g)</t>
+          <t>Dried Lerida figs, calibre 8, 500 g tray</t>
         </is>
       </c>
       <c r="F1102" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Aflatoxins / tenuazonic acid (mycotoxins)</t>
         </is>
       </c>
       <c r="G1102" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Maximum limits exceeded for mycotoxins: aflatoxin B1, total aflatoxins, and tenuazonic acid</t>
         </is>
       </c>
       <c r="H1102" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I1102" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="J1102" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1102" s="2" t="n">
@@ -69913,54 +69913,54 @@
       </c>
       <c r="M1102" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/left-coast-organics-brand-organic-chia-seeds-recalled-due-salmonella</t>
+          <t>https://rappel.conso.gouv.fr/fiche-rappel/20978/Interne</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B1103" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>USDA FSIS</t>
         </is>
       </c>
       <c r="C1103" s="2" t="inlineStr">
         <is>
-          <t>General Mills Canada / Pillsbury</t>
+          <t>Suzanna's Kitchen, Inc. (Norcross, GA)</t>
         </is>
       </c>
       <c r="D1103" s="2" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Suzanna's Kitchen</t>
         </is>
       </c>
       <c r="E1103" s="2" t="inlineStr">
         <is>
-          <t>Pizza Pops (full product line)</t>
+          <t>Ready-to-eat grilled chicken breast fillet products, ~13,720 lbs (EST P-1382)</t>
         </is>
       </c>
       <c r="F1103" s="2" t="inlineStr">
         <is>
-          <t>E. coli O26 (STEC)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1103" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination — outbreak-linked</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1103" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1103" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1103" s="2" t="inlineStr">
@@ -69972,63 +69972,63 @@
         <v>1</v>
       </c>
       <c r="L1103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1103" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/certain-pillsbury-brand-pizza-pops-recalled-due-e-coli-o26</t>
+          <t>https://www.fsis.usda.gov/recalls-alerts/suzannas-kitchen-recalls-ready-eat-grilled-chicken-breast-fillet-products-due</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B1104" s="2" t="inlineStr">
         <is>
-          <t>INVIMA (CO)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1104" s="2" t="inlineStr">
         <is>
-          <t>Nestlé de Colombia S.A.</t>
+          <t>The Ambriola Company</t>
         </is>
       </c>
       <c r="D1104" s="2" t="inlineStr">
         <is>
-          <t>NAN Alfamino</t>
+          <t>Ambriola / Locatelli / Member's Mark / Pinna / Boar's Head</t>
         </is>
       </c>
       <c r="E1104" s="2" t="inlineStr">
         <is>
-          <t>Food for special medical purposes, powder, 400 g, lot 52660017Y2</t>
+          <t>11,530 cheese products: Pecorino Romano (multi-brand)</t>
         </is>
       </c>
       <c r="F1104" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1104" s="2" t="inlineStr">
         <is>
-          <t>Contamination with cereulide toxin</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1104" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1104" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1104" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1104" s="2" t="n">
@@ -70039,59 +70039,59 @@
       </c>
       <c r="M1104" s="2" t="inlineStr">
         <is>
-          <t>https://www.invima.gov.co/blog/sala-de-prensa-13/alimento-para-propositos-medicos-especiales-contaminado-con-toxina-cereulida-no-ha-sido-comercializado-en-colombia-279</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/ambriola-company-issues-recall-cheese-products-because-listeria-health-risk</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B1105" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>NCC (ZA)</t>
         </is>
       </c>
       <c r="C1105" s="2" t="inlineStr">
         <is>
-          <t>Tri-Union Seafoods</t>
+          <t>Nestlé South Africa</t>
         </is>
       </c>
       <c r="D1105" s="2" t="inlineStr">
         <is>
-          <t>Genova</t>
+          <t>NAN Special Pro HA</t>
         </is>
       </c>
       <c r="E1105" s="2" t="inlineStr">
         <is>
-          <t>Yellowfin Tuna in Olive Oil 5 oz 4-pack + 5 oz can EVOO</t>
+          <t>NAN Special Pro HA 0–12 infant formula (6 × 800 g)</t>
         </is>
       </c>
       <c r="F1105" s="2" t="inlineStr">
         <is>
-          <t>Clostridium botulinum</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1105" s="2" t="inlineStr">
         <is>
-          <t>Botulism risk — defective easy-open pull tabs</t>
+          <t>Cereulide detected in supplied ingredient</t>
         </is>
       </c>
       <c r="H1105" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1105" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="J1105" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Middle East &amp; Africa</t>
         </is>
       </c>
       <c r="K1105" s="2" t="n">
@@ -70102,59 +70102,59 @@
       </c>
       <c r="M1105" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/tri-union-seafoods-identifies-additional-quantities-recalled-genovar-tuna-limited-retailers-due</t>
+          <t>https://thencc.org.za/product-recall-nan-special-pro-ha-infant-formula-800g/</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" s="2" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B1106" s="2" t="inlineStr">
         <is>
-          <t>SFA (SG)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1106" s="2" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="D1106" s="2" t="inlineStr">
         <is>
-          <t>Nestle NAN HA1 SupremePro</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="E1106" s="2" t="inlineStr">
         <is>
-          <t>800 g infant formula, batch 52340017C3, expiry 2027-08-31, country of origin Switzerland</t>
+          <t>Date-sweetened chocolate bars (8 flavors — expanded recall)</t>
         </is>
       </c>
       <c r="F1106" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1106" s="2" t="inlineStr">
         <is>
-          <t>Presence of cereulide toxin</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1106" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I1106" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1106" s="2" t="inlineStr">
         <is>
-          <t>Asia-Pacific</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1106" s="2" t="n">
@@ -70165,59 +70165,59 @@
       </c>
       <c r="M1106" s="2" t="inlineStr">
         <is>
-          <t>https://www.sfa.gov.sg/news-publications/newsroom/direction-to-recall-additional-infant-formula-products-due-to-presence-of-cereulide-toxin</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-expands-voluntary-recall-select-chocolate-bars-due-possible-salmonella-contamination</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B1107" s="2" t="inlineStr">
         <is>
-          <t>RappelConso (FR)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1107" s="2" t="inlineStr">
         <is>
-          <t>O.P.A.DISTRIBUTION OPA DISTRIBUTION</t>
+          <t>Loblaws Companies Limited</t>
         </is>
       </c>
       <c r="D1107" s="2" t="inlineStr">
         <is>
-          <t>AREV</t>
+          <t>no name</t>
         </is>
       </c>
       <c r="E1107" s="2" t="inlineStr">
         <is>
-          <t>Dried Lerida figs, calibre 8, 500 g tray</t>
+          <t>Beef Burgers (1.36 kg)</t>
         </is>
       </c>
       <c r="F1107" s="2" t="inlineStr">
         <is>
-          <t>Aflatoxins / tenuazonic acid (mycotoxins)</t>
+          <t>E. coli O157:H7</t>
         </is>
       </c>
       <c r="G1107" s="2" t="inlineStr">
         <is>
-          <t>Maximum limits exceeded for mycotoxins: aflatoxin B1, total aflatoxins, and tenuazonic acid</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1107" s="2" t="inlineStr">
         <is>
-          <t>Voluntary</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="I1107" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1107" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1107" s="2" t="n">
@@ -70228,59 +70228,59 @@
       </c>
       <c r="M1107" s="2" t="inlineStr">
         <is>
-          <t>https://rappel.conso.gouv.fr/fiche-rappel/20978/Interne</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/no-name-brand-beef-burgers-recalled-due-e-coli-o157h7</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B1108" s="2" t="inlineStr">
         <is>
-          <t>USDA FSIS</t>
+          <t>FDA PH</t>
         </is>
       </c>
       <c r="C1108" s="2" t="inlineStr">
         <is>
-          <t>Suzanna's Kitchen, Inc. (Norcross, GA)</t>
+          <t>Nestlé Philippines, Inc.</t>
         </is>
       </c>
       <c r="D1108" s="2" t="inlineStr">
         <is>
-          <t>Suzanna's Kitchen</t>
+          <t>NAN OPTIPRO, NANKID OPTIPRO</t>
         </is>
       </c>
       <c r="E1108" s="2" t="inlineStr">
         <is>
-          <t>Ready-to-eat grilled chicken breast fillet products, ~13,720 lbs (EST P-1382)</t>
+          <t>NAN OPTIPRO Infant Formula (0-6 months, 6-12 months) and NAN OPTI Milk Supplement (1-3 years) and NANKID OPTIPRO (3+ years) — multiple batch numbers</t>
         </is>
       </c>
       <c r="F1108" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="G1108" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="H1108" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1108" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="J1108" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="K1108" s="2" t="n">
@@ -70291,14 +70291,14 @@
       </c>
       <c r="M1108" s="2" t="inlineStr">
         <is>
-          <t>https://www.fsis.usda.gov/recalls-alerts/suzannas-kitchen-recalls-ready-eat-grilled-chicken-breast-fillet-products-due</t>
+          <t>https://www.fda.gov.ph/fda-advisory-no-2026-0030-voluntary-recall-of-nan-optipro-and-nankid-optipro-products/</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B1109" s="2" t="inlineStr">
@@ -70308,27 +70308,27 @@
       </c>
       <c r="C1109" s="2" t="inlineStr">
         <is>
-          <t>The Ambriola Company</t>
+          <t>Diva Fam Inc.</t>
         </is>
       </c>
       <c r="D1109" s="2" t="inlineStr">
         <is>
-          <t>Ambriola / Locatelli / Member's Mark / Pinna / Boar's Head</t>
+          <t>True Sea Moss</t>
         </is>
       </c>
       <c r="E1109" s="2" t="inlineStr">
         <is>
-          <t>11,530 cheese products: Pecorino Romano (multi-brand)</t>
+          <t>Sea Moss Gel Superfood, 16 fl oz</t>
         </is>
       </c>
       <c r="F1109" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Clostridium botulinum</t>
         </is>
       </c>
       <c r="G1109" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Botulism risk — missing process authority</t>
         </is>
       </c>
       <c r="H1109" s="2" t="inlineStr">
@@ -70354,59 +70354,59 @@
       </c>
       <c r="M1109" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/ambriola-company-issues-recall-cheese-products-because-listeria-health-risk</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/diva-fam-inc-announces-voluntary-recall-sea-moss-gel-superfood-products-due-possible-health-risk</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B1110" s="2" t="inlineStr">
         <is>
-          <t>NCC (ZA)</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1110" s="2" t="inlineStr">
         <is>
-          <t>Nestlé South Africa</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="D1110" s="2" t="inlineStr">
         <is>
-          <t>NAN Special Pro HA</t>
+          <t>Spring &amp; Mulberry</t>
         </is>
       </c>
       <c r="E1110" s="2" t="inlineStr">
         <is>
-          <t>NAN Special Pro HA 0–12 infant formula (6 × 800 g)</t>
+          <t>Mint Leaf Date-sweetened Chocolate Bar (initial recall)</t>
         </is>
       </c>
       <c r="F1110" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1110" s="2" t="inlineStr">
         <is>
-          <t>Cereulide detected in supplied ingredient</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1110" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Class II</t>
         </is>
       </c>
       <c r="I1110" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1110" s="2" t="inlineStr">
         <is>
-          <t>Middle East &amp; Africa</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1110" s="2" t="n">
@@ -70417,59 +70417,59 @@
       </c>
       <c r="M1110" s="2" t="inlineStr">
         <is>
-          <t>https://thencc.org.za/product-recall-nan-special-pro-ha-infant-formula-800g/</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-issues-voluntary-recall-mint-leaf-date-sweetened-chocolate-bar-due-possible</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B1111" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>ANMAT (AR)</t>
         </is>
       </c>
       <c r="C1111" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>Nestlé Argentina S.A.</t>
         </is>
       </c>
       <c r="D1111" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>Nestlé infant formulas</t>
         </is>
       </c>
       <c r="E1111" s="2" t="inlineStr">
         <is>
-          <t>Date-sweetened chocolate bars (8 flavors — expanded recall)</t>
+          <t>Multiple lots of infant formula milk</t>
         </is>
       </c>
       <c r="F1111" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1111" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Possible cereulide presence in raw material — voluntary preventive withdrawal</t>
         </is>
       </c>
       <c r="H1111" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Preventive withdrawal</t>
         </is>
       </c>
       <c r="I1111" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J1111" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1111" s="2" t="n">
@@ -70480,39 +70480,39 @@
       </c>
       <c r="M1111" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-expands-voluntary-recall-select-chocolate-bars-due-possible-salmonella-contamination</t>
+          <t>https://chequeado.com/el-explicador/la-anmat-ordeno-el-retiro-preventivo-de-leches-de-formula-para-bebes-cuales-son-los-lotes-afectados/</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B1112" s="2" t="inlineStr">
         <is>
-          <t>CFIA</t>
+          <t>FDA</t>
         </is>
       </c>
       <c r="C1112" s="2" t="inlineStr">
         <is>
-          <t>Loblaws Companies Limited</t>
+          <t>Primavera Nueva Inc.</t>
         </is>
       </c>
       <c r="D1112" s="2" t="inlineStr">
         <is>
-          <t>no name</t>
+          <t>Primavera Nueva</t>
         </is>
       </c>
       <c r="E1112" s="2" t="inlineStr">
         <is>
-          <t>Beef Burgers (1.36 kg)</t>
+          <t>4-count tamales</t>
         </is>
       </c>
       <c r="F1112" s="2" t="inlineStr">
         <is>
-          <t>E. coli O157:H7</t>
+          <t>Listeria monocytogenes</t>
         </is>
       </c>
       <c r="G1112" s="2" t="inlineStr">
@@ -70522,12 +70522,12 @@
       </c>
       <c r="H1112" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Class I</t>
         </is>
       </c>
       <c r="I1112" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J1112" s="2" t="inlineStr">
@@ -70543,59 +70543,59 @@
       </c>
       <c r="M1112" s="2" t="inlineStr">
         <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/no-name-brand-beef-burgers-recalled-due-e-coli-o157h7</t>
+          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/primavera-nueva-inc-issues-voluntary-recall-select-4-count-tamales-because-possible-health-risk-0</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B1113" s="2" t="inlineStr">
         <is>
-          <t>FDA PH</t>
+          <t>ANVISA (BR)</t>
         </is>
       </c>
       <c r="C1113" s="2" t="inlineStr">
         <is>
-          <t>Nestlé Philippines, Inc.</t>
+          <t>Nestlé Brasil Ltda</t>
         </is>
       </c>
       <c r="D1113" s="2" t="inlineStr">
         <is>
-          <t>NAN OPTIPRO, NANKID OPTIPRO</t>
+          <t>Nestogeno / Nan Supreme / Nanlac / Alfamino</t>
         </is>
       </c>
       <c r="E1113" s="2" t="inlineStr">
         <is>
-          <t>NAN OPTIPRO Infant Formula (0-6 months, 6-12 months) and NAN OPTI Milk Supplement (1-3 years) and NANKID OPTIPRO (3+ years) — multiple batch numbers</t>
+          <t>Infant formulas — multiple lots, multiple brands</t>
         </is>
       </c>
       <c r="F1113" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1113" s="2" t="inlineStr">
         <is>
-          <t>Cereulide</t>
+          <t>Toxin contamination</t>
         </is>
       </c>
       <c r="H1113" s="2" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1113" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J1113" s="2" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1113" s="2" t="n">
@@ -70606,59 +70606,59 @@
       </c>
       <c r="M1113" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov.ph/fda-advisory-no-2026-0030-voluntary-recall-of-nan-optipro-and-nankid-optipro-products/</t>
+          <t>https://www.gov.br/anvisa/pt-br/assuntos/noticias-anvisa/2026/proibida-venda-de-formula-infantil-com-risco-de-contaminacao-por-toxina</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B1114" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>CFS (HK)</t>
         </is>
       </c>
       <c r="C1114" s="2" t="inlineStr">
         <is>
-          <t>Diva Fam Inc.</t>
+          <t>— (infant formula manufacturer)</t>
         </is>
       </c>
       <c r="D1114" s="2" t="inlineStr">
         <is>
-          <t>True Sea Moss</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1114" s="2" t="inlineStr">
         <is>
-          <t>Sea Moss Gel Superfood, 16 fl oz</t>
+          <t>Powdered infant and young children formula (certain batches)</t>
         </is>
       </c>
       <c r="F1114" s="2" t="inlineStr">
         <is>
-          <t>Clostridium botulinum</t>
+          <t>Cereulide (Bacillus cereus toxin)</t>
         </is>
       </c>
       <c r="G1114" s="2" t="inlineStr">
         <is>
-          <t>Botulism risk — missing process authority</t>
+          <t>Powdered infant formula recall</t>
         </is>
       </c>
       <c r="H1114" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Food Alert</t>
         </is>
       </c>
       <c r="I1114" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="J1114" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Asia-Pacific</t>
         </is>
       </c>
       <c r="K1114" s="2" t="n">
@@ -70669,59 +70669,59 @@
       </c>
       <c r="M1114" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/diva-fam-inc-announces-voluntary-recall-sea-moss-gel-superfood-products-due-possible-health-risk</t>
+          <t>https://www.cfs.gov.hk/english/whatsnew/whatsnew_fa/2026_610.html</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B1115" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C1115" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>Origin: Romania | Notifying: Italy | Distributed: Italy</t>
         </is>
       </c>
       <c r="D1115" s="2" t="inlineStr">
         <is>
-          <t>Spring &amp; Mulberry</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E1115" s="2" t="inlineStr">
         <is>
-          <t>Mint Leaf Date-sweetened Chocolate Bar (initial recall)</t>
+          <t>Chicken breast (petto di pollo / chicken breast)</t>
         </is>
       </c>
       <c r="F1115" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Salmonella Enteritidis</t>
         </is>
       </c>
       <c r="G1115" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Salmonella enteritidis detected in chicken breast of Romanian origin distributed in Italy</t>
         </is>
       </c>
       <c r="H1115" s="2" t="inlineStr">
         <is>
-          <t>Class II</t>
+          <t>Information notification for attention</t>
         </is>
       </c>
       <c r="I1115" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="J1115" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1115" s="2" t="n">
@@ -70732,34 +70732,34 @@
       </c>
       <c r="M1115" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/spring-mulberry-issues-voluntary-recall-mint-leaf-date-sweetened-chocolate-bar-due-possible</t>
+          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/814607</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B1116" s="2" t="inlineStr">
         <is>
-          <t>ANMAT (AR)</t>
+          <t>FSA (UK)</t>
         </is>
       </c>
       <c r="C1116" s="2" t="inlineStr">
         <is>
-          <t>Nestlé Argentina S.A.</t>
+          <t>Nestlé / Danone</t>
         </is>
       </c>
       <c r="D1116" s="2" t="inlineStr">
         <is>
-          <t>Nestlé infant formulas</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="E1116" s="2" t="inlineStr">
         <is>
-          <t>Multiple lots of infant formula milk</t>
+          <t>SMA Infant Formula and Follow-On Formula</t>
         </is>
       </c>
       <c r="F1116" s="2" t="inlineStr">
@@ -70769,22 +70769,22 @@
       </c>
       <c r="G1116" s="2" t="inlineStr">
         <is>
-          <t>Possible cereulide presence in raw material — voluntary preventive withdrawal</t>
+          <t>Toxin contamination — heat-stable cereulide</t>
         </is>
       </c>
       <c r="H1116" s="2" t="inlineStr">
         <is>
-          <t>Preventive withdrawal</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="I1116" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J1116" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1116" s="2" t="n">
@@ -70795,59 +70795,59 @@
       </c>
       <c r="M1116" s="2" t="inlineStr">
         <is>
-          <t>https://chequeado.com/el-explicador/la-anmat-ordeno-el-retiro-preventivo-de-leches-de-formula-para-bebes-cuales-son-los-lotes-afectados/</t>
+          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B1117" s="2" t="inlineStr">
         <is>
-          <t>FDA</t>
+          <t>NVWA (NL)</t>
         </is>
       </c>
       <c r="C1117" s="2" t="inlineStr">
         <is>
-          <t>Primavera Nueva Inc.</t>
+          <t>Nestlé; Danone</t>
         </is>
       </c>
       <c r="D1117" s="2" t="inlineStr">
         <is>
-          <t>Primavera Nueva</t>
+          <t>Nutrilon</t>
         </is>
       </c>
       <c r="E1117" s="2" t="inlineStr">
         <is>
-          <t>4-count tamales</t>
+          <t>Infant formula (melkpoeder / zuigelingenvoeding)</t>
         </is>
       </c>
       <c r="F1117" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Cereulide (B. cereus toxin)</t>
         </is>
       </c>
       <c r="G1117" s="2" t="inlineStr">
         <is>
-          <t>Pathogen contamination</t>
+          <t>Cereulide</t>
         </is>
       </c>
       <c r="H1117" s="2" t="inlineStr">
         <is>
-          <t>Class I</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="I1117" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="J1117" s="2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1117" s="2" t="n">
@@ -70858,59 +70858,59 @@
       </c>
       <c r="M1117" s="2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov/safety/recalls-market-withdrawals-safety-alerts/primavera-nueva-inc-issues-voluntary-recall-select-4-count-tamales-because-possible-health-risk-0</t>
+          <t>https://www.nvwa.nl/actueel/actuele-onderwerpen/5-vragen-over-cereulide-in-zuigelingenvoeding</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B1118" s="2" t="inlineStr">
         <is>
-          <t>ANVISA (BR)</t>
+          <t>CFIA</t>
         </is>
       </c>
       <c r="C1118" s="2" t="inlineStr">
         <is>
-          <t>Nestlé Brasil Ltda</t>
+          <t>Si Ji Mei</t>
         </is>
       </c>
       <c r="D1118" s="2" t="inlineStr">
         <is>
-          <t>Nestogeno / Nan Supreme / Nanlac / Alfamino</t>
+          <t>Si Ji Mei</t>
         </is>
       </c>
       <c r="E1118" s="2" t="inlineStr">
         <is>
-          <t>Infant formulas — multiple lots, multiple brands</t>
+          <t>Wuhan Egg Sheets with Glutinous Rice</t>
         </is>
       </c>
       <c r="F1118" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G1118" s="2" t="inlineStr">
         <is>
-          <t>Toxin contamination</t>
+          <t>Pathogen contamination</t>
         </is>
       </c>
       <c r="H1118" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="I1118" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="J1118" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="K1118" s="2" t="n">
@@ -70921,24 +70921,24 @@
       </c>
       <c r="M1118" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.br/anvisa/pt-br/assuntos/noticias-anvisa/2026/proibida-venda-de-formula-infantil-com-risco-de-contaminacao-por-toxina</t>
+          <t>https://recalls-rappels.canada.ca/en/alert-recall/si-ji-mei-brand-wuhan-egg-sheets-glutinous-rice-recalled-due-salmonella</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B1119" s="2" t="inlineStr">
         <is>
-          <t>CFS (HK)</t>
+          <t>RASFF (EU)</t>
         </is>
       </c>
       <c r="C1119" s="2" t="inlineStr">
         <is>
-          <t>— (infant formula manufacturer)</t>
+          <t>Origin: United Kingdom | Notifying: France | Distributed: Spain</t>
         </is>
       </c>
       <c r="D1119" s="2" t="inlineStr">
@@ -70948,32 +70948,32 @@
       </c>
       <c r="E1119" s="2" t="inlineStr">
         <is>
-          <t>Powdered infant and young children formula (certain batches)</t>
+          <t>Scallops</t>
         </is>
       </c>
       <c r="F1119" s="2" t="inlineStr">
         <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
+          <t>Lipophilic biotoxins (DSP)</t>
         </is>
       </c>
       <c r="G1119" s="2" t="inlineStr">
         <is>
-          <t>Powdered infant formula recall</t>
+          <t>Lipophilic toxins (DSP) detected in scallops of UK origin distributed in Spain — alert notification (border control - consignment released before detection)</t>
         </is>
       </c>
       <c r="H1119" s="2" t="inlineStr">
         <is>
-          <t>Food Alert</t>
+          <t>Alert notification</t>
         </is>
       </c>
       <c r="I1119" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="J1119" s="2" t="inlineStr">
         <is>
-          <t>Asia-Pacific</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K1119" s="2" t="n">
@@ -70983,321 +70983,6 @@
         <v>0</v>
       </c>
       <c r="M1119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cfs.gov.hk/english/whatsnew/whatsnew_fa/2026_610.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="1120">
-      <c r="A1120" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B1120" s="2" t="inlineStr">
-        <is>
-          <t>RASFF (EU)</t>
-        </is>
-      </c>
-      <c r="C1120" s="2" t="inlineStr">
-        <is>
-          <t>Origin: Romania | Notifying: Italy | Distributed: Italy</t>
-        </is>
-      </c>
-      <c r="D1120" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E1120" s="2" t="inlineStr">
-        <is>
-          <t>Chicken breast (petto di pollo / chicken breast)</t>
-        </is>
-      </c>
-      <c r="F1120" s="2" t="inlineStr">
-        <is>
-          <t>Salmonella Enteritidis</t>
-        </is>
-      </c>
-      <c r="G1120" s="2" t="inlineStr">
-        <is>
-          <t>Salmonella enteritidis detected in chicken breast of Romanian origin distributed in Italy</t>
-        </is>
-      </c>
-      <c r="H1120" s="2" t="inlineStr">
-        <is>
-          <t>Information notification for attention</t>
-        </is>
-      </c>
-      <c r="I1120" s="2" t="inlineStr">
-        <is>
-          <t>Romania</t>
-        </is>
-      </c>
-      <c r="J1120" s="2" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="K1120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1120" s="2" t="inlineStr">
-        <is>
-          <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/814607</t>
-        </is>
-      </c>
-    </row>
-    <row r="1121">
-      <c r="A1121" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B1121" s="2" t="inlineStr">
-        <is>
-          <t>FSA (UK)</t>
-        </is>
-      </c>
-      <c r="C1121" s="2" t="inlineStr">
-        <is>
-          <t>Nestlé / Danone</t>
-        </is>
-      </c>
-      <c r="D1121" s="2" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="E1121" s="2" t="inlineStr">
-        <is>
-          <t>SMA Infant Formula and Follow-On Formula</t>
-        </is>
-      </c>
-      <c r="F1121" s="2" t="inlineStr">
-        <is>
-          <t>Cereulide (Bacillus cereus toxin)</t>
-        </is>
-      </c>
-      <c r="G1121" s="2" t="inlineStr">
-        <is>
-          <t>Toxin contamination — heat-stable cereulide</t>
-        </is>
-      </c>
-      <c r="H1121" s="2" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="I1121" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="J1121" s="2" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="K1121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.food.gov.uk/news-alerts/alert/fsa-prin-02-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1122">
-      <c r="A1122" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B1122" s="2" t="inlineStr">
-        <is>
-          <t>NVWA (NL)</t>
-        </is>
-      </c>
-      <c r="C1122" s="2" t="inlineStr">
-        <is>
-          <t>Nestlé; Danone</t>
-        </is>
-      </c>
-      <c r="D1122" s="2" t="inlineStr">
-        <is>
-          <t>Nutrilon</t>
-        </is>
-      </c>
-      <c r="E1122" s="2" t="inlineStr">
-        <is>
-          <t>Infant formula (melkpoeder / zuigelingenvoeding)</t>
-        </is>
-      </c>
-      <c r="F1122" s="2" t="inlineStr">
-        <is>
-          <t>Cereulide (B. cereus toxin)</t>
-        </is>
-      </c>
-      <c r="G1122" s="2" t="inlineStr">
-        <is>
-          <t>Cereulide</t>
-        </is>
-      </c>
-      <c r="H1122" s="2" t="inlineStr">
-        <is>
-          <t>Recall</t>
-        </is>
-      </c>
-      <c r="I1122" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="J1122" s="2" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="K1122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nvwa.nl/actueel/actuele-onderwerpen/5-vragen-over-cereulide-in-zuigelingenvoeding</t>
-        </is>
-      </c>
-    </row>
-    <row r="1123">
-      <c r="A1123" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
-      </c>
-      <c r="B1123" s="2" t="inlineStr">
-        <is>
-          <t>CFIA</t>
-        </is>
-      </c>
-      <c r="C1123" s="2" t="inlineStr">
-        <is>
-          <t>Si Ji Mei</t>
-        </is>
-      </c>
-      <c r="D1123" s="2" t="inlineStr">
-        <is>
-          <t>Si Ji Mei</t>
-        </is>
-      </c>
-      <c r="E1123" s="2" t="inlineStr">
-        <is>
-          <t>Wuhan Egg Sheets with Glutinous Rice</t>
-        </is>
-      </c>
-      <c r="F1123" s="2" t="inlineStr">
-        <is>
-          <t>Salmonella</t>
-        </is>
-      </c>
-      <c r="G1123" s="2" t="inlineStr">
-        <is>
-          <t>Pathogen contamination</t>
-        </is>
-      </c>
-      <c r="H1123" s="2" t="inlineStr">
-        <is>
-          <t>Class 2</t>
-        </is>
-      </c>
-      <c r="I1123" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="J1123" s="2" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="K1123" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1123" s="2" t="inlineStr">
-        <is>
-          <t>https://recalls-rappels.canada.ca/en/alert-recall/si-ji-mei-brand-wuhan-egg-sheets-glutinous-rice-recalled-due-salmonella</t>
-        </is>
-      </c>
-    </row>
-    <row r="1124">
-      <c r="A1124" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B1124" s="2" t="inlineStr">
-        <is>
-          <t>RASFF (EU)</t>
-        </is>
-      </c>
-      <c r="C1124" s="2" t="inlineStr">
-        <is>
-          <t>Origin: United Kingdom | Notifying: France | Distributed: Spain</t>
-        </is>
-      </c>
-      <c r="D1124" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E1124" s="2" t="inlineStr">
-        <is>
-          <t>Scallops</t>
-        </is>
-      </c>
-      <c r="F1124" s="2" t="inlineStr">
-        <is>
-          <t>Lipophilic biotoxins (DSP)</t>
-        </is>
-      </c>
-      <c r="G1124" s="2" t="inlineStr">
-        <is>
-          <t>Lipophilic toxins (DSP) detected in scallops of UK origin distributed in Spain — alert notification (border control - consignment released before detection)</t>
-        </is>
-      </c>
-      <c r="H1124" s="2" t="inlineStr">
-        <is>
-          <t>Alert notification</t>
-        </is>
-      </c>
-      <c r="I1124" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="J1124" s="2" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="K1124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1124" s="2" t="inlineStr">
         <is>
           <t>https://webgate.ec.europa.eu/rasff-window/screen/notification/814459</t>
         </is>
@@ -71337,14 +71022,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-14 17:03 UTC</t>
+          <t>Generated: 2026-07-14 19:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Records: 1123</t>
+          <t>Records: 1118</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -71022,7 +71022,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-14 19:13 UTC</t>
+          <t>Generated: 2026-07-14 19:39 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Update to</t>
+          <t>K O'Connell Fishmongers</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Update to recall of K O'Connell Fishmongers Smoked Salmon Slices (Update 1)</t>
+          <t>Smoked Salmon Slices (Update 1 to FSAI recall)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -72849,7 +72849,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-17 06:24 UTC</t>
+          <t>Generated: 2026-07-17 06:40 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -2157,7 +2157,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Mould</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Mould</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Mould</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Undeclared allergen (egg)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>0</v>
@@ -14214,7 +14214,7 @@
         </is>
       </c>
       <c r="K218" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L218" s="2" t="n">
         <v>0</v>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Foreign material (shell fragments)</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
@@ -31854,7 +31854,7 @@
         </is>
       </c>
       <c r="K498" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L498" s="2" t="n">
         <v>0</v>
@@ -33216,7 +33216,7 @@
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>Salmonella</t>
+          <t>Foreign material (metal)</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr">
@@ -33240,7 +33240,7 @@
         </is>
       </c>
       <c r="K520" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L520" s="2" t="n">
         <v>0</v>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Undeclared allergen (milk)</t>
         </is>
       </c>
       <c r="G539" s="2" t="inlineStr">
@@ -34437,7 +34437,7 @@
         </is>
       </c>
       <c r="K539" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L539" s="2" t="n">
         <v>0</v>
@@ -36138,7 +36138,7 @@
         </is>
       </c>
       <c r="K566" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L566" s="2" t="n">
         <v>0</v>
@@ -72849,7 +72849,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-17 06:40 UTC</t>
+          <t>Generated: 2026-07-17 09:04 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>La Vera Group Pty Ltd- La Vera Cheddar Pepper R/W approx 300g</t>
+          <t>La Vera Group Pty Ltd</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>M&amp;S recalls M&amp;S Food Truffle Gouda due to the presence of Listeria Monocytogenes</t>
+          <t>Marks &amp; Spencer</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Biona Organic Himalayan Basmati Brown Rice</t>
+          <t>Biona Organic</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Leis Sauerampfer (Sorrel)</t>
+          <t>Leis</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>various Glenisk Baby Organic Fromage Frais products</t>
+          <t>Glenisk</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -26145,27 +26145,27 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
+          <t>The Bare Pantry</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>The Bare Pantry</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
           <t>Bare Pantry Shelled Pistachios</t>
         </is>
       </c>
-      <c r="D408" s="2" t="inlineStr">
-        <is>
-          <t>The Bare Pantry</t>
-        </is>
-      </c>
-      <c r="E408" s="2" t="inlineStr">
-        <is>
-          <t>Bare Pantry Shelled Pistachios</t>
-        </is>
-      </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>Listeria monocytogenes</t>
+          <t>Salmonella</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>Bare Pantry Shelled Pistachios</t>
+          <t>Presence of Salmonella (FSAI recall)</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>an additional batch of Green Box Limited Enoki Mushroom (Update 1)</t>
+          <t>Green Box Limited</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
@@ -72849,7 +72849,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-17 09:04 UTC</t>
+          <t>Generated: 2026-07-17 09:26 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Salmonella enteritidis</t>
+          <t>Salmonella Enteritidis</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>EODY / Food Safety News</t>
+          <t>Region of Central Greece / EODY</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chicken fillet and chicken souvlaki — batches supplied to restaurants in Lamia (multiple suppliers)</t>
+          <t>Chicken fillet and chicken souvlaki (multiple suppliers, Lamia)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Salmonella outbreak: 30+ presented to General Hospital of Lamia, 15+ hospitalised; EODY confirmed Salmonella in chicken fillet and chicken souvlaki batches from multiple suppliers; supplier traced, investigation widening</t>
+          <t>Salmonella in chicken fillet and chicken souvlaki batches (Lamia investigation)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -77070,7 +77070,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-24 07:11 UTC</t>
+          <t>Generated: 2026-07-24 07:35 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -77070,7 +77070,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-24 07:35 UTC</t>
+          <t>Generated: 2026-07-24 08:49 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>imposé par arrêté préfectoral</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>imposé par arrêté préfectoral</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>imposé par arrêté préfectoral</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -39455,7 +39455,7 @@
       </c>
       <c r="H619" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I619" s="2" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="H620" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I620" s="2" t="inlineStr">
@@ -39581,7 +39581,7 @@
       </c>
       <c r="H621" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I621" s="2" t="inlineStr">
@@ -39644,7 +39644,7 @@
       </c>
       <c r="H622" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I622" s="2" t="inlineStr">
@@ -39707,7 +39707,7 @@
       </c>
       <c r="H623" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I623" s="2" t="inlineStr">
@@ -39770,7 +39770,7 @@
       </c>
       <c r="H624" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I624" s="2" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="H625" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I625" s="2" t="inlineStr">
@@ -40211,7 +40211,7 @@
       </c>
       <c r="H631" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I631" s="2" t="inlineStr">
@@ -40400,7 +40400,7 @@
       </c>
       <c r="H634" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I634" s="2" t="inlineStr">
@@ -40463,7 +40463,7 @@
       </c>
       <c r="H635" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I635" s="2" t="inlineStr">
@@ -41660,7 +41660,7 @@
       </c>
       <c r="H654" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I654" s="2" t="inlineStr">
@@ -44243,7 +44243,7 @@
       </c>
       <c r="H695" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I695" s="2" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="H696" s="2" t="inlineStr">
         <is>
-          <t>volontaire (sans arrêté préfectoral)</t>
+          <t>Voluntary</t>
         </is>
       </c>
       <c r="I696" s="2" t="inlineStr">
@@ -81220,7 +81220,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-30 02:45 UTC</t>
+          <t>Generated: 2026-07-30 03:01 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -8784,7 +8784,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K132" s="2" t="n">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="K172" s="2" t="n">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K194" s="2" t="n">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="K289" s="2" t="n">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="J496" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K496" s="2" t="n">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="J561" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="K561" s="2" t="n">
@@ -54207,7 +54207,7 @@
       </c>
       <c r="J853" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="K853" s="2" t="n">
@@ -80226,7 +80226,7 @@
       </c>
       <c r="J1266" s="2" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="K1266" s="2" t="n">
@@ -81724,7 +81724,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-30 18:01 UTC</t>
+          <t>Generated: 2026-07-30 20:29 UTC</t>
         </is>
       </c>
     </row>
